--- a/api/2/clv3/xlsx/pt/RegionM49.xlsx
+++ b/api/2/clv3/xlsx/pt/RegionM49.xlsx
@@ -22,36 +22,36 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:sub-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
+    <t>codeforiati:small-island-developing-states</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:land-locked-developing-countries</t>
+  </si>
+  <si>
     <t>codeforiati:intermediate-region-code</t>
   </si>
   <si>
-    <t>codeforiati:sub-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
     <t>codeforiati:least-developed-countries</t>
   </si>
   <si>
+    <t>codeforiati:developed-developing</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-3-code</t>
+  </si>
+  <si>
     <t>codeforiati:region-code</t>
   </si>
   <si>
-    <t>codeforiati:small-island-developing-states</t>
-  </si>
-  <si>
-    <t>codeforiati:land-locked-developing-countries</t>
-  </si>
-  <si>
-    <t>codeforiati:developed-developing</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -61,24 +61,24 @@
     <t>015</t>
   </si>
   <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>DZ</t>
   </si>
   <si>
-    <t>0</t>
+    <t>Developing</t>
+  </si>
+  <si>
+    <t>DZA</t>
   </si>
   <si>
     <t>002</t>
   </si>
   <si>
-    <t>Developing</t>
-  </si>
-  <si>
-    <t>DZA</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -139,15 +139,15 @@
     <t>086</t>
   </si>
   <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>IO</t>
+  </si>
+  <si>
     <t>014</t>
   </si>
   <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>IO</t>
-  </si>
-  <si>
     <t>IOT</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>024</t>
   </si>
   <si>
+    <t>AO</t>
+  </si>
+  <si>
     <t>017</t>
   </si>
   <si>
-    <t>AO</t>
-  </si>
-  <si>
     <t>AGO</t>
   </si>
   <si>
@@ -427,12 +427,12 @@
     <t>072</t>
   </si>
   <si>
+    <t>BW</t>
+  </si>
+  <si>
     <t>018</t>
   </si>
   <si>
-    <t>BW</t>
-  </si>
-  <si>
     <t>BWA</t>
   </si>
   <si>
@@ -475,12 +475,12 @@
     <t>204</t>
   </si>
   <si>
+    <t>BJ</t>
+  </si>
+  <si>
     <t>011</t>
   </si>
   <si>
-    <t>BJ</t>
-  </si>
-  <si>
     <t>BEN</t>
   </si>
   <si>
@@ -631,21 +631,21 @@
     <t>660</t>
   </si>
   <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
     <t>029</t>
   </si>
   <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>AI</t>
+    <t>AIA</t>
   </si>
   <si>
     <t>019</t>
   </si>
   <si>
-    <t>AIA</t>
-  </si>
-  <si>
     <t>028</t>
   </si>
   <si>
@@ -892,12 +892,12 @@
     <t>084</t>
   </si>
   <si>
+    <t>BZ</t>
+  </si>
+  <si>
     <t>013</t>
   </si>
   <si>
-    <t>BZ</t>
-  </si>
-  <si>
     <t>BLZ</t>
   </si>
   <si>
@@ -967,12 +967,12 @@
     <t>032</t>
   </si>
   <si>
+    <t>AR</t>
+  </si>
+  <si>
     <t>005</t>
   </si>
   <si>
-    <t>AR</t>
-  </si>
-  <si>
     <t>ARG</t>
   </si>
   <si>
@@ -1180,12 +1180,12 @@
     <t>KZ</t>
   </si>
   <si>
+    <t>KAZ</t>
+  </si>
+  <si>
     <t>142</t>
   </si>
   <si>
-    <t>KAZ</t>
-  </si>
-  <si>
     <t>417</t>
   </si>
   <si>
@@ -1648,12 +1648,12 @@
     <t>BY</t>
   </si>
   <si>
+    <t>BLR</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>BLR</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -2131,10 +2131,10 @@
     <t>AU</t>
   </si>
   <si>
+    <t>AUS</t>
+  </si>
+  <si>
     <t>009</t>
-  </si>
-  <si>
-    <t>AUS</t>
   </si>
   <si>
     <t>162</t>
@@ -2775,19 +2775,19 @@
       <c r="B2" t="s">
         <v>13</v>
       </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="s">
@@ -2810,19 +2810,19 @@
       <c r="B3" t="s">
         <v>13</v>
       </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
       <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
         <v>16</v>
       </c>
       <c r="I3" t="s">
@@ -2845,19 +2845,19 @@
       <c r="B4" t="s">
         <v>13</v>
       </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
       <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
         <v>16</v>
       </c>
       <c r="I4" t="s">
@@ -2880,19 +2880,19 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
       <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
         <v>16</v>
       </c>
       <c r="I5" t="s">
@@ -2915,23 +2915,23 @@
       <c r="B6" t="s">
         <v>13</v>
       </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
       <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
         <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
         <v>18</v>
@@ -2950,19 +2950,19 @@
       <c r="B7" t="s">
         <v>13</v>
       </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
         <v>35</v>
       </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
       <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
         <v>16</v>
       </c>
       <c r="I7" t="s">
@@ -2985,19 +2985,19 @@
       <c r="B8" t="s">
         <v>13</v>
       </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
       <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
         <v>16</v>
       </c>
       <c r="I8" t="s">
@@ -3024,19 +3024,19 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
         <v>42</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
         <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>16</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
@@ -3062,19 +3062,19 @@
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
         <v>46</v>
       </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
         <v>32</v>
@@ -3100,22 +3100,22 @@
         <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
         <v>49</v>
       </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J11" t="s">
         <v>18</v>
@@ -3138,22 +3138,22 @@
         <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
         <v>52</v>
       </c>
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -3176,22 +3176,22 @@
         <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
         <v>55</v>
       </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
         <v>18</v>
@@ -3214,19 +3214,19 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
         <v>58</v>
       </c>
-      <c r="F14" t="s">
-        <v>32</v>
-      </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
         <v>32</v>
@@ -3252,19 +3252,19 @@
         <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
         <v>61</v>
       </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I15" t="s">
         <v>16</v>
@@ -3290,19 +3290,19 @@
         <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" t="s">
         <v>64</v>
       </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I16" t="s">
         <v>16</v>
@@ -3328,22 +3328,22 @@
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
         <v>67</v>
       </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
         <v>18</v>
@@ -3366,19 +3366,19 @@
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" t="s">
         <v>70</v>
       </c>
-      <c r="F18" t="s">
-        <v>32</v>
-      </c>
       <c r="G18" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I18" t="s">
         <v>32</v>
@@ -3404,19 +3404,19 @@
         <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
         <v>73</v>
       </c>
-      <c r="F19" t="s">
-        <v>16</v>
-      </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I19" t="s">
         <v>16</v>
@@ -3442,19 +3442,19 @@
         <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" t="s">
         <v>76</v>
       </c>
-      <c r="F20" t="s">
-        <v>16</v>
-      </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I20" t="s">
         <v>16</v>
@@ -3480,22 +3480,22 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" t="s">
         <v>79</v>
       </c>
-      <c r="F21" t="s">
-        <v>32</v>
-      </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
         <v>18</v>
@@ -3518,19 +3518,19 @@
         <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" t="s">
         <v>82</v>
       </c>
-      <c r="F22" t="s">
-        <v>16</v>
-      </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I22" t="s">
         <v>16</v>
@@ -3556,19 +3556,19 @@
         <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" t="s">
         <v>85</v>
       </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I23" t="s">
         <v>32</v>
@@ -3594,19 +3594,19 @@
         <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" t="s">
         <v>88</v>
       </c>
-      <c r="F24" t="s">
-        <v>16</v>
-      </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I24" t="s">
         <v>16</v>
@@ -3632,22 +3632,22 @@
         <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" t="s">
         <v>91</v>
       </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
         <v>18</v>
@@ -3670,19 +3670,19 @@
         <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" t="s">
         <v>94</v>
       </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I26" t="s">
         <v>32</v>
@@ -3708,19 +3708,19 @@
         <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" t="s">
         <v>97</v>
       </c>
-      <c r="F27" t="s">
-        <v>32</v>
-      </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I27" t="s">
         <v>32</v>
@@ -3746,22 +3746,22 @@
         <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" t="s">
         <v>100</v>
       </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I28" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J28" t="s">
         <v>18</v>
@@ -3784,19 +3784,19 @@
         <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" t="s">
         <v>103</v>
       </c>
-      <c r="F29" t="s">
-        <v>32</v>
-      </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I29" t="s">
         <v>32</v>
@@ -3822,22 +3822,22 @@
         <v>41</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" t="s">
         <v>106</v>
       </c>
-      <c r="F30" t="s">
-        <v>16</v>
-      </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I30" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J30" t="s">
         <v>18</v>
@@ -3857,25 +3857,25 @@
         <v>13</v>
       </c>
       <c r="C31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" t="s">
         <v>109</v>
       </c>
-      <c r="D31" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+      <c r="H31" t="s">
         <v>110</v>
       </c>
-      <c r="F31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" t="s">
-        <v>16</v>
-      </c>
       <c r="I31" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J31" t="s">
         <v>18</v>
@@ -3895,22 +3895,22 @@
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" t="s">
         <v>113</v>
       </c>
-      <c r="F32" t="s">
-        <v>16</v>
-      </c>
       <c r="G32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="I32" t="s">
         <v>16</v>
@@ -3933,22 +3933,22 @@
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" t="s">
         <v>116</v>
       </c>
-      <c r="F33" t="s">
-        <v>32</v>
-      </c>
       <c r="G33" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="I33" t="s">
         <v>32</v>
@@ -3971,22 +3971,22 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" t="s">
         <v>119</v>
       </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="I34" t="s">
         <v>32</v>
@@ -4009,22 +4009,22 @@
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" t="s">
         <v>122</v>
       </c>
-      <c r="F35" t="s">
-        <v>16</v>
-      </c>
       <c r="G35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="I35" t="s">
         <v>16</v>
@@ -4047,25 +4047,25 @@
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" t="s">
         <v>125</v>
       </c>
-      <c r="F36" t="s">
-        <v>32</v>
-      </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J36" t="s">
         <v>18</v>
@@ -4085,22 +4085,22 @@
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" t="s">
         <v>128</v>
       </c>
-      <c r="F37" t="s">
-        <v>16</v>
-      </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="I37" t="s">
         <v>16</v>
@@ -4123,22 +4123,22 @@
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" t="s">
         <v>131</v>
       </c>
-      <c r="F38" t="s">
-        <v>16</v>
-      </c>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="I38" t="s">
         <v>16</v>
@@ -4161,25 +4161,25 @@
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
         <v>134</v>
       </c>
-      <c r="F39" t="s">
-        <v>32</v>
-      </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H39" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J39" t="s">
         <v>18</v>
@@ -4199,25 +4199,25 @@
         <v>13</v>
       </c>
       <c r="C40" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" t="s">
         <v>137</v>
       </c>
-      <c r="D40" t="s">
-        <v>42</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" t="s">
         <v>138</v>
       </c>
-      <c r="F40" t="s">
-        <v>16</v>
-      </c>
-      <c r="G40" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" t="s">
-        <v>16</v>
-      </c>
       <c r="I40" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J40" t="s">
         <v>18</v>
@@ -4237,25 +4237,25 @@
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" t="s">
         <v>141</v>
       </c>
-      <c r="F41" t="s">
-        <v>16</v>
-      </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="I41" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J41" t="s">
         <v>18</v>
@@ -4275,22 +4275,22 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" t="s">
         <v>144</v>
       </c>
-      <c r="F42" t="s">
-        <v>32</v>
-      </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="I42" t="s">
         <v>32</v>
@@ -4313,22 +4313,22 @@
         <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="D43" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E43" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" t="s">
         <v>147</v>
       </c>
-      <c r="F43" t="s">
-        <v>16</v>
-      </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="I43" t="s">
         <v>16</v>
@@ -4351,22 +4351,22 @@
         <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" t="s">
         <v>150</v>
       </c>
-      <c r="F44" t="s">
-        <v>16</v>
-      </c>
       <c r="G44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="I44" t="s">
         <v>16</v>
@@ -4389,25 +4389,25 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" t="s">
         <v>153</v>
       </c>
-      <c r="D45" t="s">
-        <v>42</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="G45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" t="s">
         <v>154</v>
       </c>
-      <c r="F45" t="s">
-        <v>32</v>
-      </c>
-      <c r="G45" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" t="s">
-        <v>16</v>
-      </c>
       <c r="I45" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J45" t="s">
         <v>18</v>
@@ -4427,22 +4427,22 @@
         <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E46" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" t="s">
         <v>157</v>
       </c>
-      <c r="F46" t="s">
-        <v>32</v>
-      </c>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H46" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I46" t="s">
         <v>32</v>
@@ -4465,22 +4465,22 @@
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D47" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" t="s">
         <v>160</v>
       </c>
-      <c r="F47" t="s">
-        <v>16</v>
-      </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H47" t="s">
-        <v>32</v>
+        <v>154</v>
       </c>
       <c r="I47" t="s">
         <v>16</v>
@@ -4503,22 +4503,22 @@
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D48" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" t="s">
         <v>163</v>
       </c>
-      <c r="F48" t="s">
-        <v>16</v>
-      </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I48" t="s">
         <v>16</v>
@@ -4541,25 +4541,25 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D49" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" t="s">
         <v>166</v>
       </c>
-      <c r="F49" t="s">
-        <v>32</v>
-      </c>
       <c r="G49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J49" t="s">
         <v>18</v>
@@ -4579,22 +4579,22 @@
         <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D50" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" t="s">
         <v>169</v>
       </c>
-      <c r="F50" t="s">
-        <v>16</v>
-      </c>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I50" t="s">
         <v>16</v>
@@ -4617,25 +4617,25 @@
         <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D51" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E51" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" t="s">
         <v>172</v>
       </c>
-      <c r="F51" t="s">
-        <v>32</v>
-      </c>
       <c r="G51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I51" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J51" t="s">
         <v>18</v>
@@ -4655,25 +4655,25 @@
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F52" t="s">
         <v>175</v>
       </c>
-      <c r="F52" t="s">
-        <v>32</v>
-      </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H52" t="s">
-        <v>32</v>
+        <v>154</v>
       </c>
       <c r="I52" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J52" t="s">
         <v>18</v>
@@ -4693,25 +4693,25 @@
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E53" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" t="s">
         <v>178</v>
       </c>
-      <c r="F53" t="s">
-        <v>32</v>
-      </c>
       <c r="G53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H53" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I53" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J53" t="s">
         <v>18</v>
@@ -4731,22 +4731,22 @@
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
         <v>181</v>
       </c>
-      <c r="F54" t="s">
-        <v>32</v>
-      </c>
       <c r="G54" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H54" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I54" t="s">
         <v>32</v>
@@ -4769,25 +4769,25 @@
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D55" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E55" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" t="s">
         <v>184</v>
       </c>
-      <c r="F55" t="s">
-        <v>32</v>
-      </c>
       <c r="G55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H55" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I55" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J55" t="s">
         <v>18</v>
@@ -4807,22 +4807,22 @@
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D56" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E56" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" t="s">
         <v>187</v>
       </c>
-      <c r="F56" t="s">
-        <v>32</v>
-      </c>
       <c r="G56" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H56" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I56" t="s">
         <v>32</v>
@@ -4845,22 +4845,22 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E57" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" t="s">
         <v>190</v>
       </c>
-      <c r="F57" t="s">
-        <v>16</v>
-      </c>
       <c r="G57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H57" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I57" t="s">
         <v>16</v>
@@ -4883,22 +4883,22 @@
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D58" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E58" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" t="s">
         <v>193</v>
       </c>
-      <c r="F58" t="s">
-        <v>16</v>
-      </c>
       <c r="G58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H58" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I58" t="s">
         <v>16</v>
@@ -4921,25 +4921,25 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E59" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" t="s">
         <v>196</v>
       </c>
-      <c r="F59" t="s">
-        <v>32</v>
-      </c>
       <c r="G59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H59" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I59" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J59" t="s">
         <v>18</v>
@@ -4959,25 +4959,25 @@
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E60" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" t="s">
         <v>199</v>
       </c>
-      <c r="F60" t="s">
-        <v>32</v>
-      </c>
       <c r="G60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I60" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J60" t="s">
         <v>18</v>
@@ -4997,25 +4997,25 @@
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E61" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" t="s">
         <v>202</v>
       </c>
-      <c r="F61" t="s">
-        <v>32</v>
-      </c>
       <c r="G61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H61" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="I61" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J61" t="s">
         <v>18</v>
@@ -5038,31 +5038,31 @@
         <v>205</v>
       </c>
       <c r="D62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62" t="s">
         <v>206</v>
       </c>
-      <c r="E62" t="s">
+      <c r="G62" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" t="s">
         <v>207</v>
       </c>
-      <c r="F62" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" t="s">
+      <c r="I62" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" t="s">
+        <v>18</v>
+      </c>
+      <c r="K62" t="s">
         <v>208</v>
       </c>
-      <c r="H62" t="s">
-        <v>32</v>
-      </c>
-      <c r="I62" t="s">
-        <v>16</v>
-      </c>
-      <c r="J62" t="s">
-        <v>18</v>
-      </c>
-      <c r="K62" t="s">
+      <c r="L62" t="s">
         <v>209</v>
-      </c>
-      <c r="L62" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -5076,19 +5076,19 @@
         <v>205</v>
       </c>
       <c r="D63" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" t="s">
         <v>211</v>
       </c>
-      <c r="F63" t="s">
-        <v>16</v>
-      </c>
       <c r="G63" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H63" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I63" t="s">
         <v>16</v>
@@ -5100,7 +5100,7 @@
         <v>212</v>
       </c>
       <c r="L63" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -5114,19 +5114,19 @@
         <v>205</v>
       </c>
       <c r="D64" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64" t="s">
         <v>214</v>
       </c>
-      <c r="F64" t="s">
-        <v>16</v>
-      </c>
       <c r="G64" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H64" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I64" t="s">
         <v>16</v>
@@ -5138,7 +5138,7 @@
         <v>215</v>
       </c>
       <c r="L64" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -5152,19 +5152,19 @@
         <v>205</v>
       </c>
       <c r="D65" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E65" t="s">
+        <v>32</v>
+      </c>
+      <c r="F65" t="s">
         <v>217</v>
       </c>
-      <c r="F65" t="s">
-        <v>16</v>
-      </c>
       <c r="G65" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H65" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I65" t="s">
         <v>16</v>
@@ -5176,7 +5176,7 @@
         <v>218</v>
       </c>
       <c r="L65" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -5190,19 +5190,19 @@
         <v>205</v>
       </c>
       <c r="D66" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E66" t="s">
+        <v>32</v>
+      </c>
+      <c r="F66" t="s">
         <v>220</v>
       </c>
-      <c r="F66" t="s">
-        <v>16</v>
-      </c>
       <c r="G66" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H66" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I66" t="s">
         <v>16</v>
@@ -5214,7 +5214,7 @@
         <v>221</v>
       </c>
       <c r="L66" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -5228,19 +5228,19 @@
         <v>205</v>
       </c>
       <c r="D67" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E67" t="s">
+        <v>32</v>
+      </c>
+      <c r="F67" t="s">
         <v>223</v>
       </c>
-      <c r="F67" t="s">
-        <v>16</v>
-      </c>
       <c r="G67" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H67" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I67" t="s">
         <v>16</v>
@@ -5252,7 +5252,7 @@
         <v>224</v>
       </c>
       <c r="L67" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -5266,19 +5266,19 @@
         <v>205</v>
       </c>
       <c r="D68" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E68" t="s">
+        <v>32</v>
+      </c>
+      <c r="F68" t="s">
         <v>226</v>
       </c>
-      <c r="F68" t="s">
-        <v>16</v>
-      </c>
       <c r="G68" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H68" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I68" t="s">
         <v>16</v>
@@ -5290,7 +5290,7 @@
         <v>227</v>
       </c>
       <c r="L68" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -5304,19 +5304,19 @@
         <v>205</v>
       </c>
       <c r="D69" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E69" t="s">
+        <v>16</v>
+      </c>
+      <c r="F69" t="s">
         <v>229</v>
       </c>
-      <c r="F69" t="s">
-        <v>16</v>
-      </c>
       <c r="G69" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H69" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="I69" t="s">
         <v>16</v>
@@ -5328,7 +5328,7 @@
         <v>230</v>
       </c>
       <c r="L69" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -5342,19 +5342,19 @@
         <v>205</v>
       </c>
       <c r="D70" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E70" t="s">
+        <v>32</v>
+      </c>
+      <c r="F70" t="s">
         <v>232</v>
       </c>
-      <c r="F70" t="s">
-        <v>16</v>
-      </c>
       <c r="G70" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H70" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I70" t="s">
         <v>16</v>
@@ -5366,7 +5366,7 @@
         <v>233</v>
       </c>
       <c r="L70" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -5380,19 +5380,19 @@
         <v>205</v>
       </c>
       <c r="D71" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E71" t="s">
+        <v>32</v>
+      </c>
+      <c r="F71" t="s">
         <v>235</v>
       </c>
-      <c r="F71" t="s">
-        <v>16</v>
-      </c>
       <c r="G71" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H71" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I71" t="s">
         <v>16</v>
@@ -5404,7 +5404,7 @@
         <v>236</v>
       </c>
       <c r="L71" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -5418,19 +5418,19 @@
         <v>205</v>
       </c>
       <c r="D72" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E72" t="s">
+        <v>32</v>
+      </c>
+      <c r="F72" t="s">
         <v>238</v>
       </c>
-      <c r="F72" t="s">
-        <v>16</v>
-      </c>
       <c r="G72" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H72" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I72" t="s">
         <v>16</v>
@@ -5442,7 +5442,7 @@
         <v>239</v>
       </c>
       <c r="L72" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -5456,19 +5456,19 @@
         <v>205</v>
       </c>
       <c r="D73" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E73" t="s">
+        <v>32</v>
+      </c>
+      <c r="F73" t="s">
         <v>241</v>
       </c>
-      <c r="F73" t="s">
-        <v>16</v>
-      </c>
       <c r="G73" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H73" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I73" t="s">
         <v>16</v>
@@ -5480,7 +5480,7 @@
         <v>242</v>
       </c>
       <c r="L73" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -5494,19 +5494,19 @@
         <v>205</v>
       </c>
       <c r="D74" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E74" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74" t="s">
         <v>244</v>
       </c>
-      <c r="F74" t="s">
-        <v>16</v>
-      </c>
       <c r="G74" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H74" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I74" t="s">
         <v>16</v>
@@ -5518,7 +5518,7 @@
         <v>245</v>
       </c>
       <c r="L74" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -5532,19 +5532,19 @@
         <v>205</v>
       </c>
       <c r="D75" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E75" t="s">
+        <v>16</v>
+      </c>
+      <c r="F75" t="s">
         <v>247</v>
       </c>
-      <c r="F75" t="s">
-        <v>16</v>
-      </c>
       <c r="G75" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H75" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="I75" t="s">
         <v>16</v>
@@ -5556,7 +5556,7 @@
         <v>248</v>
       </c>
       <c r="L75" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -5570,22 +5570,22 @@
         <v>205</v>
       </c>
       <c r="D76" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E76" t="s">
+        <v>32</v>
+      </c>
+      <c r="F76" t="s">
         <v>250</v>
       </c>
-      <c r="F76" t="s">
-        <v>32</v>
-      </c>
       <c r="G76" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H76" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I76" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J76" t="s">
         <v>18</v>
@@ -5594,7 +5594,7 @@
         <v>251</v>
       </c>
       <c r="L76" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -5608,19 +5608,19 @@
         <v>205</v>
       </c>
       <c r="D77" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E77" t="s">
+        <v>32</v>
+      </c>
+      <c r="F77" t="s">
         <v>253</v>
       </c>
-      <c r="F77" t="s">
-        <v>16</v>
-      </c>
       <c r="G77" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H77" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I77" t="s">
         <v>16</v>
@@ -5632,7 +5632,7 @@
         <v>254</v>
       </c>
       <c r="L77" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -5646,19 +5646,19 @@
         <v>205</v>
       </c>
       <c r="D78" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E78" t="s">
+        <v>16</v>
+      </c>
+      <c r="F78" t="s">
         <v>256</v>
       </c>
-      <c r="F78" t="s">
-        <v>16</v>
-      </c>
       <c r="G78" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H78" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="I78" t="s">
         <v>16</v>
@@ -5670,7 +5670,7 @@
         <v>257</v>
       </c>
       <c r="L78" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -5684,19 +5684,19 @@
         <v>205</v>
       </c>
       <c r="D79" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E79" t="s">
+        <v>32</v>
+      </c>
+      <c r="F79" t="s">
         <v>259</v>
       </c>
-      <c r="F79" t="s">
-        <v>16</v>
-      </c>
       <c r="G79" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H79" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I79" t="s">
         <v>16</v>
@@ -5708,7 +5708,7 @@
         <v>260</v>
       </c>
       <c r="L79" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -5722,19 +5722,19 @@
         <v>205</v>
       </c>
       <c r="D80" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E80" t="s">
+        <v>32</v>
+      </c>
+      <c r="F80" t="s">
         <v>262</v>
       </c>
-      <c r="F80" t="s">
-        <v>16</v>
-      </c>
       <c r="G80" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H80" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I80" t="s">
         <v>16</v>
@@ -5746,7 +5746,7 @@
         <v>263</v>
       </c>
       <c r="L80" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -5760,19 +5760,19 @@
         <v>205</v>
       </c>
       <c r="D81" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E81" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" t="s">
         <v>265</v>
       </c>
-      <c r="F81" t="s">
-        <v>16</v>
-      </c>
       <c r="G81" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H81" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="I81" t="s">
         <v>16</v>
@@ -5784,7 +5784,7 @@
         <v>266</v>
       </c>
       <c r="L81" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -5798,19 +5798,19 @@
         <v>205</v>
       </c>
       <c r="D82" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E82" t="s">
+        <v>32</v>
+      </c>
+      <c r="F82" t="s">
         <v>268</v>
       </c>
-      <c r="F82" t="s">
-        <v>16</v>
-      </c>
       <c r="G82" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H82" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I82" t="s">
         <v>16</v>
@@ -5822,7 +5822,7 @@
         <v>269</v>
       </c>
       <c r="L82" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -5836,19 +5836,19 @@
         <v>205</v>
       </c>
       <c r="D83" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E83" t="s">
+        <v>32</v>
+      </c>
+      <c r="F83" t="s">
         <v>271</v>
       </c>
-      <c r="F83" t="s">
-        <v>16</v>
-      </c>
       <c r="G83" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H83" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I83" t="s">
         <v>16</v>
@@ -5860,7 +5860,7 @@
         <v>272</v>
       </c>
       <c r="L83" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -5874,19 +5874,19 @@
         <v>205</v>
       </c>
       <c r="D84" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E84" t="s">
+        <v>16</v>
+      </c>
+      <c r="F84" t="s">
         <v>274</v>
       </c>
-      <c r="F84" t="s">
-        <v>16</v>
-      </c>
       <c r="G84" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H84" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="I84" t="s">
         <v>16</v>
@@ -5898,7 +5898,7 @@
         <v>275</v>
       </c>
       <c r="L84" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -5912,19 +5912,19 @@
         <v>205</v>
       </c>
       <c r="D85" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E85" t="s">
+        <v>32</v>
+      </c>
+      <c r="F85" t="s">
         <v>277</v>
       </c>
-      <c r="F85" t="s">
-        <v>16</v>
-      </c>
       <c r="G85" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H85" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I85" t="s">
         <v>16</v>
@@ -5936,7 +5936,7 @@
         <v>278</v>
       </c>
       <c r="L85" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -5950,19 +5950,19 @@
         <v>205</v>
       </c>
       <c r="D86" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E86" t="s">
+        <v>32</v>
+      </c>
+      <c r="F86" t="s">
         <v>280</v>
       </c>
-      <c r="F86" t="s">
-        <v>16</v>
-      </c>
       <c r="G86" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H86" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I86" t="s">
         <v>16</v>
@@ -5974,7 +5974,7 @@
         <v>281</v>
       </c>
       <c r="L86" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -5988,19 +5988,19 @@
         <v>205</v>
       </c>
       <c r="D87" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E87" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" t="s">
         <v>283</v>
       </c>
-      <c r="F87" t="s">
-        <v>16</v>
-      </c>
       <c r="G87" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H87" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I87" t="s">
         <v>16</v>
@@ -6012,7 +6012,7 @@
         <v>284</v>
       </c>
       <c r="L87" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -6026,19 +6026,19 @@
         <v>205</v>
       </c>
       <c r="D88" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E88" t="s">
+        <v>16</v>
+      </c>
+      <c r="F88" t="s">
         <v>286</v>
       </c>
-      <c r="F88" t="s">
-        <v>16</v>
-      </c>
       <c r="G88" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H88" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="I88" t="s">
         <v>16</v>
@@ -6050,7 +6050,7 @@
         <v>287</v>
       </c>
       <c r="L88" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -6064,19 +6064,19 @@
         <v>205</v>
       </c>
       <c r="D89" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E89" t="s">
+        <v>32</v>
+      </c>
+      <c r="F89" t="s">
         <v>289</v>
       </c>
-      <c r="F89" t="s">
-        <v>16</v>
-      </c>
       <c r="G89" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H89" t="s">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="I89" t="s">
         <v>16</v>
@@ -6088,7 +6088,7 @@
         <v>290</v>
       </c>
       <c r="L89" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -6099,22 +6099,22 @@
         <v>13</v>
       </c>
       <c r="C90" t="s">
+        <v>205</v>
+      </c>
+      <c r="D90" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90" t="s">
+        <v>32</v>
+      </c>
+      <c r="F90" t="s">
         <v>292</v>
       </c>
-      <c r="D90" t="s">
-        <v>206</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="G90" t="s">
+        <v>16</v>
+      </c>
+      <c r="H90" t="s">
         <v>293</v>
-      </c>
-      <c r="F90" t="s">
-        <v>16</v>
-      </c>
-      <c r="G90" t="s">
-        <v>208</v>
-      </c>
-      <c r="H90" t="s">
-        <v>32</v>
       </c>
       <c r="I90" t="s">
         <v>16</v>
@@ -6126,7 +6126,7 @@
         <v>294</v>
       </c>
       <c r="L90" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -6137,22 +6137,22 @@
         <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="D91" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E91" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" t="s">
         <v>296</v>
       </c>
-      <c r="F91" t="s">
-        <v>16</v>
-      </c>
       <c r="G91" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H91" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="I91" t="s">
         <v>16</v>
@@ -6164,7 +6164,7 @@
         <v>297</v>
       </c>
       <c r="L91" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -6175,22 +6175,22 @@
         <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="D92" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E92" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" t="s">
         <v>299</v>
       </c>
-      <c r="F92" t="s">
-        <v>16</v>
-      </c>
       <c r="G92" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H92" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="I92" t="s">
         <v>16</v>
@@ -6202,7 +6202,7 @@
         <v>300</v>
       </c>
       <c r="L92" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -6213,22 +6213,22 @@
         <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="D93" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E93" t="s">
+        <v>16</v>
+      </c>
+      <c r="F93" t="s">
         <v>302</v>
       </c>
-      <c r="F93" t="s">
-        <v>16</v>
-      </c>
       <c r="G93" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H93" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="I93" t="s">
         <v>16</v>
@@ -6240,7 +6240,7 @@
         <v>303</v>
       </c>
       <c r="L93" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -6251,22 +6251,22 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="D94" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E94" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" t="s">
         <v>305</v>
       </c>
-      <c r="F94" t="s">
-        <v>16</v>
-      </c>
       <c r="G94" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H94" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="I94" t="s">
         <v>16</v>
@@ -6278,7 +6278,7 @@
         <v>306</v>
       </c>
       <c r="L94" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -6289,22 +6289,22 @@
         <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="D95" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E95" t="s">
+        <v>16</v>
+      </c>
+      <c r="F95" t="s">
         <v>308</v>
       </c>
-      <c r="F95" t="s">
-        <v>16</v>
-      </c>
       <c r="G95" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H95" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="I95" t="s">
         <v>16</v>
@@ -6316,7 +6316,7 @@
         <v>309</v>
       </c>
       <c r="L95" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -6327,22 +6327,22 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="D96" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E96" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" t="s">
         <v>311</v>
       </c>
-      <c r="F96" t="s">
-        <v>16</v>
-      </c>
       <c r="G96" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H96" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="I96" t="s">
         <v>16</v>
@@ -6354,7 +6354,7 @@
         <v>312</v>
       </c>
       <c r="L96" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -6365,22 +6365,22 @@
         <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="D97" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E97" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97" t="s">
         <v>314</v>
       </c>
-      <c r="F97" t="s">
-        <v>16</v>
-      </c>
       <c r="G97" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H97" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="I97" t="s">
         <v>16</v>
@@ -6392,7 +6392,7 @@
         <v>315</v>
       </c>
       <c r="L97" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -6403,22 +6403,22 @@
         <v>13</v>
       </c>
       <c r="C98" t="s">
+        <v>205</v>
+      </c>
+      <c r="D98" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" t="s">
+        <v>16</v>
+      </c>
+      <c r="F98" t="s">
         <v>317</v>
       </c>
-      <c r="D98" t="s">
-        <v>206</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="G98" t="s">
+        <v>16</v>
+      </c>
+      <c r="H98" t="s">
         <v>318</v>
-      </c>
-      <c r="F98" t="s">
-        <v>16</v>
-      </c>
-      <c r="G98" t="s">
-        <v>208</v>
-      </c>
-      <c r="H98" t="s">
-        <v>16</v>
       </c>
       <c r="I98" t="s">
         <v>16</v>
@@ -6430,7 +6430,7 @@
         <v>319</v>
       </c>
       <c r="L98" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -6441,25 +6441,25 @@
         <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D99" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E99" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99" t="s">
         <v>321</v>
       </c>
-      <c r="F99" t="s">
-        <v>16</v>
-      </c>
       <c r="G99" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="H99" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I99" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J99" t="s">
         <v>18</v>
@@ -6468,7 +6468,7 @@
         <v>322</v>
       </c>
       <c r="L99" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -6479,22 +6479,22 @@
         <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D100" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E100" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" t="s">
         <v>324</v>
       </c>
-      <c r="F100" t="s">
-        <v>16</v>
-      </c>
       <c r="G100" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H100" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I100" t="s">
         <v>16</v>
@@ -6506,7 +6506,7 @@
         <v>325</v>
       </c>
       <c r="L100" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -6517,22 +6517,22 @@
         <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D101" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E101" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" t="s">
         <v>327</v>
       </c>
-      <c r="F101" t="s">
-        <v>16</v>
-      </c>
       <c r="G101" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H101" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I101" t="s">
         <v>16</v>
@@ -6544,7 +6544,7 @@
         <v>328</v>
       </c>
       <c r="L101" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -6555,22 +6555,22 @@
         <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D102" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E102" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" t="s">
         <v>330</v>
       </c>
-      <c r="F102" t="s">
-        <v>16</v>
-      </c>
       <c r="G102" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H102" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I102" t="s">
         <v>16</v>
@@ -6582,7 +6582,7 @@
         <v>331</v>
       </c>
       <c r="L102" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -6593,22 +6593,22 @@
         <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D103" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E103" t="s">
+        <v>16</v>
+      </c>
+      <c r="F103" t="s">
         <v>333</v>
       </c>
-      <c r="F103" t="s">
-        <v>16</v>
-      </c>
       <c r="G103" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H103" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I103" t="s">
         <v>16</v>
@@ -6620,7 +6620,7 @@
         <v>334</v>
       </c>
       <c r="L103" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -6631,22 +6631,22 @@
         <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D104" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E104" t="s">
+        <v>16</v>
+      </c>
+      <c r="F104" t="s">
         <v>336</v>
       </c>
-      <c r="F104" t="s">
-        <v>16</v>
-      </c>
       <c r="G104" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H104" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I104" t="s">
         <v>16</v>
@@ -6658,7 +6658,7 @@
         <v>337</v>
       </c>
       <c r="L104" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -6669,22 +6669,22 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D105" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E105" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105" t="s">
         <v>339</v>
       </c>
-      <c r="F105" t="s">
-        <v>16</v>
-      </c>
       <c r="G105" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H105" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I105" t="s">
         <v>16</v>
@@ -6696,7 +6696,7 @@
         <v>340</v>
       </c>
       <c r="L105" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -6707,22 +6707,22 @@
         <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D106" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E106" t="s">
+        <v>16</v>
+      </c>
+      <c r="F106" t="s">
         <v>342</v>
       </c>
-      <c r="F106" t="s">
-        <v>16</v>
-      </c>
       <c r="G106" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H106" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I106" t="s">
         <v>16</v>
@@ -6734,7 +6734,7 @@
         <v>343</v>
       </c>
       <c r="L106" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -6745,22 +6745,22 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D107" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E107" t="s">
+        <v>32</v>
+      </c>
+      <c r="F107" t="s">
         <v>345</v>
       </c>
-      <c r="F107" t="s">
-        <v>16</v>
-      </c>
       <c r="G107" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H107" t="s">
-        <v>32</v>
+        <v>318</v>
       </c>
       <c r="I107" t="s">
         <v>16</v>
@@ -6772,7 +6772,7 @@
         <v>346</v>
       </c>
       <c r="L107" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -6783,25 +6783,25 @@
         <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D108" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E108" t="s">
+        <v>16</v>
+      </c>
+      <c r="F108" t="s">
         <v>348</v>
       </c>
-      <c r="F108" t="s">
-        <v>16</v>
-      </c>
       <c r="G108" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="H108" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I108" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J108" t="s">
         <v>18</v>
@@ -6810,7 +6810,7 @@
         <v>349</v>
       </c>
       <c r="L108" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -6821,22 +6821,22 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D109" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E109" t="s">
+        <v>16</v>
+      </c>
+      <c r="F109" t="s">
         <v>351</v>
       </c>
-      <c r="F109" t="s">
-        <v>16</v>
-      </c>
       <c r="G109" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H109" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I109" t="s">
         <v>16</v>
@@ -6848,7 +6848,7 @@
         <v>352</v>
       </c>
       <c r="L109" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -6859,22 +6859,22 @@
         <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D110" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E110" t="s">
+        <v>16</v>
+      </c>
+      <c r="F110" t="s">
         <v>354</v>
       </c>
-      <c r="F110" t="s">
-        <v>16</v>
-      </c>
       <c r="G110" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H110" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I110" t="s">
         <v>16</v>
@@ -6886,7 +6886,7 @@
         <v>355</v>
       </c>
       <c r="L110" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -6897,22 +6897,22 @@
         <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D111" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E111" t="s">
+        <v>32</v>
+      </c>
+      <c r="F111" t="s">
         <v>357</v>
       </c>
-      <c r="F111" t="s">
-        <v>16</v>
-      </c>
       <c r="G111" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H111" t="s">
-        <v>32</v>
+        <v>318</v>
       </c>
       <c r="I111" t="s">
         <v>16</v>
@@ -6924,7 +6924,7 @@
         <v>358</v>
       </c>
       <c r="L111" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -6935,22 +6935,22 @@
         <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D112" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E112" t="s">
+        <v>16</v>
+      </c>
+      <c r="F112" t="s">
         <v>360</v>
       </c>
-      <c r="F112" t="s">
-        <v>16</v>
-      </c>
       <c r="G112" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H112" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I112" t="s">
         <v>16</v>
@@ -6962,7 +6962,7 @@
         <v>361</v>
       </c>
       <c r="L112" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -6973,22 +6973,22 @@
         <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>317</v>
+        <v>205</v>
       </c>
       <c r="D113" t="s">
-        <v>206</v>
+        <v>15</v>
       </c>
       <c r="E113" t="s">
+        <v>16</v>
+      </c>
+      <c r="F113" t="s">
         <v>363</v>
       </c>
-      <c r="F113" t="s">
-        <v>16</v>
-      </c>
       <c r="G113" t="s">
-        <v>208</v>
+        <v>16</v>
       </c>
       <c r="H113" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
       <c r="I113" t="s">
         <v>16</v>
@@ -7000,7 +7000,7 @@
         <v>364</v>
       </c>
       <c r="L113" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -7010,19 +7010,19 @@
       <c r="B114" t="s">
         <v>13</v>
       </c>
+      <c r="C114" t="s">
+        <v>366</v>
+      </c>
       <c r="D114" t="s">
-        <v>366</v>
+        <v>15</v>
       </c>
       <c r="E114" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114" t="s">
         <v>367</v>
       </c>
-      <c r="F114" t="s">
-        <v>16</v>
-      </c>
       <c r="G114" t="s">
-        <v>208</v>
-      </c>
-      <c r="H114" t="s">
         <v>16</v>
       </c>
       <c r="I114" t="s">
@@ -7035,7 +7035,7 @@
         <v>369</v>
       </c>
       <c r="L114" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -7045,19 +7045,19 @@
       <c r="B115" t="s">
         <v>13</v>
       </c>
+      <c r="C115" t="s">
+        <v>366</v>
+      </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>15</v>
       </c>
       <c r="E115" t="s">
+        <v>16</v>
+      </c>
+      <c r="F115" t="s">
         <v>371</v>
       </c>
-      <c r="F115" t="s">
-        <v>16</v>
-      </c>
       <c r="G115" t="s">
-        <v>208</v>
-      </c>
-      <c r="H115" t="s">
         <v>16</v>
       </c>
       <c r="I115" t="s">
@@ -7070,7 +7070,7 @@
         <v>372</v>
       </c>
       <c r="L115" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -7080,19 +7080,19 @@
       <c r="B116" t="s">
         <v>13</v>
       </c>
+      <c r="C116" t="s">
+        <v>366</v>
+      </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>15</v>
       </c>
       <c r="E116" t="s">
+        <v>16</v>
+      </c>
+      <c r="F116" t="s">
         <v>374</v>
       </c>
-      <c r="F116" t="s">
-        <v>16</v>
-      </c>
       <c r="G116" t="s">
-        <v>208</v>
-      </c>
-      <c r="H116" t="s">
         <v>16</v>
       </c>
       <c r="I116" t="s">
@@ -7105,7 +7105,7 @@
         <v>375</v>
       </c>
       <c r="L116" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -7115,19 +7115,19 @@
       <c r="B117" t="s">
         <v>13</v>
       </c>
+      <c r="C117" t="s">
+        <v>366</v>
+      </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>15</v>
       </c>
       <c r="E117" t="s">
+        <v>16</v>
+      </c>
+      <c r="F117" t="s">
         <v>377</v>
       </c>
-      <c r="F117" t="s">
-        <v>16</v>
-      </c>
       <c r="G117" t="s">
-        <v>208</v>
-      </c>
-      <c r="H117" t="s">
         <v>16</v>
       </c>
       <c r="I117" t="s">
@@ -7140,7 +7140,7 @@
         <v>378</v>
       </c>
       <c r="L117" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -7150,19 +7150,19 @@
       <c r="B118" t="s">
         <v>13</v>
       </c>
+      <c r="C118" t="s">
+        <v>366</v>
+      </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>15</v>
       </c>
       <c r="E118" t="s">
+        <v>16</v>
+      </c>
+      <c r="F118" t="s">
         <v>380</v>
       </c>
-      <c r="F118" t="s">
-        <v>16</v>
-      </c>
       <c r="G118" t="s">
-        <v>208</v>
-      </c>
-      <c r="H118" t="s">
         <v>16</v>
       </c>
       <c r="I118" t="s">
@@ -7175,7 +7175,7 @@
         <v>381</v>
       </c>
       <c r="L118" t="s">
-        <v>20</v>
+        <v>209</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -7185,13 +7185,16 @@
       <c r="B119" t="s">
         <v>13</v>
       </c>
+      <c r="D119" t="s">
+        <v>15</v>
+      </c>
       <c r="E119" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119" t="s">
         <v>383</v>
       </c>
-      <c r="F119" t="s">
-        <v>16</v>
-      </c>
-      <c r="H119" t="s">
+      <c r="G119" t="s">
         <v>16</v>
       </c>
       <c r="I119" t="s">
@@ -7199,9 +7202,6 @@
       </c>
       <c r="K119" t="s">
         <v>384</v>
-      </c>
-      <c r="L119" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -7211,32 +7211,32 @@
       <c r="B120" t="s">
         <v>13</v>
       </c>
+      <c r="C120" t="s">
+        <v>386</v>
+      </c>
       <c r="D120" t="s">
-        <v>386</v>
+        <v>15</v>
       </c>
       <c r="E120" t="s">
+        <v>16</v>
+      </c>
+      <c r="F120" t="s">
         <v>387</v>
       </c>
-      <c r="F120" t="s">
-        <v>16</v>
-      </c>
       <c r="G120" t="s">
+        <v>32</v>
+      </c>
+      <c r="I120" t="s">
+        <v>16</v>
+      </c>
+      <c r="J120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120" t="s">
         <v>388</v>
       </c>
-      <c r="H120" t="s">
-        <v>16</v>
-      </c>
-      <c r="I120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J120" t="s">
-        <v>18</v>
-      </c>
-      <c r="K120" t="s">
+      <c r="L120" t="s">
         <v>389</v>
-      </c>
-      <c r="L120" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -7246,23 +7246,23 @@
       <c r="B121" t="s">
         <v>13</v>
       </c>
+      <c r="C121" t="s">
+        <v>386</v>
+      </c>
       <c r="D121" t="s">
-        <v>386</v>
+        <v>15</v>
       </c>
       <c r="E121" t="s">
+        <v>16</v>
+      </c>
+      <c r="F121" t="s">
         <v>391</v>
       </c>
-      <c r="F121" t="s">
-        <v>16</v>
-      </c>
       <c r="G121" t="s">
-        <v>388</v>
-      </c>
-      <c r="H121" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I121" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J121" t="s">
         <v>18</v>
@@ -7271,7 +7271,7 @@
         <v>392</v>
       </c>
       <c r="L121" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -7281,23 +7281,23 @@
       <c r="B122" t="s">
         <v>13</v>
       </c>
+      <c r="C122" t="s">
+        <v>386</v>
+      </c>
       <c r="D122" t="s">
-        <v>386</v>
+        <v>15</v>
       </c>
       <c r="E122" t="s">
+        <v>16</v>
+      </c>
+      <c r="F122" t="s">
         <v>394</v>
       </c>
-      <c r="F122" t="s">
-        <v>16</v>
-      </c>
       <c r="G122" t="s">
-        <v>388</v>
-      </c>
-      <c r="H122" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I122" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J122" t="s">
         <v>18</v>
@@ -7306,7 +7306,7 @@
         <v>395</v>
       </c>
       <c r="L122" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -7316,23 +7316,23 @@
       <c r="B123" t="s">
         <v>13</v>
       </c>
+      <c r="C123" t="s">
+        <v>386</v>
+      </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>15</v>
       </c>
       <c r="E123" t="s">
+        <v>16</v>
+      </c>
+      <c r="F123" t="s">
         <v>397</v>
       </c>
-      <c r="F123" t="s">
-        <v>16</v>
-      </c>
       <c r="G123" t="s">
-        <v>388</v>
-      </c>
-      <c r="H123" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I123" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J123" t="s">
         <v>18</v>
@@ -7341,7 +7341,7 @@
         <v>398</v>
       </c>
       <c r="L123" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -7351,23 +7351,23 @@
       <c r="B124" t="s">
         <v>13</v>
       </c>
+      <c r="C124" t="s">
+        <v>386</v>
+      </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>15</v>
       </c>
       <c r="E124" t="s">
+        <v>16</v>
+      </c>
+      <c r="F124" t="s">
         <v>400</v>
       </c>
-      <c r="F124" t="s">
-        <v>16</v>
-      </c>
       <c r="G124" t="s">
-        <v>388</v>
-      </c>
-      <c r="H124" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I124" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J124" t="s">
         <v>18</v>
@@ -7376,7 +7376,7 @@
         <v>401</v>
       </c>
       <c r="L124" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -7386,19 +7386,19 @@
       <c r="B125" t="s">
         <v>13</v>
       </c>
+      <c r="C125" t="s">
+        <v>403</v>
+      </c>
       <c r="D125" t="s">
-        <v>403</v>
+        <v>15</v>
       </c>
       <c r="E125" t="s">
+        <v>16</v>
+      </c>
+      <c r="F125" t="s">
         <v>404</v>
       </c>
-      <c r="F125" t="s">
-        <v>16</v>
-      </c>
       <c r="G125" t="s">
-        <v>388</v>
-      </c>
-      <c r="H125" t="s">
         <v>16</v>
       </c>
       <c r="I125" t="s">
@@ -7411,7 +7411,7 @@
         <v>405</v>
       </c>
       <c r="L125" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -7421,19 +7421,19 @@
       <c r="B126" t="s">
         <v>13</v>
       </c>
+      <c r="C126" t="s">
+        <v>403</v>
+      </c>
       <c r="D126" t="s">
-        <v>403</v>
+        <v>15</v>
       </c>
       <c r="E126" t="s">
+        <v>16</v>
+      </c>
+      <c r="F126" t="s">
         <v>407</v>
       </c>
-      <c r="F126" t="s">
-        <v>16</v>
-      </c>
       <c r="G126" t="s">
-        <v>388</v>
-      </c>
-      <c r="H126" t="s">
         <v>16</v>
       </c>
       <c r="I126" t="s">
@@ -7446,7 +7446,7 @@
         <v>408</v>
       </c>
       <c r="L126" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -7456,19 +7456,19 @@
       <c r="B127" t="s">
         <v>13</v>
       </c>
+      <c r="C127" t="s">
+        <v>403</v>
+      </c>
       <c r="D127" t="s">
-        <v>403</v>
+        <v>15</v>
       </c>
       <c r="E127" t="s">
+        <v>16</v>
+      </c>
+      <c r="F127" t="s">
         <v>410</v>
       </c>
-      <c r="F127" t="s">
-        <v>16</v>
-      </c>
       <c r="G127" t="s">
-        <v>388</v>
-      </c>
-      <c r="H127" t="s">
         <v>16</v>
       </c>
       <c r="I127" t="s">
@@ -7481,7 +7481,7 @@
         <v>411</v>
       </c>
       <c r="L127" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -7491,19 +7491,19 @@
       <c r="B128" t="s">
         <v>13</v>
       </c>
+      <c r="C128" t="s">
+        <v>403</v>
+      </c>
       <c r="D128" t="s">
-        <v>403</v>
+        <v>15</v>
       </c>
       <c r="E128" t="s">
+        <v>16</v>
+      </c>
+      <c r="F128" t="s">
         <v>413</v>
       </c>
-      <c r="F128" t="s">
-        <v>16</v>
-      </c>
       <c r="G128" t="s">
-        <v>388</v>
-      </c>
-      <c r="H128" t="s">
         <v>16</v>
       </c>
       <c r="I128" t="s">
@@ -7516,7 +7516,7 @@
         <v>414</v>
       </c>
       <c r="L128" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -7526,19 +7526,19 @@
       <c r="B129" t="s">
         <v>13</v>
       </c>
+      <c r="C129" t="s">
+        <v>403</v>
+      </c>
       <c r="D129" t="s">
-        <v>403</v>
+        <v>15</v>
       </c>
       <c r="E129" t="s">
+        <v>16</v>
+      </c>
+      <c r="F129" t="s">
         <v>416</v>
       </c>
-      <c r="F129" t="s">
-        <v>16</v>
-      </c>
       <c r="G129" t="s">
-        <v>388</v>
-      </c>
-      <c r="H129" t="s">
         <v>16</v>
       </c>
       <c r="I129" t="s">
@@ -7551,7 +7551,7 @@
         <v>417</v>
       </c>
       <c r="L129" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -7561,23 +7561,23 @@
       <c r="B130" t="s">
         <v>13</v>
       </c>
+      <c r="C130" t="s">
+        <v>403</v>
+      </c>
       <c r="D130" t="s">
-        <v>403</v>
+        <v>15</v>
       </c>
       <c r="E130" t="s">
+        <v>16</v>
+      </c>
+      <c r="F130" t="s">
         <v>419</v>
       </c>
-      <c r="F130" t="s">
-        <v>16</v>
-      </c>
       <c r="G130" t="s">
-        <v>388</v>
-      </c>
-      <c r="H130" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I130" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J130" t="s">
         <v>18</v>
@@ -7586,7 +7586,7 @@
         <v>420</v>
       </c>
       <c r="L130" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -7596,19 +7596,19 @@
       <c r="B131" t="s">
         <v>13</v>
       </c>
+      <c r="C131" t="s">
+        <v>403</v>
+      </c>
       <c r="D131" t="s">
-        <v>403</v>
+        <v>15</v>
       </c>
       <c r="E131" t="s">
+        <v>16</v>
+      </c>
+      <c r="F131" t="s">
         <v>422</v>
       </c>
-      <c r="F131" t="s">
-        <v>16</v>
-      </c>
       <c r="G131" t="s">
-        <v>388</v>
-      </c>
-      <c r="H131" t="s">
         <v>16</v>
       </c>
       <c r="I131" t="s">
@@ -7621,7 +7621,7 @@
         <v>423</v>
       </c>
       <c r="L131" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -7631,19 +7631,19 @@
       <c r="B132" t="s">
         <v>13</v>
       </c>
+      <c r="C132" t="s">
+        <v>425</v>
+      </c>
       <c r="D132" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E132" t="s">
+        <v>16</v>
+      </c>
+      <c r="F132" t="s">
         <v>426</v>
       </c>
-      <c r="F132" t="s">
-        <v>16</v>
-      </c>
       <c r="G132" t="s">
-        <v>388</v>
-      </c>
-      <c r="H132" t="s">
         <v>16</v>
       </c>
       <c r="I132" t="s">
@@ -7656,7 +7656,7 @@
         <v>427</v>
       </c>
       <c r="L132" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -7666,23 +7666,23 @@
       <c r="B133" t="s">
         <v>13</v>
       </c>
+      <c r="C133" t="s">
+        <v>425</v>
+      </c>
       <c r="D133" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E133" t="s">
+        <v>16</v>
+      </c>
+      <c r="F133" t="s">
         <v>429</v>
       </c>
-      <c r="F133" t="s">
-        <v>32</v>
-      </c>
       <c r="G133" t="s">
-        <v>388</v>
-      </c>
-      <c r="H133" t="s">
         <v>16</v>
       </c>
       <c r="I133" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J133" t="s">
         <v>18</v>
@@ -7691,7 +7691,7 @@
         <v>430</v>
       </c>
       <c r="L133" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -7701,19 +7701,19 @@
       <c r="B134" t="s">
         <v>13</v>
       </c>
+      <c r="C134" t="s">
+        <v>425</v>
+      </c>
       <c r="D134" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E134" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134" t="s">
         <v>432</v>
       </c>
-      <c r="F134" t="s">
-        <v>16</v>
-      </c>
       <c r="G134" t="s">
-        <v>388</v>
-      </c>
-      <c r="H134" t="s">
         <v>16</v>
       </c>
       <c r="I134" t="s">
@@ -7726,7 +7726,7 @@
         <v>433</v>
       </c>
       <c r="L134" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -7736,20 +7736,20 @@
       <c r="B135" t="s">
         <v>13</v>
       </c>
+      <c r="C135" t="s">
+        <v>425</v>
+      </c>
       <c r="D135" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E135" t="s">
+        <v>16</v>
+      </c>
+      <c r="F135" t="s">
         <v>435</v>
       </c>
-      <c r="F135" t="s">
-        <v>32</v>
-      </c>
       <c r="G135" t="s">
-        <v>388</v>
-      </c>
-      <c r="H135" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I135" t="s">
         <v>32</v>
@@ -7761,7 +7761,7 @@
         <v>436</v>
       </c>
       <c r="L135" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -7771,19 +7771,19 @@
       <c r="B136" t="s">
         <v>13</v>
       </c>
+      <c r="C136" t="s">
+        <v>425</v>
+      </c>
       <c r="D136" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E136" t="s">
+        <v>16</v>
+      </c>
+      <c r="F136" t="s">
         <v>438</v>
       </c>
-      <c r="F136" t="s">
-        <v>16</v>
-      </c>
       <c r="G136" t="s">
-        <v>388</v>
-      </c>
-      <c r="H136" t="s">
         <v>16</v>
       </c>
       <c r="I136" t="s">
@@ -7796,7 +7796,7 @@
         <v>439</v>
       </c>
       <c r="L136" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -7806,23 +7806,23 @@
       <c r="B137" t="s">
         <v>13</v>
       </c>
+      <c r="C137" t="s">
+        <v>425</v>
+      </c>
       <c r="D137" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E137" t="s">
+        <v>16</v>
+      </c>
+      <c r="F137" t="s">
         <v>441</v>
       </c>
-      <c r="F137" t="s">
-        <v>32</v>
-      </c>
       <c r="G137" t="s">
-        <v>388</v>
-      </c>
-      <c r="H137" t="s">
         <v>16</v>
       </c>
       <c r="I137" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J137" t="s">
         <v>18</v>
@@ -7831,7 +7831,7 @@
         <v>442</v>
       </c>
       <c r="L137" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -7841,19 +7841,19 @@
       <c r="B138" t="s">
         <v>13</v>
       </c>
+      <c r="C138" t="s">
+        <v>425</v>
+      </c>
       <c r="D138" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E138" t="s">
+        <v>16</v>
+      </c>
+      <c r="F138" t="s">
         <v>444</v>
       </c>
-      <c r="F138" t="s">
-        <v>16</v>
-      </c>
       <c r="G138" t="s">
-        <v>388</v>
-      </c>
-      <c r="H138" t="s">
         <v>16</v>
       </c>
       <c r="I138" t="s">
@@ -7866,7 +7866,7 @@
         <v>445</v>
       </c>
       <c r="L138" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:12">
@@ -7876,20 +7876,20 @@
       <c r="B139" t="s">
         <v>13</v>
       </c>
+      <c r="C139" t="s">
+        <v>425</v>
+      </c>
       <c r="D139" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E139" t="s">
+        <v>32</v>
+      </c>
+      <c r="F139" t="s">
         <v>447</v>
       </c>
-      <c r="F139" t="s">
-        <v>16</v>
-      </c>
       <c r="G139" t="s">
-        <v>388</v>
-      </c>
-      <c r="H139" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I139" t="s">
         <v>16</v>
@@ -7901,7 +7901,7 @@
         <v>448</v>
       </c>
       <c r="L139" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -7911,19 +7911,19 @@
       <c r="B140" t="s">
         <v>13</v>
       </c>
+      <c r="C140" t="s">
+        <v>425</v>
+      </c>
       <c r="D140" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E140" t="s">
+        <v>16</v>
+      </c>
+      <c r="F140" t="s">
         <v>450</v>
       </c>
-      <c r="F140" t="s">
-        <v>16</v>
-      </c>
       <c r="G140" t="s">
-        <v>388</v>
-      </c>
-      <c r="H140" t="s">
         <v>16</v>
       </c>
       <c r="I140" t="s">
@@ -7936,7 +7936,7 @@
         <v>451</v>
       </c>
       <c r="L140" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:12">
@@ -7946,23 +7946,23 @@
       <c r="B141" t="s">
         <v>13</v>
       </c>
+      <c r="C141" t="s">
+        <v>425</v>
+      </c>
       <c r="D141" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E141" t="s">
+        <v>32</v>
+      </c>
+      <c r="F141" t="s">
         <v>453</v>
       </c>
-      <c r="F141" t="s">
-        <v>32</v>
-      </c>
       <c r="G141" t="s">
-        <v>388</v>
-      </c>
-      <c r="H141" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I141" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J141" t="s">
         <v>18</v>
@@ -7971,7 +7971,7 @@
         <v>454</v>
       </c>
       <c r="L141" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -7981,19 +7981,19 @@
       <c r="B142" t="s">
         <v>13</v>
       </c>
+      <c r="C142" t="s">
+        <v>425</v>
+      </c>
       <c r="D142" t="s">
-        <v>425</v>
+        <v>15</v>
       </c>
       <c r="E142" t="s">
+        <v>16</v>
+      </c>
+      <c r="F142" t="s">
         <v>456</v>
       </c>
-      <c r="F142" t="s">
-        <v>16</v>
-      </c>
       <c r="G142" t="s">
-        <v>388</v>
-      </c>
-      <c r="H142" t="s">
         <v>16</v>
       </c>
       <c r="I142" t="s">
@@ -8006,7 +8006,7 @@
         <v>457</v>
       </c>
       <c r="L142" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:12">
@@ -8016,20 +8016,20 @@
       <c r="B143" t="s">
         <v>13</v>
       </c>
+      <c r="C143" t="s">
+        <v>459</v>
+      </c>
       <c r="D143" t="s">
-        <v>459</v>
+        <v>15</v>
       </c>
       <c r="E143" t="s">
+        <v>16</v>
+      </c>
+      <c r="F143" t="s">
         <v>460</v>
       </c>
-      <c r="F143" t="s">
-        <v>32</v>
-      </c>
       <c r="G143" t="s">
-        <v>388</v>
-      </c>
-      <c r="H143" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I143" t="s">
         <v>32</v>
@@ -8041,7 +8041,7 @@
         <v>461</v>
       </c>
       <c r="L143" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -8051,23 +8051,23 @@
       <c r="B144" t="s">
         <v>13</v>
       </c>
+      <c r="C144" t="s">
+        <v>459</v>
+      </c>
       <c r="D144" t="s">
-        <v>459</v>
+        <v>15</v>
       </c>
       <c r="E144" t="s">
+        <v>16</v>
+      </c>
+      <c r="F144" t="s">
         <v>463</v>
       </c>
-      <c r="F144" t="s">
-        <v>32</v>
-      </c>
       <c r="G144" t="s">
-        <v>388</v>
-      </c>
-      <c r="H144" t="s">
         <v>16</v>
       </c>
       <c r="I144" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J144" t="s">
         <v>18</v>
@@ -8076,7 +8076,7 @@
         <v>464</v>
       </c>
       <c r="L144" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -8086,20 +8086,20 @@
       <c r="B145" t="s">
         <v>13</v>
       </c>
+      <c r="C145" t="s">
+        <v>459</v>
+      </c>
       <c r="D145" t="s">
-        <v>459</v>
+        <v>15</v>
       </c>
       <c r="E145" t="s">
+        <v>16</v>
+      </c>
+      <c r="F145" t="s">
         <v>466</v>
       </c>
-      <c r="F145" t="s">
-        <v>32</v>
-      </c>
       <c r="G145" t="s">
-        <v>388</v>
-      </c>
-      <c r="H145" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I145" t="s">
         <v>32</v>
@@ -8111,7 +8111,7 @@
         <v>467</v>
       </c>
       <c r="L145" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="146" spans="1:12">
@@ -8121,19 +8121,19 @@
       <c r="B146" t="s">
         <v>13</v>
       </c>
+      <c r="C146" t="s">
+        <v>459</v>
+      </c>
       <c r="D146" t="s">
-        <v>459</v>
+        <v>15</v>
       </c>
       <c r="E146" t="s">
+        <v>16</v>
+      </c>
+      <c r="F146" t="s">
         <v>469</v>
       </c>
-      <c r="F146" t="s">
-        <v>16</v>
-      </c>
       <c r="G146" t="s">
-        <v>388</v>
-      </c>
-      <c r="H146" t="s">
         <v>16</v>
       </c>
       <c r="I146" t="s">
@@ -8146,7 +8146,7 @@
         <v>470</v>
       </c>
       <c r="L146" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="147" spans="1:12">
@@ -8156,19 +8156,19 @@
       <c r="B147" t="s">
         <v>13</v>
       </c>
+      <c r="C147" t="s">
+        <v>459</v>
+      </c>
       <c r="D147" t="s">
-        <v>459</v>
+        <v>15</v>
       </c>
       <c r="E147" t="s">
+        <v>16</v>
+      </c>
+      <c r="F147" t="s">
         <v>472</v>
       </c>
-      <c r="F147" t="s">
-        <v>16</v>
-      </c>
       <c r="G147" t="s">
-        <v>388</v>
-      </c>
-      <c r="H147" t="s">
         <v>16</v>
       </c>
       <c r="I147" t="s">
@@ -8181,7 +8181,7 @@
         <v>473</v>
       </c>
       <c r="L147" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="148" spans="1:12">
@@ -8191,20 +8191,20 @@
       <c r="B148" t="s">
         <v>13</v>
       </c>
+      <c r="C148" t="s">
+        <v>459</v>
+      </c>
       <c r="D148" t="s">
-        <v>459</v>
+        <v>15</v>
       </c>
       <c r="E148" t="s">
+        <v>32</v>
+      </c>
+      <c r="F148" t="s">
         <v>475</v>
       </c>
-      <c r="F148" t="s">
-        <v>16</v>
-      </c>
       <c r="G148" t="s">
-        <v>388</v>
-      </c>
-      <c r="H148" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I148" t="s">
         <v>16</v>
@@ -8216,7 +8216,7 @@
         <v>476</v>
       </c>
       <c r="L148" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -8226,20 +8226,20 @@
       <c r="B149" t="s">
         <v>13</v>
       </c>
+      <c r="C149" t="s">
+        <v>459</v>
+      </c>
       <c r="D149" t="s">
-        <v>459</v>
+        <v>15</v>
       </c>
       <c r="E149" t="s">
+        <v>16</v>
+      </c>
+      <c r="F149" t="s">
         <v>478</v>
       </c>
-      <c r="F149" t="s">
-        <v>32</v>
-      </c>
       <c r="G149" t="s">
-        <v>388</v>
-      </c>
-      <c r="H149" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I149" t="s">
         <v>32</v>
@@ -8251,7 +8251,7 @@
         <v>479</v>
       </c>
       <c r="L149" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -8261,19 +8261,19 @@
       <c r="B150" t="s">
         <v>13</v>
       </c>
+      <c r="C150" t="s">
+        <v>459</v>
+      </c>
       <c r="D150" t="s">
-        <v>459</v>
+        <v>15</v>
       </c>
       <c r="E150" t="s">
+        <v>16</v>
+      </c>
+      <c r="F150" t="s">
         <v>481</v>
       </c>
-      <c r="F150" t="s">
-        <v>16</v>
-      </c>
       <c r="G150" t="s">
-        <v>388</v>
-      </c>
-      <c r="H150" t="s">
         <v>16</v>
       </c>
       <c r="I150" t="s">
@@ -8286,7 +8286,7 @@
         <v>482</v>
       </c>
       <c r="L150" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="151" spans="1:12">
@@ -8296,19 +8296,19 @@
       <c r="B151" t="s">
         <v>13</v>
       </c>
+      <c r="C151" t="s">
+        <v>459</v>
+      </c>
       <c r="D151" t="s">
-        <v>459</v>
+        <v>15</v>
       </c>
       <c r="E151" t="s">
+        <v>16</v>
+      </c>
+      <c r="F151" t="s">
         <v>484</v>
       </c>
-      <c r="F151" t="s">
-        <v>16</v>
-      </c>
       <c r="G151" t="s">
-        <v>388</v>
-      </c>
-      <c r="H151" t="s">
         <v>16</v>
       </c>
       <c r="I151" t="s">
@@ -8321,7 +8321,7 @@
         <v>485</v>
       </c>
       <c r="L151" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -8331,23 +8331,23 @@
       <c r="B152" t="s">
         <v>13</v>
       </c>
+      <c r="C152" t="s">
+        <v>487</v>
+      </c>
       <c r="D152" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E152" t="s">
+        <v>16</v>
+      </c>
+      <c r="F152" t="s">
         <v>488</v>
       </c>
-      <c r="F152" t="s">
-        <v>16</v>
-      </c>
       <c r="G152" t="s">
-        <v>388</v>
-      </c>
-      <c r="H152" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I152" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J152" t="s">
         <v>18</v>
@@ -8356,7 +8356,7 @@
         <v>489</v>
       </c>
       <c r="L152" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="153" spans="1:12">
@@ -8366,23 +8366,23 @@
       <c r="B153" t="s">
         <v>13</v>
       </c>
+      <c r="C153" t="s">
+        <v>487</v>
+      </c>
       <c r="D153" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E153" t="s">
+        <v>16</v>
+      </c>
+      <c r="F153" t="s">
         <v>491</v>
       </c>
-      <c r="F153" t="s">
-        <v>16</v>
-      </c>
       <c r="G153" t="s">
-        <v>388</v>
-      </c>
-      <c r="H153" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I153" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J153" t="s">
         <v>18</v>
@@ -8391,7 +8391,7 @@
         <v>492</v>
       </c>
       <c r="L153" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -8401,19 +8401,19 @@
       <c r="B154" t="s">
         <v>13</v>
       </c>
+      <c r="C154" t="s">
+        <v>487</v>
+      </c>
       <c r="D154" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E154" t="s">
+        <v>16</v>
+      </c>
+      <c r="F154" t="s">
         <v>494</v>
       </c>
-      <c r="F154" t="s">
-        <v>16</v>
-      </c>
       <c r="G154" t="s">
-        <v>388</v>
-      </c>
-      <c r="H154" t="s">
         <v>16</v>
       </c>
       <c r="I154" t="s">
@@ -8426,7 +8426,7 @@
         <v>495</v>
       </c>
       <c r="L154" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="155" spans="1:12">
@@ -8436,19 +8436,19 @@
       <c r="B155" t="s">
         <v>13</v>
       </c>
+      <c r="C155" t="s">
+        <v>487</v>
+      </c>
       <c r="D155" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E155" t="s">
+        <v>16</v>
+      </c>
+      <c r="F155" t="s">
         <v>497</v>
       </c>
-      <c r="F155" t="s">
-        <v>16</v>
-      </c>
       <c r="G155" t="s">
-        <v>388</v>
-      </c>
-      <c r="H155" t="s">
         <v>16</v>
       </c>
       <c r="I155" t="s">
@@ -8461,7 +8461,7 @@
         <v>498</v>
       </c>
       <c r="L155" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -8471,19 +8471,19 @@
       <c r="B156" t="s">
         <v>13</v>
       </c>
+      <c r="C156" t="s">
+        <v>487</v>
+      </c>
       <c r="D156" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E156" t="s">
+        <v>16</v>
+      </c>
+      <c r="F156" t="s">
         <v>500</v>
       </c>
-      <c r="F156" t="s">
-        <v>16</v>
-      </c>
       <c r="G156" t="s">
-        <v>388</v>
-      </c>
-      <c r="H156" t="s">
         <v>16</v>
       </c>
       <c r="I156" t="s">
@@ -8496,7 +8496,7 @@
         <v>501</v>
       </c>
       <c r="L156" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="157" spans="1:12">
@@ -8506,19 +8506,19 @@
       <c r="B157" t="s">
         <v>13</v>
       </c>
+      <c r="C157" t="s">
+        <v>487</v>
+      </c>
       <c r="D157" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E157" t="s">
+        <v>16</v>
+      </c>
+      <c r="F157" t="s">
         <v>503</v>
       </c>
-      <c r="F157" t="s">
-        <v>16</v>
-      </c>
       <c r="G157" t="s">
-        <v>388</v>
-      </c>
-      <c r="H157" t="s">
         <v>16</v>
       </c>
       <c r="I157" t="s">
@@ -8531,7 +8531,7 @@
         <v>504</v>
       </c>
       <c r="L157" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="158" spans="1:12">
@@ -8541,19 +8541,19 @@
       <c r="B158" t="s">
         <v>13</v>
       </c>
+      <c r="C158" t="s">
+        <v>487</v>
+      </c>
       <c r="D158" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E158" t="s">
+        <v>16</v>
+      </c>
+      <c r="F158" t="s">
         <v>506</v>
       </c>
-      <c r="F158" t="s">
-        <v>16</v>
-      </c>
       <c r="G158" t="s">
-        <v>388</v>
-      </c>
-      <c r="H158" t="s">
         <v>16</v>
       </c>
       <c r="I158" t="s">
@@ -8566,7 +8566,7 @@
         <v>507</v>
       </c>
       <c r="L158" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="159" spans="1:12">
@@ -8576,19 +8576,19 @@
       <c r="B159" t="s">
         <v>13</v>
       </c>
+      <c r="C159" t="s">
+        <v>487</v>
+      </c>
       <c r="D159" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E159" t="s">
+        <v>16</v>
+      </c>
+      <c r="F159" t="s">
         <v>509</v>
       </c>
-      <c r="F159" t="s">
-        <v>16</v>
-      </c>
       <c r="G159" t="s">
-        <v>388</v>
-      </c>
-      <c r="H159" t="s">
         <v>16</v>
       </c>
       <c r="I159" t="s">
@@ -8601,7 +8601,7 @@
         <v>510</v>
       </c>
       <c r="L159" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -8611,19 +8611,19 @@
       <c r="B160" t="s">
         <v>13</v>
       </c>
+      <c r="C160" t="s">
+        <v>487</v>
+      </c>
       <c r="D160" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E160" t="s">
+        <v>16</v>
+      </c>
+      <c r="F160" t="s">
         <v>512</v>
       </c>
-      <c r="F160" t="s">
-        <v>16</v>
-      </c>
       <c r="G160" t="s">
-        <v>388</v>
-      </c>
-      <c r="H160" t="s">
         <v>16</v>
       </c>
       <c r="I160" t="s">
@@ -8636,7 +8636,7 @@
         <v>513</v>
       </c>
       <c r="L160" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="161" spans="1:12">
@@ -8646,19 +8646,19 @@
       <c r="B161" t="s">
         <v>13</v>
       </c>
+      <c r="C161" t="s">
+        <v>487</v>
+      </c>
       <c r="D161" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E161" t="s">
+        <v>16</v>
+      </c>
+      <c r="F161" t="s">
         <v>515</v>
       </c>
-      <c r="F161" t="s">
-        <v>16</v>
-      </c>
       <c r="G161" t="s">
-        <v>388</v>
-      </c>
-      <c r="H161" t="s">
         <v>16</v>
       </c>
       <c r="I161" t="s">
@@ -8671,7 +8671,7 @@
         <v>516</v>
       </c>
       <c r="L161" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -8681,19 +8681,19 @@
       <c r="B162" t="s">
         <v>13</v>
       </c>
+      <c r="C162" t="s">
+        <v>487</v>
+      </c>
       <c r="D162" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E162" t="s">
+        <v>16</v>
+      </c>
+      <c r="F162" t="s">
         <v>518</v>
       </c>
-      <c r="F162" t="s">
-        <v>16</v>
-      </c>
       <c r="G162" t="s">
-        <v>388</v>
-      </c>
-      <c r="H162" t="s">
         <v>16</v>
       </c>
       <c r="I162" t="s">
@@ -8706,7 +8706,7 @@
         <v>519</v>
       </c>
       <c r="L162" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -8716,19 +8716,19 @@
       <c r="B163" t="s">
         <v>13</v>
       </c>
+      <c r="C163" t="s">
+        <v>487</v>
+      </c>
       <c r="D163" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E163" t="s">
+        <v>16</v>
+      </c>
+      <c r="F163" t="s">
         <v>521</v>
       </c>
-      <c r="F163" t="s">
-        <v>16</v>
-      </c>
       <c r="G163" t="s">
-        <v>388</v>
-      </c>
-      <c r="H163" t="s">
         <v>16</v>
       </c>
       <c r="I163" t="s">
@@ -8741,7 +8741,7 @@
         <v>522</v>
       </c>
       <c r="L163" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -8751,19 +8751,19 @@
       <c r="B164" t="s">
         <v>13</v>
       </c>
+      <c r="C164" t="s">
+        <v>487</v>
+      </c>
       <c r="D164" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E164" t="s">
+        <v>16</v>
+      </c>
+      <c r="F164" t="s">
         <v>524</v>
       </c>
-      <c r="F164" t="s">
-        <v>16</v>
-      </c>
       <c r="G164" t="s">
-        <v>388</v>
-      </c>
-      <c r="H164" t="s">
         <v>16</v>
       </c>
       <c r="I164" t="s">
@@ -8776,7 +8776,7 @@
         <v>525</v>
       </c>
       <c r="L164" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -8786,19 +8786,19 @@
       <c r="B165" t="s">
         <v>13</v>
       </c>
+      <c r="C165" t="s">
+        <v>487</v>
+      </c>
       <c r="D165" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E165" t="s">
+        <v>16</v>
+      </c>
+      <c r="F165" t="s">
         <v>527</v>
       </c>
-      <c r="F165" t="s">
-        <v>16</v>
-      </c>
       <c r="G165" t="s">
-        <v>388</v>
-      </c>
-      <c r="H165" t="s">
         <v>16</v>
       </c>
       <c r="I165" t="s">
@@ -8811,7 +8811,7 @@
         <v>528</v>
       </c>
       <c r="L165" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -8821,19 +8821,19 @@
       <c r="B166" t="s">
         <v>13</v>
       </c>
+      <c r="C166" t="s">
+        <v>487</v>
+      </c>
       <c r="D166" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E166" t="s">
+        <v>16</v>
+      </c>
+      <c r="F166" t="s">
         <v>530</v>
       </c>
-      <c r="F166" t="s">
-        <v>16</v>
-      </c>
       <c r="G166" t="s">
-        <v>388</v>
-      </c>
-      <c r="H166" t="s">
         <v>16</v>
       </c>
       <c r="I166" t="s">
@@ -8846,7 +8846,7 @@
         <v>531</v>
       </c>
       <c r="L166" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="167" spans="1:12">
@@ -8856,19 +8856,19 @@
       <c r="B167" t="s">
         <v>13</v>
       </c>
+      <c r="C167" t="s">
+        <v>487</v>
+      </c>
       <c r="D167" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E167" t="s">
+        <v>16</v>
+      </c>
+      <c r="F167" t="s">
         <v>533</v>
       </c>
-      <c r="F167" t="s">
-        <v>16</v>
-      </c>
       <c r="G167" t="s">
-        <v>388</v>
-      </c>
-      <c r="H167" t="s">
         <v>16</v>
       </c>
       <c r="I167" t="s">
@@ -8881,7 +8881,7 @@
         <v>534</v>
       </c>
       <c r="L167" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="168" spans="1:12">
@@ -8891,19 +8891,19 @@
       <c r="B168" t="s">
         <v>13</v>
       </c>
+      <c r="C168" t="s">
+        <v>487</v>
+      </c>
       <c r="D168" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E168" t="s">
+        <v>16</v>
+      </c>
+      <c r="F168" t="s">
         <v>536</v>
       </c>
-      <c r="F168" t="s">
-        <v>16</v>
-      </c>
       <c r="G168" t="s">
-        <v>388</v>
-      </c>
-      <c r="H168" t="s">
         <v>16</v>
       </c>
       <c r="I168" t="s">
@@ -8916,7 +8916,7 @@
         <v>537</v>
       </c>
       <c r="L168" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -8926,23 +8926,23 @@
       <c r="B169" t="s">
         <v>13</v>
       </c>
+      <c r="C169" t="s">
+        <v>487</v>
+      </c>
       <c r="D169" t="s">
-        <v>487</v>
+        <v>15</v>
       </c>
       <c r="E169" t="s">
+        <v>16</v>
+      </c>
+      <c r="F169" t="s">
         <v>539</v>
       </c>
-      <c r="F169" t="s">
-        <v>32</v>
-      </c>
       <c r="G169" t="s">
-        <v>388</v>
-      </c>
-      <c r="H169" t="s">
         <v>16</v>
       </c>
       <c r="I169" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J169" t="s">
         <v>18</v>
@@ -8951,7 +8951,7 @@
         <v>540</v>
       </c>
       <c r="L169" t="s">
-        <v>20</v>
+        <v>389</v>
       </c>
     </row>
     <row r="170" spans="1:12">
@@ -8961,19 +8961,19 @@
       <c r="B170" t="s">
         <v>13</v>
       </c>
+      <c r="C170" t="s">
+        <v>542</v>
+      </c>
       <c r="D170" t="s">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="E170" t="s">
+        <v>16</v>
+      </c>
+      <c r="F170" t="s">
         <v>543</v>
       </c>
-      <c r="F170" t="s">
-        <v>16</v>
-      </c>
       <c r="G170" t="s">
-        <v>544</v>
-      </c>
-      <c r="H170" t="s">
         <v>16</v>
       </c>
       <c r="I170" t="s">
@@ -8983,10 +8983,10 @@
         <v>368</v>
       </c>
       <c r="K170" t="s">
+        <v>544</v>
+      </c>
+      <c r="L170" t="s">
         <v>545</v>
-      </c>
-      <c r="L170" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:12">
@@ -8996,19 +8996,19 @@
       <c r="B171" t="s">
         <v>13</v>
       </c>
+      <c r="C171" t="s">
+        <v>542</v>
+      </c>
       <c r="D171" t="s">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="E171" t="s">
+        <v>16</v>
+      </c>
+      <c r="F171" t="s">
         <v>547</v>
       </c>
-      <c r="F171" t="s">
-        <v>16</v>
-      </c>
       <c r="G171" t="s">
-        <v>544</v>
-      </c>
-      <c r="H171" t="s">
         <v>16</v>
       </c>
       <c r="I171" t="s">
@@ -9021,7 +9021,7 @@
         <v>548</v>
       </c>
       <c r="L171" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -9031,19 +9031,19 @@
       <c r="B172" t="s">
         <v>13</v>
       </c>
+      <c r="C172" t="s">
+        <v>542</v>
+      </c>
       <c r="D172" t="s">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="E172" t="s">
+        <v>16</v>
+      </c>
+      <c r="F172" t="s">
         <v>550</v>
       </c>
-      <c r="F172" t="s">
-        <v>16</v>
-      </c>
       <c r="G172" t="s">
-        <v>544</v>
-      </c>
-      <c r="H172" t="s">
         <v>16</v>
       </c>
       <c r="I172" t="s">
@@ -9056,7 +9056,7 @@
         <v>551</v>
       </c>
       <c r="L172" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -9066,19 +9066,19 @@
       <c r="B173" t="s">
         <v>13</v>
       </c>
+      <c r="C173" t="s">
+        <v>542</v>
+      </c>
       <c r="D173" t="s">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="E173" t="s">
+        <v>16</v>
+      </c>
+      <c r="F173" t="s">
         <v>553</v>
       </c>
-      <c r="F173" t="s">
-        <v>16</v>
-      </c>
       <c r="G173" t="s">
-        <v>544</v>
-      </c>
-      <c r="H173" t="s">
         <v>16</v>
       </c>
       <c r="I173" t="s">
@@ -9091,7 +9091,7 @@
         <v>554</v>
       </c>
       <c r="L173" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="174" spans="1:12">
@@ -9101,19 +9101,19 @@
       <c r="B174" t="s">
         <v>13</v>
       </c>
+      <c r="C174" t="s">
+        <v>542</v>
+      </c>
       <c r="D174" t="s">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="E174" t="s">
+        <v>16</v>
+      </c>
+      <c r="F174" t="s">
         <v>556</v>
       </c>
-      <c r="F174" t="s">
-        <v>16</v>
-      </c>
       <c r="G174" t="s">
-        <v>544</v>
-      </c>
-      <c r="H174" t="s">
         <v>16</v>
       </c>
       <c r="I174" t="s">
@@ -9126,7 +9126,7 @@
         <v>557</v>
       </c>
       <c r="L174" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -9136,23 +9136,23 @@
       <c r="B175" t="s">
         <v>13</v>
       </c>
+      <c r="C175" t="s">
+        <v>542</v>
+      </c>
       <c r="D175" t="s">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="E175" t="s">
+        <v>16</v>
+      </c>
+      <c r="F175" t="s">
         <v>559</v>
       </c>
-      <c r="F175" t="s">
-        <v>16</v>
-      </c>
       <c r="G175" t="s">
-        <v>544</v>
-      </c>
-      <c r="H175" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I175" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J175" t="s">
         <v>368</v>
@@ -9161,7 +9161,7 @@
         <v>560</v>
       </c>
       <c r="L175" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -9171,19 +9171,19 @@
       <c r="B176" t="s">
         <v>13</v>
       </c>
+      <c r="C176" t="s">
+        <v>542</v>
+      </c>
       <c r="D176" t="s">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="E176" t="s">
+        <v>16</v>
+      </c>
+      <c r="F176" t="s">
         <v>562</v>
       </c>
-      <c r="F176" t="s">
-        <v>16</v>
-      </c>
       <c r="G176" t="s">
-        <v>544</v>
-      </c>
-      <c r="H176" t="s">
         <v>16</v>
       </c>
       <c r="I176" t="s">
@@ -9196,7 +9196,7 @@
         <v>563</v>
       </c>
       <c r="L176" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -9206,19 +9206,19 @@
       <c r="B177" t="s">
         <v>13</v>
       </c>
+      <c r="C177" t="s">
+        <v>542</v>
+      </c>
       <c r="D177" t="s">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="E177" t="s">
+        <v>16</v>
+      </c>
+      <c r="F177" t="s">
         <v>565</v>
       </c>
-      <c r="F177" t="s">
-        <v>16</v>
-      </c>
       <c r="G177" t="s">
-        <v>544</v>
-      </c>
-      <c r="H177" t="s">
         <v>16</v>
       </c>
       <c r="I177" t="s">
@@ -9231,7 +9231,7 @@
         <v>566</v>
       </c>
       <c r="L177" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -9241,19 +9241,19 @@
       <c r="B178" t="s">
         <v>13</v>
       </c>
+      <c r="C178" t="s">
+        <v>542</v>
+      </c>
       <c r="D178" t="s">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="E178" t="s">
+        <v>16</v>
+      </c>
+      <c r="F178" t="s">
         <v>568</v>
       </c>
-      <c r="F178" t="s">
-        <v>16</v>
-      </c>
       <c r="G178" t="s">
-        <v>544</v>
-      </c>
-      <c r="H178" t="s">
         <v>16</v>
       </c>
       <c r="I178" t="s">
@@ -9266,7 +9266,7 @@
         <v>569</v>
       </c>
       <c r="L178" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -9276,19 +9276,19 @@
       <c r="B179" t="s">
         <v>13</v>
       </c>
+      <c r="C179" t="s">
+        <v>542</v>
+      </c>
       <c r="D179" t="s">
-        <v>542</v>
+        <v>15</v>
       </c>
       <c r="E179" t="s">
+        <v>16</v>
+      </c>
+      <c r="F179" t="s">
         <v>571</v>
       </c>
-      <c r="F179" t="s">
-        <v>16</v>
-      </c>
       <c r="G179" t="s">
-        <v>544</v>
-      </c>
-      <c r="H179" t="s">
         <v>16</v>
       </c>
       <c r="I179" t="s">
@@ -9301,7 +9301,7 @@
         <v>572</v>
       </c>
       <c r="L179" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -9311,19 +9311,19 @@
       <c r="B180" t="s">
         <v>13</v>
       </c>
+      <c r="C180" t="s">
+        <v>574</v>
+      </c>
       <c r="D180" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E180" t="s">
+        <v>16</v>
+      </c>
+      <c r="F180" t="s">
         <v>575</v>
       </c>
-      <c r="F180" t="s">
-        <v>16</v>
-      </c>
       <c r="G180" t="s">
-        <v>544</v>
-      </c>
-      <c r="H180" t="s">
         <v>16</v>
       </c>
       <c r="I180" t="s">
@@ -9336,7 +9336,7 @@
         <v>576</v>
       </c>
       <c r="L180" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -9346,19 +9346,19 @@
       <c r="B181" t="s">
         <v>13</v>
       </c>
+      <c r="C181" t="s">
+        <v>574</v>
+      </c>
       <c r="D181" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E181" t="s">
+        <v>16</v>
+      </c>
+      <c r="F181" t="s">
         <v>578</v>
       </c>
-      <c r="F181" t="s">
-        <v>16</v>
-      </c>
       <c r="G181" t="s">
-        <v>544</v>
-      </c>
-      <c r="H181" t="s">
         <v>16</v>
       </c>
       <c r="I181" t="s">
@@ -9371,7 +9371,7 @@
         <v>579</v>
       </c>
       <c r="L181" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -9381,19 +9381,19 @@
       <c r="B182" t="s">
         <v>13</v>
       </c>
+      <c r="C182" t="s">
+        <v>574</v>
+      </c>
       <c r="D182" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E182" t="s">
+        <v>16</v>
+      </c>
+      <c r="F182" t="s">
         <v>581</v>
       </c>
-      <c r="F182" t="s">
-        <v>16</v>
-      </c>
       <c r="G182" t="s">
-        <v>544</v>
-      </c>
-      <c r="H182" t="s">
         <v>16</v>
       </c>
       <c r="I182" t="s">
@@ -9406,7 +9406,7 @@
         <v>582</v>
       </c>
       <c r="L182" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -9417,19 +9417,19 @@
         <v>584</v>
       </c>
       <c r="C183" t="s">
+        <v>574</v>
+      </c>
+      <c r="D183" t="s">
+        <v>15</v>
+      </c>
+      <c r="E183" t="s">
+        <v>16</v>
+      </c>
+      <c r="G183" t="s">
+        <v>16</v>
+      </c>
+      <c r="H183" t="s">
         <v>585</v>
-      </c>
-      <c r="D183" t="s">
-        <v>574</v>
-      </c>
-      <c r="F183" t="s">
-        <v>16</v>
-      </c>
-      <c r="G183" t="s">
-        <v>544</v>
-      </c>
-      <c r="H183" t="s">
-        <v>16</v>
       </c>
       <c r="I183" t="s">
         <v>16</v>
@@ -9438,7 +9438,7 @@
         <v>368</v>
       </c>
       <c r="L183" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -9448,19 +9448,19 @@
       <c r="B184" t="s">
         <v>13</v>
       </c>
+      <c r="C184" t="s">
+        <v>574</v>
+      </c>
       <c r="D184" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E184" t="s">
+        <v>16</v>
+      </c>
+      <c r="F184" t="s">
         <v>587</v>
       </c>
-      <c r="F184" t="s">
-        <v>16</v>
-      </c>
       <c r="G184" t="s">
-        <v>544</v>
-      </c>
-      <c r="H184" t="s">
         <v>16</v>
       </c>
       <c r="I184" t="s">
@@ -9473,7 +9473,7 @@
         <v>588</v>
       </c>
       <c r="L184" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -9483,19 +9483,19 @@
       <c r="B185" t="s">
         <v>13</v>
       </c>
+      <c r="C185" t="s">
+        <v>574</v>
+      </c>
       <c r="D185" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E185" t="s">
+        <v>16</v>
+      </c>
+      <c r="F185" t="s">
         <v>590</v>
       </c>
-      <c r="F185" t="s">
-        <v>16</v>
-      </c>
       <c r="G185" t="s">
-        <v>544</v>
-      </c>
-      <c r="H185" t="s">
         <v>16</v>
       </c>
       <c r="I185" t="s">
@@ -9508,7 +9508,7 @@
         <v>591</v>
       </c>
       <c r="L185" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -9518,19 +9518,19 @@
       <c r="B186" t="s">
         <v>13</v>
       </c>
+      <c r="C186" t="s">
+        <v>574</v>
+      </c>
       <c r="D186" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E186" t="s">
+        <v>16</v>
+      </c>
+      <c r="F186" t="s">
         <v>593</v>
       </c>
-      <c r="F186" t="s">
-        <v>16</v>
-      </c>
       <c r="G186" t="s">
-        <v>544</v>
-      </c>
-      <c r="H186" t="s">
         <v>16</v>
       </c>
       <c r="I186" t="s">
@@ -9543,7 +9543,7 @@
         <v>594</v>
       </c>
       <c r="L186" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -9553,19 +9553,19 @@
       <c r="B187" t="s">
         <v>13</v>
       </c>
+      <c r="C187" t="s">
+        <v>574</v>
+      </c>
       <c r="D187" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E187" t="s">
+        <v>16</v>
+      </c>
+      <c r="F187" t="s">
         <v>596</v>
       </c>
-      <c r="F187" t="s">
-        <v>16</v>
-      </c>
       <c r="G187" t="s">
-        <v>544</v>
-      </c>
-      <c r="H187" t="s">
         <v>16</v>
       </c>
       <c r="I187" t="s">
@@ -9578,7 +9578,7 @@
         <v>597</v>
       </c>
       <c r="L187" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -9588,19 +9588,19 @@
       <c r="B188" t="s">
         <v>13</v>
       </c>
+      <c r="C188" t="s">
+        <v>574</v>
+      </c>
       <c r="D188" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E188" t="s">
+        <v>16</v>
+      </c>
+      <c r="F188" t="s">
         <v>599</v>
       </c>
-      <c r="F188" t="s">
-        <v>16</v>
-      </c>
       <c r="G188" t="s">
-        <v>544</v>
-      </c>
-      <c r="H188" t="s">
         <v>16</v>
       </c>
       <c r="I188" t="s">
@@ -9613,7 +9613,7 @@
         <v>600</v>
       </c>
       <c r="L188" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -9623,19 +9623,19 @@
       <c r="B189" t="s">
         <v>13</v>
       </c>
+      <c r="C189" t="s">
+        <v>574</v>
+      </c>
       <c r="D189" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E189" t="s">
+        <v>16</v>
+      </c>
+      <c r="F189" t="s">
         <v>602</v>
       </c>
-      <c r="F189" t="s">
-        <v>16</v>
-      </c>
       <c r="G189" t="s">
-        <v>544</v>
-      </c>
-      <c r="H189" t="s">
         <v>16</v>
       </c>
       <c r="I189" t="s">
@@ -9648,7 +9648,7 @@
         <v>603</v>
       </c>
       <c r="L189" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -9658,19 +9658,19 @@
       <c r="B190" t="s">
         <v>13</v>
       </c>
+      <c r="C190" t="s">
+        <v>574</v>
+      </c>
       <c r="D190" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E190" t="s">
+        <v>16</v>
+      </c>
+      <c r="F190" t="s">
         <v>605</v>
       </c>
-      <c r="F190" t="s">
-        <v>16</v>
-      </c>
       <c r="G190" t="s">
-        <v>544</v>
-      </c>
-      <c r="H190" t="s">
         <v>16</v>
       </c>
       <c r="I190" t="s">
@@ -9683,7 +9683,7 @@
         <v>606</v>
       </c>
       <c r="L190" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -9693,19 +9693,19 @@
       <c r="B191" t="s">
         <v>13</v>
       </c>
+      <c r="C191" t="s">
+        <v>574</v>
+      </c>
       <c r="D191" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E191" t="s">
+        <v>16</v>
+      </c>
+      <c r="F191" t="s">
         <v>608</v>
       </c>
-      <c r="F191" t="s">
-        <v>16</v>
-      </c>
       <c r="G191" t="s">
-        <v>544</v>
-      </c>
-      <c r="H191" t="s">
         <v>16</v>
       </c>
       <c r="I191" t="s">
@@ -9718,7 +9718,7 @@
         <v>609</v>
       </c>
       <c r="L191" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -9728,19 +9728,19 @@
       <c r="B192" t="s">
         <v>13</v>
       </c>
+      <c r="C192" t="s">
+        <v>574</v>
+      </c>
       <c r="D192" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E192" t="s">
+        <v>16</v>
+      </c>
+      <c r="F192" t="s">
         <v>611</v>
       </c>
-      <c r="F192" t="s">
-        <v>16</v>
-      </c>
       <c r="G192" t="s">
-        <v>544</v>
-      </c>
-      <c r="H192" t="s">
         <v>16</v>
       </c>
       <c r="I192" t="s">
@@ -9753,7 +9753,7 @@
         <v>612</v>
       </c>
       <c r="L192" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -9763,19 +9763,19 @@
       <c r="B193" t="s">
         <v>13</v>
       </c>
+      <c r="C193" t="s">
+        <v>574</v>
+      </c>
       <c r="D193" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E193" t="s">
+        <v>16</v>
+      </c>
+      <c r="F193" t="s">
         <v>614</v>
       </c>
-      <c r="F193" t="s">
-        <v>16</v>
-      </c>
       <c r="G193" t="s">
-        <v>544</v>
-      </c>
-      <c r="H193" t="s">
         <v>16</v>
       </c>
       <c r="I193" t="s">
@@ -9788,7 +9788,7 @@
         <v>615</v>
       </c>
       <c r="L193" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -9798,19 +9798,19 @@
       <c r="B194" t="s">
         <v>13</v>
       </c>
+      <c r="C194" t="s">
+        <v>574</v>
+      </c>
       <c r="D194" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E194" t="s">
+        <v>16</v>
+      </c>
+      <c r="F194" t="s">
         <v>617</v>
       </c>
-      <c r="F194" t="s">
-        <v>16</v>
-      </c>
       <c r="G194" t="s">
-        <v>544</v>
-      </c>
-      <c r="H194" t="s">
         <v>16</v>
       </c>
       <c r="I194" t="s">
@@ -9823,7 +9823,7 @@
         <v>618</v>
       </c>
       <c r="L194" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -9833,19 +9833,19 @@
       <c r="B195" t="s">
         <v>13</v>
       </c>
+      <c r="C195" t="s">
+        <v>574</v>
+      </c>
       <c r="D195" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E195" t="s">
+        <v>16</v>
+      </c>
+      <c r="F195" t="s">
         <v>620</v>
       </c>
-      <c r="F195" t="s">
-        <v>16</v>
-      </c>
       <c r="G195" t="s">
-        <v>544</v>
-      </c>
-      <c r="H195" t="s">
         <v>16</v>
       </c>
       <c r="I195" t="s">
@@ -9858,7 +9858,7 @@
         <v>621</v>
       </c>
       <c r="L195" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -9868,19 +9868,19 @@
       <c r="B196" t="s">
         <v>13</v>
       </c>
+      <c r="C196" t="s">
+        <v>574</v>
+      </c>
       <c r="D196" t="s">
-        <v>574</v>
+        <v>15</v>
       </c>
       <c r="E196" t="s">
+        <v>16</v>
+      </c>
+      <c r="F196" t="s">
         <v>623</v>
       </c>
-      <c r="F196" t="s">
-        <v>16</v>
-      </c>
       <c r="G196" t="s">
-        <v>544</v>
-      </c>
-      <c r="H196" t="s">
         <v>16</v>
       </c>
       <c r="I196" t="s">
@@ -9893,7 +9893,7 @@
         <v>624</v>
       </c>
       <c r="L196" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -9903,19 +9903,19 @@
       <c r="B197" t="s">
         <v>13</v>
       </c>
+      <c r="C197" t="s">
+        <v>626</v>
+      </c>
       <c r="D197" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E197" t="s">
+        <v>16</v>
+      </c>
+      <c r="F197" t="s">
         <v>627</v>
       </c>
-      <c r="F197" t="s">
-        <v>16</v>
-      </c>
       <c r="G197" t="s">
-        <v>544</v>
-      </c>
-      <c r="H197" t="s">
         <v>16</v>
       </c>
       <c r="I197" t="s">
@@ -9928,7 +9928,7 @@
         <v>628</v>
       </c>
       <c r="L197" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -9938,19 +9938,19 @@
       <c r="B198" t="s">
         <v>13</v>
       </c>
+      <c r="C198" t="s">
+        <v>626</v>
+      </c>
       <c r="D198" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E198" t="s">
+        <v>16</v>
+      </c>
+      <c r="F198" t="s">
         <v>630</v>
       </c>
-      <c r="F198" t="s">
-        <v>16</v>
-      </c>
       <c r="G198" t="s">
-        <v>544</v>
-      </c>
-      <c r="H198" t="s">
         <v>16</v>
       </c>
       <c r="I198" t="s">
@@ -9963,7 +9963,7 @@
         <v>631</v>
       </c>
       <c r="L198" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -9973,19 +9973,19 @@
       <c r="B199" t="s">
         <v>13</v>
       </c>
+      <c r="C199" t="s">
+        <v>626</v>
+      </c>
       <c r="D199" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E199" t="s">
+        <v>16</v>
+      </c>
+      <c r="F199" t="s">
         <v>633</v>
       </c>
-      <c r="F199" t="s">
-        <v>16</v>
-      </c>
       <c r="G199" t="s">
-        <v>544</v>
-      </c>
-      <c r="H199" t="s">
         <v>16</v>
       </c>
       <c r="I199" t="s">
@@ -9998,7 +9998,7 @@
         <v>634</v>
       </c>
       <c r="L199" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -10008,19 +10008,19 @@
       <c r="B200" t="s">
         <v>13</v>
       </c>
+      <c r="C200" t="s">
+        <v>626</v>
+      </c>
       <c r="D200" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E200" t="s">
+        <v>16</v>
+      </c>
+      <c r="F200" t="s">
         <v>636</v>
       </c>
-      <c r="F200" t="s">
-        <v>16</v>
-      </c>
       <c r="G200" t="s">
-        <v>544</v>
-      </c>
-      <c r="H200" t="s">
         <v>16</v>
       </c>
       <c r="I200" t="s">
@@ -10033,7 +10033,7 @@
         <v>637</v>
       </c>
       <c r="L200" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -10043,19 +10043,19 @@
       <c r="B201" t="s">
         <v>13</v>
       </c>
+      <c r="C201" t="s">
+        <v>626</v>
+      </c>
       <c r="D201" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E201" t="s">
+        <v>16</v>
+      </c>
+      <c r="F201" t="s">
         <v>639</v>
       </c>
-      <c r="F201" t="s">
-        <v>16</v>
-      </c>
       <c r="G201" t="s">
-        <v>544</v>
-      </c>
-      <c r="H201" t="s">
         <v>16</v>
       </c>
       <c r="I201" t="s">
@@ -10068,7 +10068,7 @@
         <v>640</v>
       </c>
       <c r="L201" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -10078,19 +10078,19 @@
       <c r="B202" t="s">
         <v>13</v>
       </c>
+      <c r="C202" t="s">
+        <v>626</v>
+      </c>
       <c r="D202" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E202" t="s">
+        <v>16</v>
+      </c>
+      <c r="F202" t="s">
         <v>642</v>
       </c>
-      <c r="F202" t="s">
-        <v>16</v>
-      </c>
       <c r="G202" t="s">
-        <v>544</v>
-      </c>
-      <c r="H202" t="s">
         <v>16</v>
       </c>
       <c r="I202" t="s">
@@ -10103,7 +10103,7 @@
         <v>643</v>
       </c>
       <c r="L202" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -10113,19 +10113,19 @@
       <c r="B203" t="s">
         <v>13</v>
       </c>
+      <c r="C203" t="s">
+        <v>626</v>
+      </c>
       <c r="D203" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E203" t="s">
+        <v>16</v>
+      </c>
+      <c r="F203" t="s">
         <v>645</v>
       </c>
-      <c r="F203" t="s">
-        <v>16</v>
-      </c>
       <c r="G203" t="s">
-        <v>544</v>
-      </c>
-      <c r="H203" t="s">
         <v>16</v>
       </c>
       <c r="I203" t="s">
@@ -10138,7 +10138,7 @@
         <v>646</v>
       </c>
       <c r="L203" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -10148,19 +10148,19 @@
       <c r="B204" t="s">
         <v>13</v>
       </c>
+      <c r="C204" t="s">
+        <v>626</v>
+      </c>
       <c r="D204" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E204" t="s">
+        <v>16</v>
+      </c>
+      <c r="F204" t="s">
         <v>648</v>
       </c>
-      <c r="F204" t="s">
-        <v>16</v>
-      </c>
       <c r="G204" t="s">
-        <v>544</v>
-      </c>
-      <c r="H204" t="s">
         <v>16</v>
       </c>
       <c r="I204" t="s">
@@ -10173,7 +10173,7 @@
         <v>649</v>
       </c>
       <c r="L204" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -10183,19 +10183,19 @@
       <c r="B205" t="s">
         <v>13</v>
       </c>
+      <c r="C205" t="s">
+        <v>626</v>
+      </c>
       <c r="D205" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E205" t="s">
+        <v>16</v>
+      </c>
+      <c r="F205" t="s">
         <v>651</v>
       </c>
-      <c r="F205" t="s">
-        <v>16</v>
-      </c>
       <c r="G205" t="s">
-        <v>544</v>
-      </c>
-      <c r="H205" t="s">
         <v>16</v>
       </c>
       <c r="I205" t="s">
@@ -10208,7 +10208,7 @@
         <v>652</v>
       </c>
       <c r="L205" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -10218,19 +10218,19 @@
       <c r="B206" t="s">
         <v>13</v>
       </c>
+      <c r="C206" t="s">
+        <v>626</v>
+      </c>
       <c r="D206" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E206" t="s">
+        <v>16</v>
+      </c>
+      <c r="F206" t="s">
         <v>654</v>
       </c>
-      <c r="F206" t="s">
-        <v>16</v>
-      </c>
       <c r="G206" t="s">
-        <v>544</v>
-      </c>
-      <c r="H206" t="s">
         <v>16</v>
       </c>
       <c r="I206" t="s">
@@ -10243,7 +10243,7 @@
         <v>655</v>
       </c>
       <c r="L206" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -10253,23 +10253,23 @@
       <c r="B207" t="s">
         <v>13</v>
       </c>
+      <c r="C207" t="s">
+        <v>626</v>
+      </c>
       <c r="D207" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E207" t="s">
+        <v>16</v>
+      </c>
+      <c r="F207" t="s">
         <v>657</v>
       </c>
-      <c r="F207" t="s">
-        <v>16</v>
-      </c>
       <c r="G207" t="s">
-        <v>544</v>
-      </c>
-      <c r="H207" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I207" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J207" t="s">
         <v>368</v>
@@ -10278,7 +10278,7 @@
         <v>658</v>
       </c>
       <c r="L207" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -10288,19 +10288,19 @@
       <c r="B208" t="s">
         <v>13</v>
       </c>
+      <c r="C208" t="s">
+        <v>626</v>
+      </c>
       <c r="D208" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E208" t="s">
+        <v>16</v>
+      </c>
+      <c r="F208" t="s">
         <v>660</v>
       </c>
-      <c r="F208" t="s">
-        <v>16</v>
-      </c>
       <c r="G208" t="s">
-        <v>544</v>
-      </c>
-      <c r="H208" t="s">
         <v>16</v>
       </c>
       <c r="I208" t="s">
@@ -10313,7 +10313,7 @@
         <v>661</v>
       </c>
       <c r="L208" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -10323,19 +10323,19 @@
       <c r="B209" t="s">
         <v>13</v>
       </c>
+      <c r="C209" t="s">
+        <v>626</v>
+      </c>
       <c r="D209" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E209" t="s">
+        <v>16</v>
+      </c>
+      <c r="F209" t="s">
         <v>663</v>
       </c>
-      <c r="F209" t="s">
-        <v>16</v>
-      </c>
       <c r="G209" t="s">
-        <v>544</v>
-      </c>
-      <c r="H209" t="s">
         <v>16</v>
       </c>
       <c r="I209" t="s">
@@ -10348,7 +10348,7 @@
         <v>664</v>
       </c>
       <c r="L209" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -10358,19 +10358,19 @@
       <c r="B210" t="s">
         <v>13</v>
       </c>
+      <c r="C210" t="s">
+        <v>626</v>
+      </c>
       <c r="D210" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E210" t="s">
+        <v>16</v>
+      </c>
+      <c r="F210" t="s">
         <v>666</v>
       </c>
-      <c r="F210" t="s">
-        <v>16</v>
-      </c>
       <c r="G210" t="s">
-        <v>544</v>
-      </c>
-      <c r="H210" t="s">
         <v>16</v>
       </c>
       <c r="I210" t="s">
@@ -10383,7 +10383,7 @@
         <v>667</v>
       </c>
       <c r="L210" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -10393,19 +10393,19 @@
       <c r="B211" t="s">
         <v>13</v>
       </c>
+      <c r="C211" t="s">
+        <v>626</v>
+      </c>
       <c r="D211" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E211" t="s">
+        <v>16</v>
+      </c>
+      <c r="F211" t="s">
         <v>669</v>
       </c>
-      <c r="F211" t="s">
-        <v>16</v>
-      </c>
       <c r="G211" t="s">
-        <v>544</v>
-      </c>
-      <c r="H211" t="s">
         <v>16</v>
       </c>
       <c r="I211" t="s">
@@ -10418,7 +10418,7 @@
         <v>670</v>
       </c>
       <c r="L211" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -10428,19 +10428,19 @@
       <c r="B212" t="s">
         <v>13</v>
       </c>
+      <c r="C212" t="s">
+        <v>626</v>
+      </c>
       <c r="D212" t="s">
-        <v>626</v>
+        <v>15</v>
       </c>
       <c r="E212" t="s">
+        <v>16</v>
+      </c>
+      <c r="F212" t="s">
         <v>672</v>
       </c>
-      <c r="F212" t="s">
-        <v>16</v>
-      </c>
       <c r="G212" t="s">
-        <v>544</v>
-      </c>
-      <c r="H212" t="s">
         <v>16</v>
       </c>
       <c r="I212" t="s">
@@ -10453,7 +10453,7 @@
         <v>673</v>
       </c>
       <c r="L212" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -10463,19 +10463,19 @@
       <c r="B213" t="s">
         <v>13</v>
       </c>
+      <c r="C213" t="s">
+        <v>675</v>
+      </c>
       <c r="D213" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="E213" t="s">
+        <v>16</v>
+      </c>
+      <c r="F213" t="s">
         <v>676</v>
       </c>
-      <c r="F213" t="s">
-        <v>16</v>
-      </c>
       <c r="G213" t="s">
-        <v>544</v>
-      </c>
-      <c r="H213" t="s">
         <v>16</v>
       </c>
       <c r="I213" t="s">
@@ -10488,7 +10488,7 @@
         <v>677</v>
       </c>
       <c r="L213" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -10498,19 +10498,19 @@
       <c r="B214" t="s">
         <v>13</v>
       </c>
+      <c r="C214" t="s">
+        <v>675</v>
+      </c>
       <c r="D214" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="E214" t="s">
+        <v>16</v>
+      </c>
+      <c r="F214" t="s">
         <v>679</v>
       </c>
-      <c r="F214" t="s">
-        <v>16</v>
-      </c>
       <c r="G214" t="s">
-        <v>544</v>
-      </c>
-      <c r="H214" t="s">
         <v>16</v>
       </c>
       <c r="I214" t="s">
@@ -10523,7 +10523,7 @@
         <v>680</v>
       </c>
       <c r="L214" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -10533,19 +10533,19 @@
       <c r="B215" t="s">
         <v>13</v>
       </c>
+      <c r="C215" t="s">
+        <v>675</v>
+      </c>
       <c r="D215" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="E215" t="s">
+        <v>16</v>
+      </c>
+      <c r="F215" t="s">
         <v>682</v>
       </c>
-      <c r="F215" t="s">
-        <v>16</v>
-      </c>
       <c r="G215" t="s">
-        <v>544</v>
-      </c>
-      <c r="H215" t="s">
         <v>16</v>
       </c>
       <c r="I215" t="s">
@@ -10558,7 +10558,7 @@
         <v>683</v>
       </c>
       <c r="L215" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -10568,19 +10568,19 @@
       <c r="B216" t="s">
         <v>13</v>
       </c>
+      <c r="C216" t="s">
+        <v>675</v>
+      </c>
       <c r="D216" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="E216" t="s">
+        <v>16</v>
+      </c>
+      <c r="F216" t="s">
         <v>685</v>
       </c>
-      <c r="F216" t="s">
-        <v>16</v>
-      </c>
       <c r="G216" t="s">
-        <v>544</v>
-      </c>
-      <c r="H216" t="s">
         <v>16</v>
       </c>
       <c r="I216" t="s">
@@ -10593,7 +10593,7 @@
         <v>686</v>
       </c>
       <c r="L216" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -10603,19 +10603,19 @@
       <c r="B217" t="s">
         <v>13</v>
       </c>
+      <c r="C217" t="s">
+        <v>675</v>
+      </c>
       <c r="D217" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="E217" t="s">
+        <v>16</v>
+      </c>
+      <c r="F217" t="s">
         <v>688</v>
       </c>
-      <c r="F217" t="s">
-        <v>16</v>
-      </c>
       <c r="G217" t="s">
-        <v>544</v>
-      </c>
-      <c r="H217" t="s">
         <v>16</v>
       </c>
       <c r="I217" t="s">
@@ -10628,7 +10628,7 @@
         <v>689</v>
       </c>
       <c r="L217" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -10638,19 +10638,19 @@
       <c r="B218" t="s">
         <v>13</v>
       </c>
+      <c r="C218" t="s">
+        <v>675</v>
+      </c>
       <c r="D218" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="E218" t="s">
+        <v>16</v>
+      </c>
+      <c r="F218" t="s">
         <v>691</v>
       </c>
-      <c r="F218" t="s">
-        <v>16</v>
-      </c>
       <c r="G218" t="s">
-        <v>544</v>
-      </c>
-      <c r="H218" t="s">
         <v>16</v>
       </c>
       <c r="I218" t="s">
@@ -10663,7 +10663,7 @@
         <v>692</v>
       </c>
       <c r="L218" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -10673,19 +10673,19 @@
       <c r="B219" t="s">
         <v>13</v>
       </c>
+      <c r="C219" t="s">
+        <v>675</v>
+      </c>
       <c r="D219" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="E219" t="s">
+        <v>16</v>
+      </c>
+      <c r="F219" t="s">
         <v>694</v>
       </c>
-      <c r="F219" t="s">
-        <v>16</v>
-      </c>
       <c r="G219" t="s">
-        <v>544</v>
-      </c>
-      <c r="H219" t="s">
         <v>16</v>
       </c>
       <c r="I219" t="s">
@@ -10698,7 +10698,7 @@
         <v>695</v>
       </c>
       <c r="L219" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -10708,19 +10708,19 @@
       <c r="B220" t="s">
         <v>13</v>
       </c>
+      <c r="C220" t="s">
+        <v>675</v>
+      </c>
       <c r="D220" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="E220" t="s">
+        <v>16</v>
+      </c>
+      <c r="F220" t="s">
         <v>697</v>
       </c>
-      <c r="F220" t="s">
-        <v>16</v>
-      </c>
       <c r="G220" t="s">
-        <v>544</v>
-      </c>
-      <c r="H220" t="s">
         <v>16</v>
       </c>
       <c r="I220" t="s">
@@ -10733,7 +10733,7 @@
         <v>698</v>
       </c>
       <c r="L220" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -10743,19 +10743,19 @@
       <c r="B221" t="s">
         <v>13</v>
       </c>
+      <c r="C221" t="s">
+        <v>675</v>
+      </c>
       <c r="D221" t="s">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="E221" t="s">
+        <v>16</v>
+      </c>
+      <c r="F221" t="s">
         <v>700</v>
       </c>
-      <c r="F221" t="s">
-        <v>16</v>
-      </c>
       <c r="G221" t="s">
-        <v>544</v>
-      </c>
-      <c r="H221" t="s">
         <v>16</v>
       </c>
       <c r="I221" t="s">
@@ -10768,7 +10768,7 @@
         <v>701</v>
       </c>
       <c r="L221" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -10778,19 +10778,19 @@
       <c r="B222" t="s">
         <v>13</v>
       </c>
+      <c r="C222" t="s">
+        <v>703</v>
+      </c>
       <c r="D222" t="s">
-        <v>703</v>
+        <v>15</v>
       </c>
       <c r="E222" t="s">
+        <v>16</v>
+      </c>
+      <c r="F222" t="s">
         <v>704</v>
       </c>
-      <c r="F222" t="s">
-        <v>16</v>
-      </c>
       <c r="G222" t="s">
-        <v>705</v>
-      </c>
-      <c r="H222" t="s">
         <v>16</v>
       </c>
       <c r="I222" t="s">
@@ -10800,10 +10800,10 @@
         <v>368</v>
       </c>
       <c r="K222" t="s">
+        <v>705</v>
+      </c>
+      <c r="L222" t="s">
         <v>706</v>
-      </c>
-      <c r="L222" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -10813,19 +10813,19 @@
       <c r="B223" t="s">
         <v>13</v>
       </c>
+      <c r="C223" t="s">
+        <v>703</v>
+      </c>
       <c r="D223" t="s">
-        <v>703</v>
+        <v>15</v>
       </c>
       <c r="E223" t="s">
+        <v>16</v>
+      </c>
+      <c r="F223" t="s">
         <v>708</v>
       </c>
-      <c r="F223" t="s">
-        <v>16</v>
-      </c>
       <c r="G223" t="s">
-        <v>705</v>
-      </c>
-      <c r="H223" t="s">
         <v>16</v>
       </c>
       <c r="I223" t="s">
@@ -10838,7 +10838,7 @@
         <v>709</v>
       </c>
       <c r="L223" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -10848,19 +10848,19 @@
       <c r="B224" t="s">
         <v>13</v>
       </c>
+      <c r="C224" t="s">
+        <v>703</v>
+      </c>
       <c r="D224" t="s">
-        <v>703</v>
+        <v>15</v>
       </c>
       <c r="E224" t="s">
+        <v>16</v>
+      </c>
+      <c r="F224" t="s">
         <v>711</v>
       </c>
-      <c r="F224" t="s">
-        <v>16</v>
-      </c>
       <c r="G224" t="s">
-        <v>705</v>
-      </c>
-      <c r="H224" t="s">
         <v>16</v>
       </c>
       <c r="I224" t="s">
@@ -10873,7 +10873,7 @@
         <v>712</v>
       </c>
       <c r="L224" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -10883,19 +10883,19 @@
       <c r="B225" t="s">
         <v>13</v>
       </c>
+      <c r="C225" t="s">
+        <v>703</v>
+      </c>
       <c r="D225" t="s">
-        <v>703</v>
+        <v>15</v>
       </c>
       <c r="E225" t="s">
+        <v>16</v>
+      </c>
+      <c r="F225" t="s">
         <v>714</v>
       </c>
-      <c r="F225" t="s">
-        <v>16</v>
-      </c>
       <c r="G225" t="s">
-        <v>705</v>
-      </c>
-      <c r="H225" t="s">
         <v>16</v>
       </c>
       <c r="I225" t="s">
@@ -10908,7 +10908,7 @@
         <v>715</v>
       </c>
       <c r="L225" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -10918,19 +10918,19 @@
       <c r="B226" t="s">
         <v>13</v>
       </c>
+      <c r="C226" t="s">
+        <v>703</v>
+      </c>
       <c r="D226" t="s">
-        <v>703</v>
+        <v>15</v>
       </c>
       <c r="E226" t="s">
+        <v>16</v>
+      </c>
+      <c r="F226" t="s">
         <v>717</v>
       </c>
-      <c r="F226" t="s">
-        <v>16</v>
-      </c>
       <c r="G226" t="s">
-        <v>705</v>
-      </c>
-      <c r="H226" t="s">
         <v>16</v>
       </c>
       <c r="I226" t="s">
@@ -10943,7 +10943,7 @@
         <v>718</v>
       </c>
       <c r="L226" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -10953,19 +10953,19 @@
       <c r="B227" t="s">
         <v>13</v>
       </c>
+      <c r="C227" t="s">
+        <v>703</v>
+      </c>
       <c r="D227" t="s">
-        <v>703</v>
+        <v>15</v>
       </c>
       <c r="E227" t="s">
+        <v>16</v>
+      </c>
+      <c r="F227" t="s">
         <v>720</v>
       </c>
-      <c r="F227" t="s">
-        <v>16</v>
-      </c>
       <c r="G227" t="s">
-        <v>705</v>
-      </c>
-      <c r="H227" t="s">
         <v>16</v>
       </c>
       <c r="I227" t="s">
@@ -10978,7 +10978,7 @@
         <v>721</v>
       </c>
       <c r="L227" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -10988,20 +10988,20 @@
       <c r="B228" t="s">
         <v>13</v>
       </c>
+      <c r="C228" t="s">
+        <v>723</v>
+      </c>
       <c r="D228" t="s">
-        <v>723</v>
+        <v>15</v>
       </c>
       <c r="E228" t="s">
+        <v>32</v>
+      </c>
+      <c r="F228" t="s">
         <v>724</v>
       </c>
-      <c r="F228" t="s">
-        <v>16</v>
-      </c>
       <c r="G228" t="s">
-        <v>705</v>
-      </c>
-      <c r="H228" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I228" t="s">
         <v>16</v>
@@ -11013,7 +11013,7 @@
         <v>725</v>
       </c>
       <c r="L228" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -11023,20 +11023,20 @@
       <c r="B229" t="s">
         <v>13</v>
       </c>
+      <c r="C229" t="s">
+        <v>723</v>
+      </c>
       <c r="D229" t="s">
-        <v>723</v>
+        <v>15</v>
       </c>
       <c r="E229" t="s">
+        <v>32</v>
+      </c>
+      <c r="F229" t="s">
         <v>727</v>
       </c>
-      <c r="F229" t="s">
-        <v>16</v>
-      </c>
       <c r="G229" t="s">
-        <v>705</v>
-      </c>
-      <c r="H229" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I229" t="s">
         <v>16</v>
@@ -11048,7 +11048,7 @@
         <v>728</v>
       </c>
       <c r="L229" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -11058,20 +11058,20 @@
       <c r="B230" t="s">
         <v>13</v>
       </c>
+      <c r="C230" t="s">
+        <v>723</v>
+      </c>
       <c r="D230" t="s">
-        <v>723</v>
+        <v>15</v>
       </c>
       <c r="E230" t="s">
+        <v>32</v>
+      </c>
+      <c r="F230" t="s">
         <v>730</v>
       </c>
-      <c r="F230" t="s">
-        <v>16</v>
-      </c>
       <c r="G230" t="s">
-        <v>705</v>
-      </c>
-      <c r="H230" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I230" t="s">
         <v>16</v>
@@ -11083,7 +11083,7 @@
         <v>731</v>
       </c>
       <c r="L230" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -11093,23 +11093,23 @@
       <c r="B231" t="s">
         <v>13</v>
       </c>
+      <c r="C231" t="s">
+        <v>723</v>
+      </c>
       <c r="D231" t="s">
-        <v>723</v>
+        <v>15</v>
       </c>
       <c r="E231" t="s">
+        <v>32</v>
+      </c>
+      <c r="F231" t="s">
         <v>733</v>
       </c>
-      <c r="F231" t="s">
-        <v>32</v>
-      </c>
       <c r="G231" t="s">
-        <v>705</v>
-      </c>
-      <c r="H231" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I231" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J231" t="s">
         <v>18</v>
@@ -11118,7 +11118,7 @@
         <v>734</v>
       </c>
       <c r="L231" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -11128,23 +11128,23 @@
       <c r="B232" t="s">
         <v>13</v>
       </c>
+      <c r="C232" t="s">
+        <v>723</v>
+      </c>
       <c r="D232" t="s">
-        <v>723</v>
+        <v>15</v>
       </c>
       <c r="E232" t="s">
+        <v>32</v>
+      </c>
+      <c r="F232" t="s">
         <v>736</v>
       </c>
-      <c r="F232" t="s">
-        <v>32</v>
-      </c>
       <c r="G232" t="s">
-        <v>705</v>
-      </c>
-      <c r="H232" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I232" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J232" t="s">
         <v>18</v>
@@ -11153,7 +11153,7 @@
         <v>737</v>
       </c>
       <c r="L232" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -11163,20 +11163,20 @@
       <c r="B233" t="s">
         <v>13</v>
       </c>
+      <c r="C233" t="s">
+        <v>739</v>
+      </c>
       <c r="D233" t="s">
-        <v>739</v>
+        <v>15</v>
       </c>
       <c r="E233" t="s">
+        <v>32</v>
+      </c>
+      <c r="F233" t="s">
         <v>740</v>
       </c>
-      <c r="F233" t="s">
-        <v>16</v>
-      </c>
       <c r="G233" t="s">
-        <v>705</v>
-      </c>
-      <c r="H233" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I233" t="s">
         <v>16</v>
@@ -11188,7 +11188,7 @@
         <v>741</v>
       </c>
       <c r="L233" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -11198,23 +11198,23 @@
       <c r="B234" t="s">
         <v>13</v>
       </c>
+      <c r="C234" t="s">
+        <v>739</v>
+      </c>
       <c r="D234" t="s">
-        <v>739</v>
+        <v>15</v>
       </c>
       <c r="E234" t="s">
+        <v>32</v>
+      </c>
+      <c r="F234" t="s">
         <v>743</v>
       </c>
-      <c r="F234" t="s">
-        <v>32</v>
-      </c>
       <c r="G234" t="s">
-        <v>705</v>
-      </c>
-      <c r="H234" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I234" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J234" t="s">
         <v>18</v>
@@ -11223,7 +11223,7 @@
         <v>744</v>
       </c>
       <c r="L234" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -11233,20 +11233,20 @@
       <c r="B235" t="s">
         <v>13</v>
       </c>
+      <c r="C235" t="s">
+        <v>739</v>
+      </c>
       <c r="D235" t="s">
-        <v>739</v>
+        <v>15</v>
       </c>
       <c r="E235" t="s">
+        <v>32</v>
+      </c>
+      <c r="F235" t="s">
         <v>746</v>
       </c>
-      <c r="F235" t="s">
-        <v>16</v>
-      </c>
       <c r="G235" t="s">
-        <v>705</v>
-      </c>
-      <c r="H235" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I235" t="s">
         <v>16</v>
@@ -11258,7 +11258,7 @@
         <v>747</v>
       </c>
       <c r="L235" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -11268,20 +11268,20 @@
       <c r="B236" t="s">
         <v>13</v>
       </c>
+      <c r="C236" t="s">
+        <v>739</v>
+      </c>
       <c r="D236" t="s">
-        <v>739</v>
+        <v>15</v>
       </c>
       <c r="E236" t="s">
+        <v>32</v>
+      </c>
+      <c r="F236" t="s">
         <v>749</v>
       </c>
-      <c r="F236" t="s">
-        <v>16</v>
-      </c>
       <c r="G236" t="s">
-        <v>705</v>
-      </c>
-      <c r="H236" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I236" t="s">
         <v>16</v>
@@ -11293,7 +11293,7 @@
         <v>750</v>
       </c>
       <c r="L236" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -11303,20 +11303,20 @@
       <c r="B237" t="s">
         <v>13</v>
       </c>
+      <c r="C237" t="s">
+        <v>739</v>
+      </c>
       <c r="D237" t="s">
-        <v>739</v>
+        <v>15</v>
       </c>
       <c r="E237" t="s">
+        <v>32</v>
+      </c>
+      <c r="F237" t="s">
         <v>752</v>
       </c>
-      <c r="F237" t="s">
-        <v>16</v>
-      </c>
       <c r="G237" t="s">
-        <v>705</v>
-      </c>
-      <c r="H237" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I237" t="s">
         <v>16</v>
@@ -11328,7 +11328,7 @@
         <v>753</v>
       </c>
       <c r="L237" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -11338,20 +11338,20 @@
       <c r="B238" t="s">
         <v>13</v>
       </c>
+      <c r="C238" t="s">
+        <v>739</v>
+      </c>
       <c r="D238" t="s">
-        <v>739</v>
+        <v>15</v>
       </c>
       <c r="E238" t="s">
+        <v>32</v>
+      </c>
+      <c r="F238" t="s">
         <v>755</v>
       </c>
-      <c r="F238" t="s">
-        <v>16</v>
-      </c>
       <c r="G238" t="s">
-        <v>705</v>
-      </c>
-      <c r="H238" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I238" t="s">
         <v>16</v>
@@ -11363,7 +11363,7 @@
         <v>756</v>
       </c>
       <c r="L238" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -11373,20 +11373,20 @@
       <c r="B239" t="s">
         <v>13</v>
       </c>
+      <c r="C239" t="s">
+        <v>739</v>
+      </c>
       <c r="D239" t="s">
-        <v>739</v>
+        <v>15</v>
       </c>
       <c r="E239" t="s">
+        <v>32</v>
+      </c>
+      <c r="F239" t="s">
         <v>758</v>
       </c>
-      <c r="F239" t="s">
-        <v>16</v>
-      </c>
       <c r="G239" t="s">
-        <v>705</v>
-      </c>
-      <c r="H239" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I239" t="s">
         <v>16</v>
@@ -11398,7 +11398,7 @@
         <v>759</v>
       </c>
       <c r="L239" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -11408,19 +11408,19 @@
       <c r="B240" t="s">
         <v>13</v>
       </c>
+      <c r="C240" t="s">
+        <v>739</v>
+      </c>
       <c r="D240" t="s">
-        <v>739</v>
+        <v>15</v>
       </c>
       <c r="E240" t="s">
+        <v>16</v>
+      </c>
+      <c r="F240" t="s">
         <v>761</v>
       </c>
-      <c r="F240" t="s">
-        <v>16</v>
-      </c>
       <c r="G240" t="s">
-        <v>705</v>
-      </c>
-      <c r="H240" t="s">
         <v>16</v>
       </c>
       <c r="I240" t="s">
@@ -11433,7 +11433,7 @@
         <v>762</v>
       </c>
       <c r="L240" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="241" spans="1:12">
@@ -11443,20 +11443,20 @@
       <c r="B241" t="s">
         <v>13</v>
       </c>
+      <c r="C241" t="s">
+        <v>764</v>
+      </c>
       <c r="D241" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="E241" t="s">
+        <v>32</v>
+      </c>
+      <c r="F241" t="s">
         <v>765</v>
       </c>
-      <c r="F241" t="s">
-        <v>16</v>
-      </c>
       <c r="G241" t="s">
-        <v>705</v>
-      </c>
-      <c r="H241" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I241" t="s">
         <v>16</v>
@@ -11468,7 +11468,7 @@
         <v>766</v>
       </c>
       <c r="L241" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="242" spans="1:12">
@@ -11478,20 +11478,20 @@
       <c r="B242" t="s">
         <v>13</v>
       </c>
+      <c r="C242" t="s">
+        <v>764</v>
+      </c>
       <c r="D242" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="E242" t="s">
+        <v>32</v>
+      </c>
+      <c r="F242" t="s">
         <v>768</v>
       </c>
-      <c r="F242" t="s">
-        <v>16</v>
-      </c>
       <c r="G242" t="s">
-        <v>705</v>
-      </c>
-      <c r="H242" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I242" t="s">
         <v>16</v>
@@ -11503,7 +11503,7 @@
         <v>769</v>
       </c>
       <c r="L242" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -11513,20 +11513,20 @@
       <c r="B243" t="s">
         <v>13</v>
       </c>
+      <c r="C243" t="s">
+        <v>764</v>
+      </c>
       <c r="D243" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="E243" t="s">
+        <v>32</v>
+      </c>
+      <c r="F243" t="s">
         <v>771</v>
       </c>
-      <c r="F243" t="s">
-        <v>16</v>
-      </c>
       <c r="G243" t="s">
-        <v>705</v>
-      </c>
-      <c r="H243" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I243" t="s">
         <v>16</v>
@@ -11538,7 +11538,7 @@
         <v>772</v>
       </c>
       <c r="L243" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="244" spans="1:12">
@@ -11548,20 +11548,20 @@
       <c r="B244" t="s">
         <v>13</v>
       </c>
+      <c r="C244" t="s">
+        <v>764</v>
+      </c>
       <c r="D244" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="E244" t="s">
+        <v>32</v>
+      </c>
+      <c r="F244" t="s">
         <v>774</v>
       </c>
-      <c r="F244" t="s">
-        <v>16</v>
-      </c>
       <c r="G244" t="s">
-        <v>705</v>
-      </c>
-      <c r="H244" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I244" t="s">
         <v>16</v>
@@ -11573,7 +11573,7 @@
         <v>775</v>
       </c>
       <c r="L244" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="245" spans="1:12">
@@ -11583,19 +11583,19 @@
       <c r="B245" t="s">
         <v>13</v>
       </c>
+      <c r="C245" t="s">
+        <v>764</v>
+      </c>
       <c r="D245" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="E245" t="s">
+        <v>16</v>
+      </c>
+      <c r="F245" t="s">
         <v>777</v>
       </c>
-      <c r="F245" t="s">
-        <v>16</v>
-      </c>
       <c r="G245" t="s">
-        <v>705</v>
-      </c>
-      <c r="H245" t="s">
         <v>16</v>
       </c>
       <c r="I245" t="s">
@@ -11608,7 +11608,7 @@
         <v>778</v>
       </c>
       <c r="L245" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="246" spans="1:12">
@@ -11618,20 +11618,20 @@
       <c r="B246" t="s">
         <v>13</v>
       </c>
+      <c r="C246" t="s">
+        <v>764</v>
+      </c>
       <c r="D246" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="E246" t="s">
+        <v>32</v>
+      </c>
+      <c r="F246" t="s">
         <v>780</v>
       </c>
-      <c r="F246" t="s">
-        <v>16</v>
-      </c>
       <c r="G246" t="s">
-        <v>705</v>
-      </c>
-      <c r="H246" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I246" t="s">
         <v>16</v>
@@ -11643,7 +11643,7 @@
         <v>781</v>
       </c>
       <c r="L246" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -11653,19 +11653,19 @@
       <c r="B247" t="s">
         <v>13</v>
       </c>
+      <c r="C247" t="s">
+        <v>764</v>
+      </c>
       <c r="D247" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="E247" t="s">
+        <v>16</v>
+      </c>
+      <c r="F247" t="s">
         <v>783</v>
       </c>
-      <c r="F247" t="s">
-        <v>16</v>
-      </c>
       <c r="G247" t="s">
-        <v>705</v>
-      </c>
-      <c r="H247" t="s">
         <v>16</v>
       </c>
       <c r="I247" t="s">
@@ -11678,7 +11678,7 @@
         <v>784</v>
       </c>
       <c r="L247" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="248" spans="1:12">
@@ -11688,20 +11688,20 @@
       <c r="B248" t="s">
         <v>13</v>
       </c>
+      <c r="C248" t="s">
+        <v>764</v>
+      </c>
       <c r="D248" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="E248" t="s">
+        <v>32</v>
+      </c>
+      <c r="F248" t="s">
         <v>786</v>
       </c>
-      <c r="F248" t="s">
-        <v>16</v>
-      </c>
       <c r="G248" t="s">
-        <v>705</v>
-      </c>
-      <c r="H248" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I248" t="s">
         <v>16</v>
@@ -11713,7 +11713,7 @@
         <v>787</v>
       </c>
       <c r="L248" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="249" spans="1:12">
@@ -11723,23 +11723,23 @@
       <c r="B249" t="s">
         <v>13</v>
       </c>
+      <c r="C249" t="s">
+        <v>764</v>
+      </c>
       <c r="D249" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="E249" t="s">
+        <v>32</v>
+      </c>
+      <c r="F249" t="s">
         <v>789</v>
       </c>
-      <c r="F249" t="s">
-        <v>32</v>
-      </c>
       <c r="G249" t="s">
-        <v>705</v>
-      </c>
-      <c r="H249" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I249" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J249" t="s">
         <v>18</v>
@@ -11748,7 +11748,7 @@
         <v>790</v>
       </c>
       <c r="L249" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -11758,19 +11758,19 @@
       <c r="B250" t="s">
         <v>13</v>
       </c>
+      <c r="C250" t="s">
+        <v>764</v>
+      </c>
       <c r="D250" t="s">
-        <v>764</v>
+        <v>15</v>
       </c>
       <c r="E250" t="s">
+        <v>16</v>
+      </c>
+      <c r="F250" t="s">
         <v>792</v>
       </c>
-      <c r="F250" t="s">
-        <v>16</v>
-      </c>
       <c r="G250" t="s">
-        <v>705</v>
-      </c>
-      <c r="H250" t="s">
         <v>16</v>
       </c>
       <c r="I250" t="s">
@@ -11783,7 +11783,7 @@
         <v>793</v>
       </c>
       <c r="L250" t="s">
-        <v>20</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/clv3/xlsx/pt/RegionM49.xlsx
+++ b/api/2/clv3/xlsx/pt/RegionM49.xlsx
@@ -25,33 +25,33 @@
     <t>codeforiati:sub-region-code</t>
   </si>
   <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:intermediate-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
     <t>codeforiati:least-developed-countries</t>
   </si>
   <si>
+    <t>codeforiati:iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
     <t>codeforiati:land-locked-developing-countries</t>
   </si>
   <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
     <t>codeforiati:small-island-developing-states</t>
   </si>
   <si>
     <t>codeforiati:developed-developing</t>
   </si>
   <si>
-    <t>codeforiati:intermediate-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
@@ -61,24 +61,24 @@
     <t>015</t>
   </si>
   <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>DZ</t>
+    <t>DZA</t>
   </si>
   <si>
     <t>001</t>
   </si>
   <si>
-    <t>DZA</t>
-  </si>
-  <si>
     <t>Developing</t>
   </si>
   <si>
-    <t>002</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>729</t>
   </si>
   <si>
+    <t>SD</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
     <t>SDN</t>
   </si>
   <si>
@@ -142,15 +142,15 @@
     <t>202</t>
   </si>
   <si>
+    <t>014</t>
+  </si>
+  <si>
     <t>IO</t>
   </si>
   <si>
     <t>IOT</t>
   </si>
   <si>
-    <t>014</t>
-  </si>
-  <si>
     <t>108</t>
   </si>
   <si>
@@ -343,15 +343,15 @@
     <t>024</t>
   </si>
   <si>
+    <t>017</t>
+  </si>
+  <si>
     <t>AO</t>
   </si>
   <si>
     <t>AGO</t>
   </si>
   <si>
-    <t>017</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -427,15 +427,15 @@
     <t>072</t>
   </si>
   <si>
+    <t>018</t>
+  </si>
+  <si>
     <t>BW</t>
   </si>
   <si>
     <t>BWA</t>
   </si>
   <si>
-    <t>018</t>
-  </si>
-  <si>
     <t>748</t>
   </si>
   <si>
@@ -475,15 +475,15 @@
     <t>204</t>
   </si>
   <si>
+    <t>011</t>
+  </si>
+  <si>
     <t>BJ</t>
   </si>
   <si>
     <t>BEN</t>
   </si>
   <si>
-    <t>011</t>
-  </si>
-  <si>
     <t>854</t>
   </si>
   <si>
@@ -634,18 +634,18 @@
     <t>419</t>
   </si>
   <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
     <t>AI</t>
   </si>
   <si>
     <t>AIA</t>
   </si>
   <si>
-    <t>029</t>
-  </si>
-  <si>
-    <t>019</t>
-  </si>
-  <si>
     <t>028</t>
   </si>
   <si>
@@ -892,15 +892,15 @@
     <t>084</t>
   </si>
   <si>
+    <t>013</t>
+  </si>
+  <si>
     <t>BZ</t>
   </si>
   <si>
     <t>BLZ</t>
   </si>
   <si>
-    <t>013</t>
-  </si>
-  <si>
     <t>188</t>
   </si>
   <si>
@@ -967,15 +967,15 @@
     <t>032</t>
   </si>
   <si>
+    <t>005</t>
+  </si>
+  <si>
     <t>AR</t>
   </si>
   <si>
     <t>ARG</t>
   </si>
   <si>
-    <t>005</t>
-  </si>
-  <si>
     <t>068</t>
   </si>
   <si>
@@ -1177,15 +1177,15 @@
     <t>143</t>
   </si>
   <si>
+    <t>142</t>
+  </si>
+  <si>
     <t>KZ</t>
   </si>
   <si>
     <t>KAZ</t>
   </si>
   <si>
-    <t>142</t>
-  </si>
-  <si>
     <t>417</t>
   </si>
   <si>
@@ -1645,15 +1645,15 @@
     <t>151</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>BY</t>
   </si>
   <si>
     <t>BLR</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -2128,13 +2128,13 @@
     <t>053</t>
   </si>
   <si>
+    <t>009</t>
+  </si>
+  <si>
     <t>AU</t>
   </si>
   <si>
     <t>AUS</t>
-  </si>
-  <si>
-    <t>009</t>
   </si>
   <si>
     <t>162</t>
@@ -2781,9 +2781,6 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
@@ -2794,10 +2791,13 @@
         <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -2816,9 +2816,6 @@
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
       <c r="F3" t="s">
         <v>22</v>
       </c>
@@ -2829,10 +2826,13 @@
         <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
       </c>
       <c r="L3" t="s">
         <v>20</v>
@@ -2851,9 +2851,6 @@
       <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
       <c r="F4" t="s">
         <v>25</v>
       </c>
@@ -2864,10 +2861,13 @@
         <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
       </c>
       <c r="L4" t="s">
         <v>20</v>
@@ -2886,9 +2886,6 @@
       <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" t="s">
         <v>28</v>
       </c>
@@ -2899,10 +2896,13 @@
         <v>29</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
       </c>
       <c r="L5" t="s">
         <v>20</v>
@@ -2919,25 +2919,25 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
       </c>
       <c r="L6" t="s">
         <v>20</v>
@@ -2956,9 +2956,6 @@
       <c r="D7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
       <c r="F7" t="s">
         <v>35</v>
       </c>
@@ -2969,10 +2966,13 @@
         <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K7" t="s">
+        <v>17</v>
       </c>
       <c r="L7" t="s">
         <v>20</v>
@@ -2991,9 +2991,6 @@
       <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
       <c r="F8" t="s">
         <v>38</v>
       </c>
@@ -3004,10 +3001,13 @@
         <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
       </c>
       <c r="L8" t="s">
         <v>20</v>
@@ -3027,25 +3027,25 @@
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L9" t="s">
         <v>20</v>
@@ -3062,28 +3062,28 @@
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
         <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
         <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K10" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L10" t="s">
         <v>20</v>
@@ -3100,28 +3100,28 @@
         <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
         <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
         <v>50</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L11" t="s">
         <v>20</v>
@@ -3138,28 +3138,28 @@
         <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
         <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H12" t="s">
         <v>53</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L12" t="s">
         <v>20</v>
@@ -3176,28 +3176,28 @@
         <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s">
         <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H13" t="s">
         <v>56</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K13" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L13" t="s">
         <v>20</v>
@@ -3214,28 +3214,28 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
         <v>58</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H14" t="s">
         <v>59</v>
       </c>
       <c r="I14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K14" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L14" t="s">
         <v>20</v>
@@ -3255,7 +3255,7 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
         <v>61</v>
@@ -3267,13 +3267,13 @@
         <v>62</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K15" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L15" t="s">
         <v>20</v>
@@ -3293,7 +3293,7 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
         <v>64</v>
@@ -3305,13 +3305,13 @@
         <v>65</v>
       </c>
       <c r="I16" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K16" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L16" t="s">
         <v>20</v>
@@ -3328,28 +3328,28 @@
         <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
         <v>67</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H17" t="s">
         <v>68</v>
       </c>
       <c r="I17" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K17" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L17" t="s">
         <v>20</v>
@@ -3366,28 +3366,28 @@
         <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
         <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H18" t="s">
         <v>71</v>
       </c>
       <c r="I18" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K18" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L18" t="s">
         <v>20</v>
@@ -3407,7 +3407,7 @@
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
         <v>73</v>
@@ -3419,13 +3419,13 @@
         <v>74</v>
       </c>
       <c r="I19" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L19" t="s">
         <v>20</v>
@@ -3445,7 +3445,7 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
         <v>76</v>
@@ -3457,13 +3457,13 @@
         <v>77</v>
       </c>
       <c r="I20" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L20" t="s">
         <v>20</v>
@@ -3480,28 +3480,28 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s">
         <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H21" t="s">
         <v>80</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L21" t="s">
         <v>20</v>
@@ -3521,7 +3521,7 @@
         <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
         <v>82</v>
@@ -3533,13 +3533,13 @@
         <v>83</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K22" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
@@ -3556,28 +3556,28 @@
         <v>41</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
         <v>85</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H23" t="s">
         <v>86</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K23" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L23" t="s">
         <v>20</v>
@@ -3597,7 +3597,7 @@
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s">
         <v>88</v>
@@ -3609,13 +3609,13 @@
         <v>89</v>
       </c>
       <c r="I24" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L24" t="s">
         <v>20</v>
@@ -3632,28 +3632,28 @@
         <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
         <v>91</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H25" t="s">
         <v>92</v>
       </c>
       <c r="I25" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K25" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L25" t="s">
         <v>20</v>
@@ -3670,28 +3670,28 @@
         <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
         <v>94</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H26" t="s">
         <v>95</v>
       </c>
       <c r="I26" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K26" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L26" t="s">
         <v>20</v>
@@ -3708,28 +3708,28 @@
         <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F27" t="s">
         <v>97</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H27" t="s">
         <v>98</v>
       </c>
       <c r="I27" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K27" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L27" t="s">
         <v>20</v>
@@ -3746,28 +3746,28 @@
         <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F28" t="s">
         <v>100</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H28" t="s">
         <v>101</v>
       </c>
       <c r="I28" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L28" t="s">
         <v>20</v>
@@ -3784,28 +3784,28 @@
         <v>41</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F29" t="s">
         <v>103</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H29" t="s">
         <v>104</v>
       </c>
       <c r="I29" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J29" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K29" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L29" t="s">
         <v>20</v>
@@ -3825,7 +3825,7 @@
         <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F30" t="s">
         <v>106</v>
@@ -3837,13 +3837,13 @@
         <v>107</v>
       </c>
       <c r="I30" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K30" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L30" t="s">
         <v>20</v>
@@ -3860,28 +3860,28 @@
         <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="F31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="L31" t="s">
         <v>20</v>
@@ -3901,7 +3901,7 @@
         <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="F32" t="s">
         <v>113</v>
@@ -3913,13 +3913,13 @@
         <v>114</v>
       </c>
       <c r="I32" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K32" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="L32" t="s">
         <v>20</v>
@@ -3936,28 +3936,28 @@
         <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="F33" t="s">
         <v>116</v>
       </c>
       <c r="G33" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H33" t="s">
         <v>117</v>
       </c>
       <c r="I33" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J33" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K33" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="L33" t="s">
         <v>20</v>
@@ -3974,28 +3974,28 @@
         <v>41</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="F34" t="s">
         <v>119</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H34" t="s">
         <v>120</v>
       </c>
       <c r="I34" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K34" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="L34" t="s">
         <v>20</v>
@@ -4015,7 +4015,7 @@
         <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="F35" t="s">
         <v>122</v>
@@ -4027,13 +4027,13 @@
         <v>123</v>
       </c>
       <c r="I35" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K35" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="L35" t="s">
         <v>20</v>
@@ -4050,28 +4050,28 @@
         <v>41</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="F36" t="s">
         <v>125</v>
       </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H36" t="s">
         <v>126</v>
       </c>
       <c r="I36" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J36" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K36" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="L36" t="s">
         <v>20</v>
@@ -4091,7 +4091,7 @@
         <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="F37" t="s">
         <v>128</v>
@@ -4103,13 +4103,13 @@
         <v>129</v>
       </c>
       <c r="I37" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K37" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="L37" t="s">
         <v>20</v>
@@ -4129,7 +4129,7 @@
         <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="F38" t="s">
         <v>131</v>
@@ -4141,13 +4141,13 @@
         <v>132</v>
       </c>
       <c r="I38" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K38" t="s">
-        <v>111</v>
+        <v>17</v>
       </c>
       <c r="L38" t="s">
         <v>20</v>
@@ -4164,28 +4164,28 @@
         <v>41</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="F39" t="s">
         <v>134</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H39" t="s">
         <v>135</v>
       </c>
       <c r="I39" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="L39" t="s">
         <v>20</v>
@@ -4205,25 +4205,25 @@
         <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="F40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G40" t="s">
         <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I40" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K40" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="L40" t="s">
         <v>20</v>
@@ -4243,7 +4243,7 @@
         <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="F41" t="s">
         <v>141</v>
@@ -4255,13 +4255,13 @@
         <v>142</v>
       </c>
       <c r="I41" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K41" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="L41" t="s">
         <v>20</v>
@@ -4278,28 +4278,28 @@
         <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="F42" t="s">
         <v>144</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H42" t="s">
         <v>145</v>
       </c>
       <c r="I42" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J42" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K42" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="L42" t="s">
         <v>20</v>
@@ -4319,7 +4319,7 @@
         <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="F43" t="s">
         <v>147</v>
@@ -4331,13 +4331,13 @@
         <v>148</v>
       </c>
       <c r="I43" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K43" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="L43" t="s">
         <v>20</v>
@@ -4357,7 +4357,7 @@
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="F44" t="s">
         <v>150</v>
@@ -4369,13 +4369,13 @@
         <v>151</v>
       </c>
       <c r="I44" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K44" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="L44" t="s">
         <v>20</v>
@@ -4392,28 +4392,28 @@
         <v>41</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E45" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I45" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L45" t="s">
         <v>20</v>
@@ -4430,28 +4430,28 @@
         <v>41</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="F46" t="s">
         <v>157</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H46" t="s">
         <v>158</v>
       </c>
       <c r="I46" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J46" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K46" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L46" t="s">
         <v>20</v>
@@ -4471,7 +4471,7 @@
         <v>15</v>
       </c>
       <c r="E47" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F47" t="s">
         <v>160</v>
@@ -4483,13 +4483,13 @@
         <v>161</v>
       </c>
       <c r="I47" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J47" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K47" t="s">
-        <v>155</v>
+        <v>32</v>
       </c>
       <c r="L47" t="s">
         <v>20</v>
@@ -4509,7 +4509,7 @@
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F48" t="s">
         <v>163</v>
@@ -4521,13 +4521,13 @@
         <v>164</v>
       </c>
       <c r="I48" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K48" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L48" t="s">
         <v>20</v>
@@ -4544,28 +4544,28 @@
         <v>41</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F49" t="s">
         <v>166</v>
       </c>
       <c r="G49" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H49" t="s">
         <v>167</v>
       </c>
       <c r="I49" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K49" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L49" t="s">
         <v>20</v>
@@ -4585,7 +4585,7 @@
         <v>15</v>
       </c>
       <c r="E50" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F50" t="s">
         <v>169</v>
@@ -4597,13 +4597,13 @@
         <v>170</v>
       </c>
       <c r="I50" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J50" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K50" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L50" t="s">
         <v>20</v>
@@ -4620,28 +4620,28 @@
         <v>41</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F51" t="s">
         <v>172</v>
       </c>
       <c r="G51" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H51" t="s">
         <v>173</v>
       </c>
       <c r="I51" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J51" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K51" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L51" t="s">
         <v>20</v>
@@ -4658,28 +4658,28 @@
         <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E52" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F52" t="s">
         <v>175</v>
       </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H52" t="s">
         <v>176</v>
       </c>
       <c r="I52" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J52" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K52" t="s">
-        <v>155</v>
+        <v>32</v>
       </c>
       <c r="L52" t="s">
         <v>20</v>
@@ -4696,28 +4696,28 @@
         <v>41</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E53" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F53" t="s">
         <v>178</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H53" t="s">
         <v>179</v>
       </c>
       <c r="I53" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K53" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L53" t="s">
         <v>20</v>
@@ -4734,28 +4734,28 @@
         <v>41</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="F54" t="s">
         <v>181</v>
       </c>
       <c r="G54" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H54" t="s">
         <v>182</v>
       </c>
       <c r="I54" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J54" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K54" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L54" t="s">
         <v>20</v>
@@ -4772,28 +4772,28 @@
         <v>41</v>
       </c>
       <c r="D55" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E55" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F55" t="s">
         <v>184</v>
       </c>
       <c r="G55" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H55" t="s">
         <v>185</v>
       </c>
       <c r="I55" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K55" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L55" t="s">
         <v>20</v>
@@ -4810,28 +4810,28 @@
         <v>41</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="F56" t="s">
         <v>187</v>
       </c>
       <c r="G56" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H56" t="s">
         <v>188</v>
       </c>
       <c r="I56" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J56" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K56" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L56" t="s">
         <v>20</v>
@@ -4851,7 +4851,7 @@
         <v>15</v>
       </c>
       <c r="E57" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F57" t="s">
         <v>190</v>
@@ -4863,13 +4863,13 @@
         <v>191</v>
       </c>
       <c r="I57" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J57" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K57" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L57" t="s">
         <v>20</v>
@@ -4889,7 +4889,7 @@
         <v>15</v>
       </c>
       <c r="E58" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F58" t="s">
         <v>193</v>
@@ -4901,13 +4901,13 @@
         <v>194</v>
       </c>
       <c r="I58" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K58" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L58" t="s">
         <v>20</v>
@@ -4924,28 +4924,28 @@
         <v>41</v>
       </c>
       <c r="D59" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E59" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F59" t="s">
         <v>196</v>
       </c>
       <c r="G59" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H59" t="s">
         <v>197</v>
       </c>
       <c r="I59" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J59" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K59" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L59" t="s">
         <v>20</v>
@@ -4962,28 +4962,28 @@
         <v>41</v>
       </c>
       <c r="D60" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E60" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F60" t="s">
         <v>199</v>
       </c>
       <c r="G60" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H60" t="s">
         <v>200</v>
       </c>
       <c r="I60" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K60" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L60" t="s">
         <v>20</v>
@@ -5000,28 +5000,28 @@
         <v>41</v>
       </c>
       <c r="D61" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>15</v>
+        <v>153</v>
       </c>
       <c r="F61" t="s">
         <v>202</v>
       </c>
       <c r="G61" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H61" t="s">
         <v>203</v>
       </c>
       <c r="I61" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J61" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K61" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="L61" t="s">
         <v>20</v>
@@ -5038,31 +5038,31 @@
         <v>205</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E62" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F62" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G62" t="s">
         <v>17</v>
       </c>
       <c r="H62" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I62" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J62" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K62" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L62" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -5076,10 +5076,10 @@
         <v>205</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E63" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F63" t="s">
         <v>211</v>
@@ -5091,16 +5091,16 @@
         <v>212</v>
       </c>
       <c r="I63" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J63" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K63" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L63" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -5114,10 +5114,10 @@
         <v>205</v>
       </c>
       <c r="D64" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E64" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F64" t="s">
         <v>214</v>
@@ -5129,16 +5129,16 @@
         <v>215</v>
       </c>
       <c r="I64" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K64" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L64" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -5152,10 +5152,10 @@
         <v>205</v>
       </c>
       <c r="D65" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E65" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F65" t="s">
         <v>217</v>
@@ -5167,16 +5167,16 @@
         <v>218</v>
       </c>
       <c r="I65" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J65" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K65" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L65" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -5190,10 +5190,10 @@
         <v>205</v>
       </c>
       <c r="D66" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E66" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F66" t="s">
         <v>220</v>
@@ -5205,16 +5205,16 @@
         <v>221</v>
       </c>
       <c r="I66" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K66" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L66" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -5228,10 +5228,10 @@
         <v>205</v>
       </c>
       <c r="D67" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E67" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F67" t="s">
         <v>223</v>
@@ -5243,16 +5243,16 @@
         <v>224</v>
       </c>
       <c r="I67" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K67" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L67" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -5266,10 +5266,10 @@
         <v>205</v>
       </c>
       <c r="D68" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E68" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F68" t="s">
         <v>226</v>
@@ -5281,16 +5281,16 @@
         <v>227</v>
       </c>
       <c r="I68" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K68" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L68" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -5304,10 +5304,10 @@
         <v>205</v>
       </c>
       <c r="D69" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E69" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F69" t="s">
         <v>229</v>
@@ -5319,16 +5319,16 @@
         <v>230</v>
       </c>
       <c r="I69" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J69" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K69" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="L69" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -5342,10 +5342,10 @@
         <v>205</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E70" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F70" t="s">
         <v>232</v>
@@ -5357,16 +5357,16 @@
         <v>233</v>
       </c>
       <c r="I70" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J70" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K70" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L70" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -5380,10 +5380,10 @@
         <v>205</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E71" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F71" t="s">
         <v>235</v>
@@ -5395,16 +5395,16 @@
         <v>236</v>
       </c>
       <c r="I71" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J71" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K71" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L71" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -5418,10 +5418,10 @@
         <v>205</v>
       </c>
       <c r="D72" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E72" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F72" t="s">
         <v>238</v>
@@ -5433,16 +5433,16 @@
         <v>239</v>
       </c>
       <c r="I72" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J72" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K72" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L72" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -5456,10 +5456,10 @@
         <v>205</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E73" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F73" t="s">
         <v>241</v>
@@ -5471,16 +5471,16 @@
         <v>242</v>
       </c>
       <c r="I73" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J73" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K73" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L73" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -5494,10 +5494,10 @@
         <v>205</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E74" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F74" t="s">
         <v>244</v>
@@ -5509,16 +5509,16 @@
         <v>245</v>
       </c>
       <c r="I74" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J74" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K74" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L74" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -5532,10 +5532,10 @@
         <v>205</v>
       </c>
       <c r="D75" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E75" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F75" t="s">
         <v>247</v>
@@ -5547,16 +5547,16 @@
         <v>248</v>
       </c>
       <c r="I75" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J75" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K75" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="L75" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -5570,31 +5570,31 @@
         <v>205</v>
       </c>
       <c r="D76" t="s">
-        <v>31</v>
+        <v>206</v>
       </c>
       <c r="E76" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F76" t="s">
         <v>250</v>
       </c>
       <c r="G76" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H76" t="s">
         <v>251</v>
       </c>
       <c r="I76" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J76" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K76" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L76" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -5608,10 +5608,10 @@
         <v>205</v>
       </c>
       <c r="D77" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E77" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F77" t="s">
         <v>253</v>
@@ -5623,16 +5623,16 @@
         <v>254</v>
       </c>
       <c r="I77" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J77" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K77" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L77" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -5646,10 +5646,10 @@
         <v>205</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E78" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F78" t="s">
         <v>256</v>
@@ -5661,16 +5661,16 @@
         <v>257</v>
       </c>
       <c r="I78" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J78" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K78" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="L78" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -5684,10 +5684,10 @@
         <v>205</v>
       </c>
       <c r="D79" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E79" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F79" t="s">
         <v>259</v>
@@ -5699,16 +5699,16 @@
         <v>260</v>
       </c>
       <c r="I79" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J79" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K79" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L79" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -5722,10 +5722,10 @@
         <v>205</v>
       </c>
       <c r="D80" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E80" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F80" t="s">
         <v>262</v>
@@ -5737,16 +5737,16 @@
         <v>263</v>
       </c>
       <c r="I80" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J80" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K80" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L80" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -5760,10 +5760,10 @@
         <v>205</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E81" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F81" t="s">
         <v>265</v>
@@ -5775,16 +5775,16 @@
         <v>266</v>
       </c>
       <c r="I81" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J81" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K81" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="L81" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -5798,10 +5798,10 @@
         <v>205</v>
       </c>
       <c r="D82" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E82" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F82" t="s">
         <v>268</v>
@@ -5813,16 +5813,16 @@
         <v>269</v>
       </c>
       <c r="I82" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J82" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K82" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L82" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -5836,10 +5836,10 @@
         <v>205</v>
       </c>
       <c r="D83" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E83" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F83" t="s">
         <v>271</v>
@@ -5851,16 +5851,16 @@
         <v>272</v>
       </c>
       <c r="I83" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J83" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K83" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L83" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -5874,10 +5874,10 @@
         <v>205</v>
       </c>
       <c r="D84" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E84" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F84" t="s">
         <v>274</v>
@@ -5889,16 +5889,16 @@
         <v>275</v>
       </c>
       <c r="I84" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J84" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K84" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="L84" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -5912,10 +5912,10 @@
         <v>205</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E85" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F85" t="s">
         <v>277</v>
@@ -5927,16 +5927,16 @@
         <v>278</v>
       </c>
       <c r="I85" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J85" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K85" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L85" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -5950,10 +5950,10 @@
         <v>205</v>
       </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E86" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F86" t="s">
         <v>280</v>
@@ -5965,16 +5965,16 @@
         <v>281</v>
       </c>
       <c r="I86" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J86" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K86" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L86" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -5988,10 +5988,10 @@
         <v>205</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E87" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F87" t="s">
         <v>283</v>
@@ -6003,16 +6003,16 @@
         <v>284</v>
       </c>
       <c r="I87" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J87" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K87" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L87" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -6026,10 +6026,10 @@
         <v>205</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E88" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F88" t="s">
         <v>286</v>
@@ -6041,16 +6041,16 @@
         <v>287</v>
       </c>
       <c r="I88" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J88" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K88" t="s">
-        <v>208</v>
+        <v>17</v>
       </c>
       <c r="L88" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -6064,10 +6064,10 @@
         <v>205</v>
       </c>
       <c r="D89" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E89" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="F89" t="s">
         <v>289</v>
@@ -6079,16 +6079,16 @@
         <v>290</v>
       </c>
       <c r="I89" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J89" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K89" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="L89" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -6102,31 +6102,31 @@
         <v>205</v>
       </c>
       <c r="D90" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E90" t="s">
-        <v>15</v>
+        <v>292</v>
       </c>
       <c r="F90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G90" t="s">
         <v>17</v>
       </c>
       <c r="H90" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I90" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J90" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K90" t="s">
-        <v>294</v>
+        <v>32</v>
       </c>
       <c r="L90" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -6140,10 +6140,10 @@
         <v>205</v>
       </c>
       <c r="D91" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E91" t="s">
-        <v>15</v>
+        <v>292</v>
       </c>
       <c r="F91" t="s">
         <v>296</v>
@@ -6155,16 +6155,16 @@
         <v>297</v>
       </c>
       <c r="I91" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J91" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K91" t="s">
-        <v>294</v>
+        <v>17</v>
       </c>
       <c r="L91" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -6178,10 +6178,10 @@
         <v>205</v>
       </c>
       <c r="D92" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E92" t="s">
-        <v>15</v>
+        <v>292</v>
       </c>
       <c r="F92" t="s">
         <v>299</v>
@@ -6193,16 +6193,16 @@
         <v>300</v>
       </c>
       <c r="I92" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J92" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K92" t="s">
-        <v>294</v>
+        <v>17</v>
       </c>
       <c r="L92" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -6216,10 +6216,10 @@
         <v>205</v>
       </c>
       <c r="D93" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E93" t="s">
-        <v>15</v>
+        <v>292</v>
       </c>
       <c r="F93" t="s">
         <v>302</v>
@@ -6231,16 +6231,16 @@
         <v>303</v>
       </c>
       <c r="I93" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J93" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K93" t="s">
-        <v>294</v>
+        <v>17</v>
       </c>
       <c r="L93" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -6254,10 +6254,10 @@
         <v>205</v>
       </c>
       <c r="D94" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E94" t="s">
-        <v>15</v>
+        <v>292</v>
       </c>
       <c r="F94" t="s">
         <v>305</v>
@@ -6269,16 +6269,16 @@
         <v>306</v>
       </c>
       <c r="I94" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K94" t="s">
-        <v>294</v>
+        <v>17</v>
       </c>
       <c r="L94" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -6292,10 +6292,10 @@
         <v>205</v>
       </c>
       <c r="D95" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E95" t="s">
-        <v>15</v>
+        <v>292</v>
       </c>
       <c r="F95" t="s">
         <v>308</v>
@@ -6307,16 +6307,16 @@
         <v>309</v>
       </c>
       <c r="I95" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J95" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K95" t="s">
-        <v>294</v>
+        <v>17</v>
       </c>
       <c r="L95" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -6330,10 +6330,10 @@
         <v>205</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E96" t="s">
-        <v>15</v>
+        <v>292</v>
       </c>
       <c r="F96" t="s">
         <v>311</v>
@@ -6345,16 +6345,16 @@
         <v>312</v>
       </c>
       <c r="I96" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J96" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K96" t="s">
-        <v>294</v>
+        <v>17</v>
       </c>
       <c r="L96" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -6368,10 +6368,10 @@
         <v>205</v>
       </c>
       <c r="D97" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E97" t="s">
-        <v>15</v>
+        <v>292</v>
       </c>
       <c r="F97" t="s">
         <v>314</v>
@@ -6383,16 +6383,16 @@
         <v>315</v>
       </c>
       <c r="I97" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J97" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K97" t="s">
-        <v>294</v>
+        <v>17</v>
       </c>
       <c r="L97" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -6406,31 +6406,31 @@
         <v>205</v>
       </c>
       <c r="D98" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E98" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F98" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G98" t="s">
         <v>17</v>
       </c>
       <c r="H98" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I98" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J98" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K98" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L98" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -6444,10 +6444,10 @@
         <v>205</v>
       </c>
       <c r="D99" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E99" t="s">
-        <v>31</v>
+        <v>317</v>
       </c>
       <c r="F99" t="s">
         <v>321</v>
@@ -6459,16 +6459,16 @@
         <v>322</v>
       </c>
       <c r="I99" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J99" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K99" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L99" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -6482,10 +6482,10 @@
         <v>205</v>
       </c>
       <c r="D100" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E100" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F100" t="s">
         <v>324</v>
@@ -6497,16 +6497,16 @@
         <v>325</v>
       </c>
       <c r="I100" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J100" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K100" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L100" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -6520,10 +6520,10 @@
         <v>205</v>
       </c>
       <c r="D101" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E101" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F101" t="s">
         <v>327</v>
@@ -6535,16 +6535,16 @@
         <v>328</v>
       </c>
       <c r="I101" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J101" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K101" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L101" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -6558,10 +6558,10 @@
         <v>205</v>
       </c>
       <c r="D102" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E102" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F102" t="s">
         <v>330</v>
@@ -6573,16 +6573,16 @@
         <v>331</v>
       </c>
       <c r="I102" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J102" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K102" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L102" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -6596,10 +6596,10 @@
         <v>205</v>
       </c>
       <c r="D103" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E103" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F103" t="s">
         <v>333</v>
@@ -6611,16 +6611,16 @@
         <v>334</v>
       </c>
       <c r="I103" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J103" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K103" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L103" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -6634,10 +6634,10 @@
         <v>205</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E104" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F104" t="s">
         <v>336</v>
@@ -6649,16 +6649,16 @@
         <v>337</v>
       </c>
       <c r="I104" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J104" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K104" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L104" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -6672,10 +6672,10 @@
         <v>205</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E105" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F105" t="s">
         <v>339</v>
@@ -6687,16 +6687,16 @@
         <v>340</v>
       </c>
       <c r="I105" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J105" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K105" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L105" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -6710,10 +6710,10 @@
         <v>205</v>
       </c>
       <c r="D106" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E106" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F106" t="s">
         <v>342</v>
@@ -6725,16 +6725,16 @@
         <v>343</v>
       </c>
       <c r="I106" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J106" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K106" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L106" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -6748,10 +6748,10 @@
         <v>205</v>
       </c>
       <c r="D107" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E107" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F107" t="s">
         <v>345</v>
@@ -6763,16 +6763,16 @@
         <v>346</v>
       </c>
       <c r="I107" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J107" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K107" t="s">
-        <v>319</v>
+        <v>32</v>
       </c>
       <c r="L107" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -6786,10 +6786,10 @@
         <v>205</v>
       </c>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E108" t="s">
-        <v>31</v>
+        <v>317</v>
       </c>
       <c r="F108" t="s">
         <v>348</v>
@@ -6801,16 +6801,16 @@
         <v>349</v>
       </c>
       <c r="I108" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J108" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K108" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L108" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -6824,10 +6824,10 @@
         <v>205</v>
       </c>
       <c r="D109" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E109" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F109" t="s">
         <v>351</v>
@@ -6839,16 +6839,16 @@
         <v>352</v>
       </c>
       <c r="I109" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J109" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K109" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L109" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -6862,10 +6862,10 @@
         <v>205</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E110" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F110" t="s">
         <v>354</v>
@@ -6877,16 +6877,16 @@
         <v>355</v>
       </c>
       <c r="I110" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J110" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K110" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L110" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -6900,10 +6900,10 @@
         <v>205</v>
       </c>
       <c r="D111" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E111" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F111" t="s">
         <v>357</v>
@@ -6915,16 +6915,16 @@
         <v>358</v>
       </c>
       <c r="I111" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J111" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K111" t="s">
-        <v>319</v>
+        <v>32</v>
       </c>
       <c r="L111" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -6938,10 +6938,10 @@
         <v>205</v>
       </c>
       <c r="D112" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E112" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F112" t="s">
         <v>360</v>
@@ -6953,16 +6953,16 @@
         <v>361</v>
       </c>
       <c r="I112" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J112" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K112" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L112" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -6976,10 +6976,10 @@
         <v>205</v>
       </c>
       <c r="D113" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="E113" t="s">
-        <v>15</v>
+        <v>317</v>
       </c>
       <c r="F113" t="s">
         <v>363</v>
@@ -6991,16 +6991,16 @@
         <v>364</v>
       </c>
       <c r="I113" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J113" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K113" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="L113" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -7014,10 +7014,7 @@
         <v>366</v>
       </c>
       <c r="D114" t="s">
-        <v>15</v>
-      </c>
-      <c r="E114" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="F114" t="s">
         <v>367</v>
@@ -7029,13 +7026,16 @@
         <v>368</v>
       </c>
       <c r="I114" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J114" t="s">
+        <v>17</v>
+      </c>
+      <c r="K114" t="s">
+        <v>17</v>
+      </c>
+      <c r="L114" t="s">
         <v>369</v>
-      </c>
-      <c r="L114" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -7049,10 +7049,7 @@
         <v>366</v>
       </c>
       <c r="D115" t="s">
-        <v>15</v>
-      </c>
-      <c r="E115" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="F115" t="s">
         <v>371</v>
@@ -7064,13 +7061,16 @@
         <v>372</v>
       </c>
       <c r="I115" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J115" t="s">
+        <v>17</v>
+      </c>
+      <c r="K115" t="s">
+        <v>17</v>
+      </c>
+      <c r="L115" t="s">
         <v>369</v>
-      </c>
-      <c r="L115" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -7084,10 +7084,7 @@
         <v>366</v>
       </c>
       <c r="D116" t="s">
-        <v>15</v>
-      </c>
-      <c r="E116" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="F116" t="s">
         <v>374</v>
@@ -7099,13 +7096,16 @@
         <v>375</v>
       </c>
       <c r="I116" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J116" t="s">
+        <v>17</v>
+      </c>
+      <c r="K116" t="s">
+        <v>17</v>
+      </c>
+      <c r="L116" t="s">
         <v>369</v>
-      </c>
-      <c r="L116" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -7119,10 +7119,7 @@
         <v>366</v>
       </c>
       <c r="D117" t="s">
-        <v>15</v>
-      </c>
-      <c r="E117" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="F117" t="s">
         <v>377</v>
@@ -7134,13 +7131,16 @@
         <v>378</v>
       </c>
       <c r="I117" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J117" t="s">
+        <v>17</v>
+      </c>
+      <c r="K117" t="s">
+        <v>17</v>
+      </c>
+      <c r="L117" t="s">
         <v>369</v>
-      </c>
-      <c r="L117" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -7154,10 +7154,7 @@
         <v>366</v>
       </c>
       <c r="D118" t="s">
-        <v>15</v>
-      </c>
-      <c r="E118" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="F118" t="s">
         <v>380</v>
@@ -7169,13 +7166,16 @@
         <v>381</v>
       </c>
       <c r="I118" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J118" t="s">
+        <v>17</v>
+      </c>
+      <c r="K118" t="s">
+        <v>17</v>
+      </c>
+      <c r="L118" t="s">
         <v>369</v>
-      </c>
-      <c r="L118" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -7185,12 +7185,6 @@
       <c r="B119" t="s">
         <v>13</v>
       </c>
-      <c r="D119" t="s">
-        <v>15</v>
-      </c>
-      <c r="E119" t="s">
-        <v>15</v>
-      </c>
       <c r="F119" t="s">
         <v>383</v>
       </c>
@@ -7201,7 +7195,13 @@
         <v>384</v>
       </c>
       <c r="I119" t="s">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="J119" t="s">
+        <v>17</v>
+      </c>
+      <c r="K119" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -7215,28 +7215,28 @@
         <v>386</v>
       </c>
       <c r="D120" t="s">
-        <v>15</v>
-      </c>
-      <c r="E120" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F120" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G120" t="s">
         <v>17</v>
       </c>
       <c r="H120" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="I120" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J120" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K120" t="s">
+        <v>17</v>
       </c>
       <c r="L120" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -7250,10 +7250,7 @@
         <v>386</v>
       </c>
       <c r="D121" t="s">
-        <v>15</v>
-      </c>
-      <c r="E121" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F121" t="s">
         <v>391</v>
@@ -7265,13 +7262,16 @@
         <v>392</v>
       </c>
       <c r="I121" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J121" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K121" t="s">
+        <v>17</v>
       </c>
       <c r="L121" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -7285,10 +7285,7 @@
         <v>386</v>
       </c>
       <c r="D122" t="s">
-        <v>15</v>
-      </c>
-      <c r="E122" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F122" t="s">
         <v>394</v>
@@ -7300,13 +7297,16 @@
         <v>395</v>
       </c>
       <c r="I122" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J122" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K122" t="s">
+        <v>17</v>
       </c>
       <c r="L122" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -7320,10 +7320,7 @@
         <v>386</v>
       </c>
       <c r="D123" t="s">
-        <v>15</v>
-      </c>
-      <c r="E123" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F123" t="s">
         <v>397</v>
@@ -7335,13 +7332,16 @@
         <v>398</v>
       </c>
       <c r="I123" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J123" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K123" t="s">
+        <v>17</v>
       </c>
       <c r="L123" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -7355,10 +7355,7 @@
         <v>386</v>
       </c>
       <c r="D124" t="s">
-        <v>15</v>
-      </c>
-      <c r="E124" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F124" t="s">
         <v>400</v>
@@ -7370,13 +7367,16 @@
         <v>401</v>
       </c>
       <c r="I124" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J124" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K124" t="s">
+        <v>17</v>
       </c>
       <c r="L124" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -7390,10 +7390,7 @@
         <v>403</v>
       </c>
       <c r="D125" t="s">
-        <v>15</v>
-      </c>
-      <c r="E125" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F125" t="s">
         <v>404</v>
@@ -7405,13 +7402,16 @@
         <v>405</v>
       </c>
       <c r="I125" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J125" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K125" t="s">
+        <v>17</v>
       </c>
       <c r="L125" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -7425,10 +7425,7 @@
         <v>403</v>
       </c>
       <c r="D126" t="s">
-        <v>15</v>
-      </c>
-      <c r="E126" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F126" t="s">
         <v>407</v>
@@ -7440,13 +7437,16 @@
         <v>408</v>
       </c>
       <c r="I126" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J126" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K126" t="s">
+        <v>17</v>
       </c>
       <c r="L126" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -7460,10 +7460,7 @@
         <v>403</v>
       </c>
       <c r="D127" t="s">
-        <v>15</v>
-      </c>
-      <c r="E127" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F127" t="s">
         <v>410</v>
@@ -7475,13 +7472,16 @@
         <v>411</v>
       </c>
       <c r="I127" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J127" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K127" t="s">
+        <v>17</v>
       </c>
       <c r="L127" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -7495,10 +7495,7 @@
         <v>403</v>
       </c>
       <c r="D128" t="s">
-        <v>15</v>
-      </c>
-      <c r="E128" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F128" t="s">
         <v>413</v>
@@ -7510,13 +7507,16 @@
         <v>414</v>
       </c>
       <c r="I128" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J128" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K128" t="s">
+        <v>17</v>
       </c>
       <c r="L128" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -7530,10 +7530,7 @@
         <v>403</v>
       </c>
       <c r="D129" t="s">
-        <v>15</v>
-      </c>
-      <c r="E129" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F129" t="s">
         <v>416</v>
@@ -7545,13 +7542,16 @@
         <v>417</v>
       </c>
       <c r="I129" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J129" t="s">
+        <v>17</v>
+      </c>
+      <c r="K129" t="s">
+        <v>17</v>
+      </c>
+      <c r="L129" t="s">
         <v>369</v>
-      </c>
-      <c r="L129" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -7565,10 +7565,7 @@
         <v>403</v>
       </c>
       <c r="D130" t="s">
-        <v>15</v>
-      </c>
-      <c r="E130" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F130" t="s">
         <v>419</v>
@@ -7580,13 +7577,16 @@
         <v>420</v>
       </c>
       <c r="I130" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J130" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K130" t="s">
+        <v>17</v>
       </c>
       <c r="L130" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -7600,10 +7600,7 @@
         <v>403</v>
       </c>
       <c r="D131" t="s">
-        <v>15</v>
-      </c>
-      <c r="E131" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F131" t="s">
         <v>422</v>
@@ -7615,13 +7612,16 @@
         <v>423</v>
       </c>
       <c r="I131" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J131" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K131" t="s">
+        <v>17</v>
       </c>
       <c r="L131" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -7635,10 +7635,7 @@
         <v>425</v>
       </c>
       <c r="D132" t="s">
-        <v>15</v>
-      </c>
-      <c r="E132" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F132" t="s">
         <v>426</v>
@@ -7650,13 +7647,16 @@
         <v>427</v>
       </c>
       <c r="I132" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J132" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K132" t="s">
+        <v>17</v>
       </c>
       <c r="L132" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -7670,28 +7670,28 @@
         <v>425</v>
       </c>
       <c r="D133" t="s">
-        <v>31</v>
-      </c>
-      <c r="E133" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F133" t="s">
         <v>429</v>
       </c>
       <c r="G133" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H133" t="s">
         <v>430</v>
       </c>
       <c r="I133" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J133" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K133" t="s">
+        <v>17</v>
       </c>
       <c r="L133" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -7705,10 +7705,7 @@
         <v>425</v>
       </c>
       <c r="D134" t="s">
-        <v>15</v>
-      </c>
-      <c r="E134" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F134" t="s">
         <v>432</v>
@@ -7720,13 +7717,16 @@
         <v>433</v>
       </c>
       <c r="I134" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J134" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K134" t="s">
+        <v>17</v>
       </c>
       <c r="L134" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -7740,28 +7740,28 @@
         <v>425</v>
       </c>
       <c r="D135" t="s">
-        <v>31</v>
-      </c>
-      <c r="E135" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F135" t="s">
         <v>435</v>
       </c>
       <c r="G135" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H135" t="s">
         <v>436</v>
       </c>
       <c r="I135" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J135" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K135" t="s">
+        <v>17</v>
       </c>
       <c r="L135" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -7775,10 +7775,7 @@
         <v>425</v>
       </c>
       <c r="D136" t="s">
-        <v>15</v>
-      </c>
-      <c r="E136" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F136" t="s">
         <v>438</v>
@@ -7790,13 +7787,16 @@
         <v>439</v>
       </c>
       <c r="I136" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J136" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K136" t="s">
+        <v>17</v>
       </c>
       <c r="L136" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -7810,28 +7810,28 @@
         <v>425</v>
       </c>
       <c r="D137" t="s">
-        <v>31</v>
-      </c>
-      <c r="E137" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F137" t="s">
         <v>441</v>
       </c>
       <c r="G137" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H137" t="s">
         <v>442</v>
       </c>
       <c r="I137" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J137" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K137" t="s">
+        <v>17</v>
       </c>
       <c r="L137" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -7845,10 +7845,7 @@
         <v>425</v>
       </c>
       <c r="D138" t="s">
-        <v>15</v>
-      </c>
-      <c r="E138" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F138" t="s">
         <v>444</v>
@@ -7860,13 +7857,16 @@
         <v>445</v>
       </c>
       <c r="I138" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J138" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K138" t="s">
+        <v>17</v>
       </c>
       <c r="L138" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" spans="1:12">
@@ -7880,10 +7880,7 @@
         <v>425</v>
       </c>
       <c r="D139" t="s">
-        <v>15</v>
-      </c>
-      <c r="E139" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F139" t="s">
         <v>447</v>
@@ -7895,13 +7892,16 @@
         <v>448</v>
       </c>
       <c r="I139" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J139" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K139" t="s">
+        <v>32</v>
       </c>
       <c r="L139" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -7915,10 +7915,7 @@
         <v>425</v>
       </c>
       <c r="D140" t="s">
-        <v>15</v>
-      </c>
-      <c r="E140" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F140" t="s">
         <v>450</v>
@@ -7930,13 +7927,16 @@
         <v>451</v>
       </c>
       <c r="I140" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J140" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K140" t="s">
+        <v>17</v>
       </c>
       <c r="L140" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:12">
@@ -7950,28 +7950,28 @@
         <v>425</v>
       </c>
       <c r="D141" t="s">
-        <v>31</v>
-      </c>
-      <c r="E141" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F141" t="s">
         <v>453</v>
       </c>
       <c r="G141" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H141" t="s">
         <v>454</v>
       </c>
       <c r="I141" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J141" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K141" t="s">
+        <v>32</v>
       </c>
       <c r="L141" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -7985,10 +7985,7 @@
         <v>425</v>
       </c>
       <c r="D142" t="s">
-        <v>15</v>
-      </c>
-      <c r="E142" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F142" t="s">
         <v>456</v>
@@ -8000,13 +7997,16 @@
         <v>457</v>
       </c>
       <c r="I142" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J142" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K142" t="s">
+        <v>17</v>
       </c>
       <c r="L142" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:12">
@@ -8020,28 +8020,28 @@
         <v>459</v>
       </c>
       <c r="D143" t="s">
-        <v>31</v>
-      </c>
-      <c r="E143" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F143" t="s">
         <v>460</v>
       </c>
       <c r="G143" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H143" t="s">
         <v>461</v>
       </c>
       <c r="I143" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J143" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K143" t="s">
+        <v>17</v>
       </c>
       <c r="L143" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -8055,28 +8055,28 @@
         <v>459</v>
       </c>
       <c r="D144" t="s">
-        <v>31</v>
-      </c>
-      <c r="E144" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F144" t="s">
         <v>463</v>
       </c>
       <c r="G144" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H144" t="s">
         <v>464</v>
       </c>
       <c r="I144" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J144" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K144" t="s">
+        <v>17</v>
       </c>
       <c r="L144" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -8090,28 +8090,28 @@
         <v>459</v>
       </c>
       <c r="D145" t="s">
-        <v>31</v>
-      </c>
-      <c r="E145" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F145" t="s">
         <v>466</v>
       </c>
       <c r="G145" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H145" t="s">
         <v>467</v>
       </c>
       <c r="I145" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J145" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K145" t="s">
+        <v>17</v>
       </c>
       <c r="L145" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146" spans="1:12">
@@ -8125,10 +8125,7 @@
         <v>459</v>
       </c>
       <c r="D146" t="s">
-        <v>15</v>
-      </c>
-      <c r="E146" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F146" t="s">
         <v>469</v>
@@ -8140,13 +8137,16 @@
         <v>470</v>
       </c>
       <c r="I146" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J146" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K146" t="s">
+        <v>17</v>
       </c>
       <c r="L146" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147" spans="1:12">
@@ -8160,10 +8160,7 @@
         <v>459</v>
       </c>
       <c r="D147" t="s">
-        <v>15</v>
-      </c>
-      <c r="E147" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F147" t="s">
         <v>472</v>
@@ -8175,13 +8172,16 @@
         <v>473</v>
       </c>
       <c r="I147" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J147" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K147" t="s">
+        <v>17</v>
       </c>
       <c r="L147" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148" spans="1:12">
@@ -8195,10 +8195,7 @@
         <v>459</v>
       </c>
       <c r="D148" t="s">
-        <v>15</v>
-      </c>
-      <c r="E148" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F148" t="s">
         <v>475</v>
@@ -8210,13 +8207,16 @@
         <v>476</v>
       </c>
       <c r="I148" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J148" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K148" t="s">
+        <v>32</v>
       </c>
       <c r="L148" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -8230,28 +8230,28 @@
         <v>459</v>
       </c>
       <c r="D149" t="s">
-        <v>31</v>
-      </c>
-      <c r="E149" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F149" t="s">
         <v>478</v>
       </c>
       <c r="G149" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H149" t="s">
         <v>479</v>
       </c>
       <c r="I149" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J149" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K149" t="s">
+        <v>17</v>
       </c>
       <c r="L149" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -8265,10 +8265,7 @@
         <v>459</v>
       </c>
       <c r="D150" t="s">
-        <v>15</v>
-      </c>
-      <c r="E150" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F150" t="s">
         <v>481</v>
@@ -8280,13 +8277,16 @@
         <v>482</v>
       </c>
       <c r="I150" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J150" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K150" t="s">
+        <v>17</v>
       </c>
       <c r="L150" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" spans="1:12">
@@ -8300,10 +8300,7 @@
         <v>459</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
-      </c>
-      <c r="E151" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F151" t="s">
         <v>484</v>
@@ -8315,13 +8312,16 @@
         <v>485</v>
       </c>
       <c r="I151" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J151" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K151" t="s">
+        <v>17</v>
       </c>
       <c r="L151" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -8335,10 +8335,7 @@
         <v>487</v>
       </c>
       <c r="D152" t="s">
-        <v>15</v>
-      </c>
-      <c r="E152" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F152" t="s">
         <v>488</v>
@@ -8350,13 +8347,16 @@
         <v>489</v>
       </c>
       <c r="I152" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J152" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K152" t="s">
+        <v>17</v>
       </c>
       <c r="L152" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" spans="1:12">
@@ -8370,10 +8370,7 @@
         <v>487</v>
       </c>
       <c r="D153" t="s">
-        <v>15</v>
-      </c>
-      <c r="E153" t="s">
-        <v>31</v>
+        <v>387</v>
       </c>
       <c r="F153" t="s">
         <v>491</v>
@@ -8385,13 +8382,16 @@
         <v>492</v>
       </c>
       <c r="I153" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J153" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="K153" t="s">
+        <v>17</v>
       </c>
       <c r="L153" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -8405,10 +8405,7 @@
         <v>487</v>
       </c>
       <c r="D154" t="s">
-        <v>15</v>
-      </c>
-      <c r="E154" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F154" t="s">
         <v>494</v>
@@ -8420,13 +8417,16 @@
         <v>495</v>
       </c>
       <c r="I154" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J154" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K154" t="s">
+        <v>17</v>
       </c>
       <c r="L154" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155" spans="1:12">
@@ -8440,10 +8440,7 @@
         <v>487</v>
       </c>
       <c r="D155" t="s">
-        <v>15</v>
-      </c>
-      <c r="E155" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F155" t="s">
         <v>497</v>
@@ -8455,13 +8452,16 @@
         <v>498</v>
       </c>
       <c r="I155" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J155" t="s">
+        <v>17</v>
+      </c>
+      <c r="K155" t="s">
+        <v>17</v>
+      </c>
+      <c r="L155" t="s">
         <v>369</v>
-      </c>
-      <c r="L155" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -8475,10 +8475,7 @@
         <v>487</v>
       </c>
       <c r="D156" t="s">
-        <v>15</v>
-      </c>
-      <c r="E156" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F156" t="s">
         <v>500</v>
@@ -8490,13 +8487,16 @@
         <v>501</v>
       </c>
       <c r="I156" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J156" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K156" t="s">
+        <v>17</v>
       </c>
       <c r="L156" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157" spans="1:12">
@@ -8510,10 +8510,7 @@
         <v>487</v>
       </c>
       <c r="D157" t="s">
-        <v>15</v>
-      </c>
-      <c r="E157" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F157" t="s">
         <v>503</v>
@@ -8525,13 +8522,16 @@
         <v>504</v>
       </c>
       <c r="I157" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J157" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K157" t="s">
+        <v>17</v>
       </c>
       <c r="L157" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158" spans="1:12">
@@ -8545,10 +8545,7 @@
         <v>487</v>
       </c>
       <c r="D158" t="s">
-        <v>15</v>
-      </c>
-      <c r="E158" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F158" t="s">
         <v>506</v>
@@ -8560,13 +8557,16 @@
         <v>507</v>
       </c>
       <c r="I158" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J158" t="s">
+        <v>17</v>
+      </c>
+      <c r="K158" t="s">
+        <v>17</v>
+      </c>
+      <c r="L158" t="s">
         <v>369</v>
-      </c>
-      <c r="L158" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="159" spans="1:12">
@@ -8580,10 +8580,7 @@
         <v>487</v>
       </c>
       <c r="D159" t="s">
-        <v>15</v>
-      </c>
-      <c r="E159" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F159" t="s">
         <v>509</v>
@@ -8595,13 +8592,16 @@
         <v>510</v>
       </c>
       <c r="I159" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J159" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K159" t="s">
+        <v>17</v>
       </c>
       <c r="L159" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -8615,10 +8615,7 @@
         <v>487</v>
       </c>
       <c r="D160" t="s">
-        <v>15</v>
-      </c>
-      <c r="E160" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F160" t="s">
         <v>512</v>
@@ -8630,13 +8627,16 @@
         <v>513</v>
       </c>
       <c r="I160" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J160" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K160" t="s">
+        <v>17</v>
       </c>
       <c r="L160" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" spans="1:12">
@@ -8650,10 +8650,7 @@
         <v>487</v>
       </c>
       <c r="D161" t="s">
-        <v>15</v>
-      </c>
-      <c r="E161" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F161" t="s">
         <v>515</v>
@@ -8665,13 +8662,16 @@
         <v>516</v>
       </c>
       <c r="I161" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J161" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K161" t="s">
+        <v>17</v>
       </c>
       <c r="L161" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -8685,10 +8685,7 @@
         <v>487</v>
       </c>
       <c r="D162" t="s">
-        <v>15</v>
-      </c>
-      <c r="E162" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F162" t="s">
         <v>518</v>
@@ -8700,13 +8697,16 @@
         <v>519</v>
       </c>
       <c r="I162" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J162" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K162" t="s">
+        <v>17</v>
       </c>
       <c r="L162" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -8720,10 +8720,7 @@
         <v>487</v>
       </c>
       <c r="D163" t="s">
-        <v>15</v>
-      </c>
-      <c r="E163" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F163" t="s">
         <v>521</v>
@@ -8735,13 +8732,16 @@
         <v>522</v>
       </c>
       <c r="I163" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J163" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K163" t="s">
+        <v>17</v>
       </c>
       <c r="L163" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -8755,10 +8755,7 @@
         <v>487</v>
       </c>
       <c r="D164" t="s">
-        <v>15</v>
-      </c>
-      <c r="E164" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F164" t="s">
         <v>524</v>
@@ -8770,13 +8767,16 @@
         <v>525</v>
       </c>
       <c r="I164" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J164" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K164" t="s">
+        <v>17</v>
       </c>
       <c r="L164" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -8790,10 +8790,7 @@
         <v>487</v>
       </c>
       <c r="D165" t="s">
-        <v>15</v>
-      </c>
-      <c r="E165" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F165" t="s">
         <v>527</v>
@@ -8805,13 +8802,16 @@
         <v>528</v>
       </c>
       <c r="I165" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J165" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K165" t="s">
+        <v>17</v>
       </c>
       <c r="L165" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -8825,10 +8825,7 @@
         <v>487</v>
       </c>
       <c r="D166" t="s">
-        <v>15</v>
-      </c>
-      <c r="E166" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F166" t="s">
         <v>530</v>
@@ -8840,13 +8837,16 @@
         <v>531</v>
       </c>
       <c r="I166" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J166" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K166" t="s">
+        <v>17</v>
       </c>
       <c r="L166" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:12">
@@ -8860,10 +8860,7 @@
         <v>487</v>
       </c>
       <c r="D167" t="s">
-        <v>15</v>
-      </c>
-      <c r="E167" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F167" t="s">
         <v>533</v>
@@ -8875,13 +8872,16 @@
         <v>534</v>
       </c>
       <c r="I167" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J167" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K167" t="s">
+        <v>17</v>
       </c>
       <c r="L167" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168" spans="1:12">
@@ -8895,10 +8895,7 @@
         <v>487</v>
       </c>
       <c r="D168" t="s">
-        <v>15</v>
-      </c>
-      <c r="E168" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F168" t="s">
         <v>536</v>
@@ -8910,13 +8907,16 @@
         <v>537</v>
       </c>
       <c r="I168" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J168" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K168" t="s">
+        <v>17</v>
       </c>
       <c r="L168" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -8930,28 +8930,28 @@
         <v>487</v>
       </c>
       <c r="D169" t="s">
-        <v>31</v>
-      </c>
-      <c r="E169" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="F169" t="s">
         <v>539</v>
       </c>
       <c r="G169" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H169" t="s">
         <v>540</v>
       </c>
       <c r="I169" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J169" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K169" t="s">
+        <v>17</v>
       </c>
       <c r="L169" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170" spans="1:12">
@@ -8965,28 +8965,28 @@
         <v>542</v>
       </c>
       <c r="D170" t="s">
-        <v>15</v>
-      </c>
-      <c r="E170" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F170" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G170" t="s">
         <v>17</v>
       </c>
       <c r="H170" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I170" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J170" t="s">
+        <v>17</v>
+      </c>
+      <c r="K170" t="s">
+        <v>17</v>
+      </c>
+      <c r="L170" t="s">
         <v>369</v>
-      </c>
-      <c r="L170" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="171" spans="1:12">
@@ -9000,10 +9000,7 @@
         <v>542</v>
       </c>
       <c r="D171" t="s">
-        <v>15</v>
-      </c>
-      <c r="E171" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F171" t="s">
         <v>547</v>
@@ -9015,13 +9012,16 @@
         <v>548</v>
       </c>
       <c r="I171" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J171" t="s">
+        <v>17</v>
+      </c>
+      <c r="K171" t="s">
+        <v>17</v>
+      </c>
+      <c r="L171" t="s">
         <v>369</v>
-      </c>
-      <c r="L171" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -9035,10 +9035,7 @@
         <v>542</v>
       </c>
       <c r="D172" t="s">
-        <v>15</v>
-      </c>
-      <c r="E172" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F172" t="s">
         <v>550</v>
@@ -9050,13 +9047,16 @@
         <v>551</v>
       </c>
       <c r="I172" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J172" t="s">
+        <v>17</v>
+      </c>
+      <c r="K172" t="s">
+        <v>17</v>
+      </c>
+      <c r="L172" t="s">
         <v>369</v>
-      </c>
-      <c r="L172" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -9070,10 +9070,7 @@
         <v>542</v>
       </c>
       <c r="D173" t="s">
-        <v>15</v>
-      </c>
-      <c r="E173" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F173" t="s">
         <v>553</v>
@@ -9085,13 +9082,16 @@
         <v>554</v>
       </c>
       <c r="I173" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J173" t="s">
+        <v>17</v>
+      </c>
+      <c r="K173" t="s">
+        <v>17</v>
+      </c>
+      <c r="L173" t="s">
         <v>369</v>
-      </c>
-      <c r="L173" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="174" spans="1:12">
@@ -9105,10 +9105,7 @@
         <v>542</v>
       </c>
       <c r="D174" t="s">
-        <v>15</v>
-      </c>
-      <c r="E174" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F174" t="s">
         <v>556</v>
@@ -9120,13 +9117,16 @@
         <v>557</v>
       </c>
       <c r="I174" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J174" t="s">
+        <v>17</v>
+      </c>
+      <c r="K174" t="s">
+        <v>17</v>
+      </c>
+      <c r="L174" t="s">
         <v>369</v>
-      </c>
-      <c r="L174" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -9140,10 +9140,7 @@
         <v>542</v>
       </c>
       <c r="D175" t="s">
-        <v>15</v>
-      </c>
-      <c r="E175" t="s">
-        <v>31</v>
+        <v>543</v>
       </c>
       <c r="F175" t="s">
         <v>559</v>
@@ -9155,13 +9152,16 @@
         <v>560</v>
       </c>
       <c r="I175" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J175" t="s">
+        <v>32</v>
+      </c>
+      <c r="K175" t="s">
+        <v>17</v>
+      </c>
+      <c r="L175" t="s">
         <v>369</v>
-      </c>
-      <c r="L175" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -9175,10 +9175,7 @@
         <v>542</v>
       </c>
       <c r="D176" t="s">
-        <v>15</v>
-      </c>
-      <c r="E176" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F176" t="s">
         <v>562</v>
@@ -9190,13 +9187,16 @@
         <v>563</v>
       </c>
       <c r="I176" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J176" t="s">
+        <v>17</v>
+      </c>
+      <c r="K176" t="s">
+        <v>17</v>
+      </c>
+      <c r="L176" t="s">
         <v>369</v>
-      </c>
-      <c r="L176" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -9210,10 +9210,7 @@
         <v>542</v>
       </c>
       <c r="D177" t="s">
-        <v>15</v>
-      </c>
-      <c r="E177" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F177" t="s">
         <v>565</v>
@@ -9225,13 +9222,16 @@
         <v>566</v>
       </c>
       <c r="I177" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J177" t="s">
+        <v>17</v>
+      </c>
+      <c r="K177" t="s">
+        <v>17</v>
+      </c>
+      <c r="L177" t="s">
         <v>369</v>
-      </c>
-      <c r="L177" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -9245,10 +9245,7 @@
         <v>542</v>
       </c>
       <c r="D178" t="s">
-        <v>15</v>
-      </c>
-      <c r="E178" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F178" t="s">
         <v>568</v>
@@ -9260,13 +9257,16 @@
         <v>569</v>
       </c>
       <c r="I178" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J178" t="s">
+        <v>17</v>
+      </c>
+      <c r="K178" t="s">
+        <v>17</v>
+      </c>
+      <c r="L178" t="s">
         <v>369</v>
-      </c>
-      <c r="L178" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -9280,10 +9280,7 @@
         <v>542</v>
       </c>
       <c r="D179" t="s">
-        <v>15</v>
-      </c>
-      <c r="E179" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F179" t="s">
         <v>571</v>
@@ -9295,13 +9292,16 @@
         <v>572</v>
       </c>
       <c r="I179" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J179" t="s">
+        <v>17</v>
+      </c>
+      <c r="K179" t="s">
+        <v>17</v>
+      </c>
+      <c r="L179" t="s">
         <v>369</v>
-      </c>
-      <c r="L179" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -9315,10 +9315,7 @@
         <v>574</v>
       </c>
       <c r="D180" t="s">
-        <v>15</v>
-      </c>
-      <c r="E180" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F180" t="s">
         <v>575</v>
@@ -9330,13 +9327,16 @@
         <v>576</v>
       </c>
       <c r="I180" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J180" t="s">
+        <v>17</v>
+      </c>
+      <c r="K180" t="s">
+        <v>17</v>
+      </c>
+      <c r="L180" t="s">
         <v>369</v>
-      </c>
-      <c r="L180" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -9350,10 +9350,7 @@
         <v>574</v>
       </c>
       <c r="D181" t="s">
-        <v>15</v>
-      </c>
-      <c r="E181" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F181" t="s">
         <v>578</v>
@@ -9365,13 +9362,16 @@
         <v>579</v>
       </c>
       <c r="I181" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J181" t="s">
+        <v>17</v>
+      </c>
+      <c r="K181" t="s">
+        <v>17</v>
+      </c>
+      <c r="L181" t="s">
         <v>369</v>
-      </c>
-      <c r="L181" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -9385,10 +9385,7 @@
         <v>574</v>
       </c>
       <c r="D182" t="s">
-        <v>15</v>
-      </c>
-      <c r="E182" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F182" t="s">
         <v>581</v>
@@ -9400,13 +9397,16 @@
         <v>582</v>
       </c>
       <c r="I182" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J182" t="s">
+        <v>17</v>
+      </c>
+      <c r="K182" t="s">
+        <v>17</v>
+      </c>
+      <c r="L182" t="s">
         <v>369</v>
-      </c>
-      <c r="L182" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -9420,25 +9420,25 @@
         <v>574</v>
       </c>
       <c r="D183" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="E183" t="s">
-        <v>15</v>
+        <v>585</v>
       </c>
       <c r="G183" t="s">
         <v>17</v>
       </c>
       <c r="I183" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J183" t="s">
+        <v>17</v>
+      </c>
+      <c r="K183" t="s">
+        <v>17</v>
+      </c>
+      <c r="L183" t="s">
         <v>369</v>
-      </c>
-      <c r="K183" t="s">
-        <v>585</v>
-      </c>
-      <c r="L183" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -9452,10 +9452,7 @@
         <v>574</v>
       </c>
       <c r="D184" t="s">
-        <v>15</v>
-      </c>
-      <c r="E184" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F184" t="s">
         <v>587</v>
@@ -9467,13 +9464,16 @@
         <v>588</v>
       </c>
       <c r="I184" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J184" t="s">
+        <v>17</v>
+      </c>
+      <c r="K184" t="s">
+        <v>17</v>
+      </c>
+      <c r="L184" t="s">
         <v>369</v>
-      </c>
-      <c r="L184" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -9487,10 +9487,7 @@
         <v>574</v>
       </c>
       <c r="D185" t="s">
-        <v>15</v>
-      </c>
-      <c r="E185" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F185" t="s">
         <v>590</v>
@@ -9502,13 +9499,16 @@
         <v>591</v>
       </c>
       <c r="I185" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J185" t="s">
+        <v>17</v>
+      </c>
+      <c r="K185" t="s">
+        <v>17</v>
+      </c>
+      <c r="L185" t="s">
         <v>369</v>
-      </c>
-      <c r="L185" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -9522,10 +9522,7 @@
         <v>574</v>
       </c>
       <c r="D186" t="s">
-        <v>15</v>
-      </c>
-      <c r="E186" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F186" t="s">
         <v>593</v>
@@ -9537,13 +9534,16 @@
         <v>594</v>
       </c>
       <c r="I186" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J186" t="s">
+        <v>17</v>
+      </c>
+      <c r="K186" t="s">
+        <v>17</v>
+      </c>
+      <c r="L186" t="s">
         <v>369</v>
-      </c>
-      <c r="L186" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -9557,10 +9557,7 @@
         <v>574</v>
       </c>
       <c r="D187" t="s">
-        <v>15</v>
-      </c>
-      <c r="E187" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F187" t="s">
         <v>596</v>
@@ -9572,13 +9569,16 @@
         <v>597</v>
       </c>
       <c r="I187" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J187" t="s">
+        <v>17</v>
+      </c>
+      <c r="K187" t="s">
+        <v>17</v>
+      </c>
+      <c r="L187" t="s">
         <v>369</v>
-      </c>
-      <c r="L187" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -9592,10 +9592,7 @@
         <v>574</v>
       </c>
       <c r="D188" t="s">
-        <v>15</v>
-      </c>
-      <c r="E188" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F188" t="s">
         <v>599</v>
@@ -9607,13 +9604,16 @@
         <v>600</v>
       </c>
       <c r="I188" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J188" t="s">
+        <v>17</v>
+      </c>
+      <c r="K188" t="s">
+        <v>17</v>
+      </c>
+      <c r="L188" t="s">
         <v>369</v>
-      </c>
-      <c r="L188" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -9627,10 +9627,7 @@
         <v>574</v>
       </c>
       <c r="D189" t="s">
-        <v>15</v>
-      </c>
-      <c r="E189" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F189" t="s">
         <v>602</v>
@@ -9642,13 +9639,16 @@
         <v>603</v>
       </c>
       <c r="I189" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J189" t="s">
+        <v>17</v>
+      </c>
+      <c r="K189" t="s">
+        <v>17</v>
+      </c>
+      <c r="L189" t="s">
         <v>369</v>
-      </c>
-      <c r="L189" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -9662,10 +9662,7 @@
         <v>574</v>
       </c>
       <c r="D190" t="s">
-        <v>15</v>
-      </c>
-      <c r="E190" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F190" t="s">
         <v>605</v>
@@ -9677,13 +9674,16 @@
         <v>606</v>
       </c>
       <c r="I190" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J190" t="s">
+        <v>17</v>
+      </c>
+      <c r="K190" t="s">
+        <v>17</v>
+      </c>
+      <c r="L190" t="s">
         <v>369</v>
-      </c>
-      <c r="L190" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -9697,10 +9697,7 @@
         <v>574</v>
       </c>
       <c r="D191" t="s">
-        <v>15</v>
-      </c>
-      <c r="E191" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F191" t="s">
         <v>608</v>
@@ -9712,13 +9709,16 @@
         <v>609</v>
       </c>
       <c r="I191" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J191" t="s">
+        <v>17</v>
+      </c>
+      <c r="K191" t="s">
+        <v>17</v>
+      </c>
+      <c r="L191" t="s">
         <v>369</v>
-      </c>
-      <c r="L191" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -9732,10 +9732,7 @@
         <v>574</v>
       </c>
       <c r="D192" t="s">
-        <v>15</v>
-      </c>
-      <c r="E192" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F192" t="s">
         <v>611</v>
@@ -9747,13 +9744,16 @@
         <v>612</v>
       </c>
       <c r="I192" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J192" t="s">
+        <v>17</v>
+      </c>
+      <c r="K192" t="s">
+        <v>17</v>
+      </c>
+      <c r="L192" t="s">
         <v>369</v>
-      </c>
-      <c r="L192" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -9767,10 +9767,7 @@
         <v>574</v>
       </c>
       <c r="D193" t="s">
-        <v>15</v>
-      </c>
-      <c r="E193" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F193" t="s">
         <v>614</v>
@@ -9782,13 +9779,16 @@
         <v>615</v>
       </c>
       <c r="I193" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J193" t="s">
+        <v>17</v>
+      </c>
+      <c r="K193" t="s">
+        <v>17</v>
+      </c>
+      <c r="L193" t="s">
         <v>369</v>
-      </c>
-      <c r="L193" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -9802,10 +9802,7 @@
         <v>574</v>
       </c>
       <c r="D194" t="s">
-        <v>15</v>
-      </c>
-      <c r="E194" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F194" t="s">
         <v>617</v>
@@ -9817,13 +9814,16 @@
         <v>618</v>
       </c>
       <c r="I194" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J194" t="s">
+        <v>17</v>
+      </c>
+      <c r="K194" t="s">
+        <v>17</v>
+      </c>
+      <c r="L194" t="s">
         <v>369</v>
-      </c>
-      <c r="L194" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -9837,10 +9837,7 @@
         <v>574</v>
       </c>
       <c r="D195" t="s">
-        <v>15</v>
-      </c>
-      <c r="E195" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F195" t="s">
         <v>620</v>
@@ -9852,13 +9849,16 @@
         <v>621</v>
       </c>
       <c r="I195" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J195" t="s">
+        <v>17</v>
+      </c>
+      <c r="K195" t="s">
+        <v>17</v>
+      </c>
+      <c r="L195" t="s">
         <v>369</v>
-      </c>
-      <c r="L195" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -9872,10 +9872,7 @@
         <v>574</v>
       </c>
       <c r="D196" t="s">
-        <v>15</v>
-      </c>
-      <c r="E196" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F196" t="s">
         <v>623</v>
@@ -9887,13 +9884,16 @@
         <v>624</v>
       </c>
       <c r="I196" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J196" t="s">
+        <v>17</v>
+      </c>
+      <c r="K196" t="s">
+        <v>17</v>
+      </c>
+      <c r="L196" t="s">
         <v>369</v>
-      </c>
-      <c r="L196" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -9907,10 +9907,7 @@
         <v>626</v>
       </c>
       <c r="D197" t="s">
-        <v>15</v>
-      </c>
-      <c r="E197" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F197" t="s">
         <v>627</v>
@@ -9922,13 +9919,16 @@
         <v>628</v>
       </c>
       <c r="I197" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J197" t="s">
+        <v>17</v>
+      </c>
+      <c r="K197" t="s">
+        <v>17</v>
+      </c>
+      <c r="L197" t="s">
         <v>369</v>
-      </c>
-      <c r="L197" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -9942,10 +9942,7 @@
         <v>626</v>
       </c>
       <c r="D198" t="s">
-        <v>15</v>
-      </c>
-      <c r="E198" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F198" t="s">
         <v>630</v>
@@ -9957,13 +9954,16 @@
         <v>631</v>
       </c>
       <c r="I198" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J198" t="s">
+        <v>17</v>
+      </c>
+      <c r="K198" t="s">
+        <v>17</v>
+      </c>
+      <c r="L198" t="s">
         <v>369</v>
-      </c>
-      <c r="L198" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -9977,10 +9977,7 @@
         <v>626</v>
       </c>
       <c r="D199" t="s">
-        <v>15</v>
-      </c>
-      <c r="E199" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F199" t="s">
         <v>633</v>
@@ -9992,13 +9989,16 @@
         <v>634</v>
       </c>
       <c r="I199" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J199" t="s">
+        <v>17</v>
+      </c>
+      <c r="K199" t="s">
+        <v>17</v>
+      </c>
+      <c r="L199" t="s">
         <v>369</v>
-      </c>
-      <c r="L199" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -10012,10 +10012,7 @@
         <v>626</v>
       </c>
       <c r="D200" t="s">
-        <v>15</v>
-      </c>
-      <c r="E200" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F200" t="s">
         <v>636</v>
@@ -10027,13 +10024,16 @@
         <v>637</v>
       </c>
       <c r="I200" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J200" t="s">
+        <v>17</v>
+      </c>
+      <c r="K200" t="s">
+        <v>17</v>
+      </c>
+      <c r="L200" t="s">
         <v>369</v>
-      </c>
-      <c r="L200" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -10047,10 +10047,7 @@
         <v>626</v>
       </c>
       <c r="D201" t="s">
-        <v>15</v>
-      </c>
-      <c r="E201" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F201" t="s">
         <v>639</v>
@@ -10062,13 +10059,16 @@
         <v>640</v>
       </c>
       <c r="I201" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J201" t="s">
+        <v>17</v>
+      </c>
+      <c r="K201" t="s">
+        <v>17</v>
+      </c>
+      <c r="L201" t="s">
         <v>369</v>
-      </c>
-      <c r="L201" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -10082,10 +10082,7 @@
         <v>626</v>
       </c>
       <c r="D202" t="s">
-        <v>15</v>
-      </c>
-      <c r="E202" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F202" t="s">
         <v>642</v>
@@ -10097,13 +10094,16 @@
         <v>643</v>
       </c>
       <c r="I202" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J202" t="s">
+        <v>17</v>
+      </c>
+      <c r="K202" t="s">
+        <v>17</v>
+      </c>
+      <c r="L202" t="s">
         <v>369</v>
-      </c>
-      <c r="L202" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -10117,10 +10117,7 @@
         <v>626</v>
       </c>
       <c r="D203" t="s">
-        <v>15</v>
-      </c>
-      <c r="E203" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F203" t="s">
         <v>645</v>
@@ -10132,13 +10129,16 @@
         <v>646</v>
       </c>
       <c r="I203" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J203" t="s">
+        <v>17</v>
+      </c>
+      <c r="K203" t="s">
+        <v>17</v>
+      </c>
+      <c r="L203" t="s">
         <v>369</v>
-      </c>
-      <c r="L203" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -10152,10 +10152,7 @@
         <v>626</v>
       </c>
       <c r="D204" t="s">
-        <v>15</v>
-      </c>
-      <c r="E204" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F204" t="s">
         <v>648</v>
@@ -10167,13 +10164,16 @@
         <v>649</v>
       </c>
       <c r="I204" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J204" t="s">
+        <v>17</v>
+      </c>
+      <c r="K204" t="s">
+        <v>17</v>
+      </c>
+      <c r="L204" t="s">
         <v>369</v>
-      </c>
-      <c r="L204" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -10187,10 +10187,7 @@
         <v>626</v>
       </c>
       <c r="D205" t="s">
-        <v>15</v>
-      </c>
-      <c r="E205" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F205" t="s">
         <v>651</v>
@@ -10202,13 +10199,16 @@
         <v>652</v>
       </c>
       <c r="I205" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J205" t="s">
+        <v>17</v>
+      </c>
+      <c r="K205" t="s">
+        <v>17</v>
+      </c>
+      <c r="L205" t="s">
         <v>369</v>
-      </c>
-      <c r="L205" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -10222,10 +10222,7 @@
         <v>626</v>
       </c>
       <c r="D206" t="s">
-        <v>15</v>
-      </c>
-      <c r="E206" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F206" t="s">
         <v>654</v>
@@ -10237,13 +10234,16 @@
         <v>655</v>
       </c>
       <c r="I206" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J206" t="s">
+        <v>17</v>
+      </c>
+      <c r="K206" t="s">
+        <v>17</v>
+      </c>
+      <c r="L206" t="s">
         <v>369</v>
-      </c>
-      <c r="L206" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -10257,10 +10257,7 @@
         <v>626</v>
       </c>
       <c r="D207" t="s">
-        <v>15</v>
-      </c>
-      <c r="E207" t="s">
-        <v>31</v>
+        <v>543</v>
       </c>
       <c r="F207" t="s">
         <v>657</v>
@@ -10272,13 +10269,16 @@
         <v>658</v>
       </c>
       <c r="I207" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J207" t="s">
+        <v>32</v>
+      </c>
+      <c r="K207" t="s">
+        <v>17</v>
+      </c>
+      <c r="L207" t="s">
         <v>369</v>
-      </c>
-      <c r="L207" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -10292,10 +10292,7 @@
         <v>626</v>
       </c>
       <c r="D208" t="s">
-        <v>15</v>
-      </c>
-      <c r="E208" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F208" t="s">
         <v>660</v>
@@ -10307,13 +10304,16 @@
         <v>661</v>
       </c>
       <c r="I208" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J208" t="s">
+        <v>17</v>
+      </c>
+      <c r="K208" t="s">
+        <v>17</v>
+      </c>
+      <c r="L208" t="s">
         <v>369</v>
-      </c>
-      <c r="L208" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -10327,10 +10327,7 @@
         <v>626</v>
       </c>
       <c r="D209" t="s">
-        <v>15</v>
-      </c>
-      <c r="E209" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F209" t="s">
         <v>663</v>
@@ -10342,13 +10339,16 @@
         <v>664</v>
       </c>
       <c r="I209" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J209" t="s">
+        <v>17</v>
+      </c>
+      <c r="K209" t="s">
+        <v>17</v>
+      </c>
+      <c r="L209" t="s">
         <v>369</v>
-      </c>
-      <c r="L209" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -10362,10 +10362,7 @@
         <v>626</v>
       </c>
       <c r="D210" t="s">
-        <v>15</v>
-      </c>
-      <c r="E210" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F210" t="s">
         <v>666</v>
@@ -10377,13 +10374,16 @@
         <v>667</v>
       </c>
       <c r="I210" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J210" t="s">
+        <v>17</v>
+      </c>
+      <c r="K210" t="s">
+        <v>17</v>
+      </c>
+      <c r="L210" t="s">
         <v>369</v>
-      </c>
-      <c r="L210" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -10397,10 +10397,7 @@
         <v>626</v>
       </c>
       <c r="D211" t="s">
-        <v>15</v>
-      </c>
-      <c r="E211" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F211" t="s">
         <v>669</v>
@@ -10412,13 +10409,16 @@
         <v>670</v>
       </c>
       <c r="I211" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J211" t="s">
+        <v>17</v>
+      </c>
+      <c r="K211" t="s">
+        <v>17</v>
+      </c>
+      <c r="L211" t="s">
         <v>369</v>
-      </c>
-      <c r="L211" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -10432,10 +10432,7 @@
         <v>626</v>
       </c>
       <c r="D212" t="s">
-        <v>15</v>
-      </c>
-      <c r="E212" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F212" t="s">
         <v>672</v>
@@ -10447,13 +10444,16 @@
         <v>673</v>
       </c>
       <c r="I212" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J212" t="s">
+        <v>17</v>
+      </c>
+      <c r="K212" t="s">
+        <v>17</v>
+      </c>
+      <c r="L212" t="s">
         <v>369</v>
-      </c>
-      <c r="L212" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -10467,10 +10467,7 @@
         <v>675</v>
       </c>
       <c r="D213" t="s">
-        <v>15</v>
-      </c>
-      <c r="E213" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F213" t="s">
         <v>676</v>
@@ -10482,13 +10479,16 @@
         <v>677</v>
       </c>
       <c r="I213" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J213" t="s">
+        <v>17</v>
+      </c>
+      <c r="K213" t="s">
+        <v>17</v>
+      </c>
+      <c r="L213" t="s">
         <v>369</v>
-      </c>
-      <c r="L213" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -10502,10 +10502,7 @@
         <v>675</v>
       </c>
       <c r="D214" t="s">
-        <v>15</v>
-      </c>
-      <c r="E214" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F214" t="s">
         <v>679</v>
@@ -10517,13 +10514,16 @@
         <v>680</v>
       </c>
       <c r="I214" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J214" t="s">
+        <v>17</v>
+      </c>
+      <c r="K214" t="s">
+        <v>17</v>
+      </c>
+      <c r="L214" t="s">
         <v>369</v>
-      </c>
-      <c r="L214" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -10537,10 +10537,7 @@
         <v>675</v>
       </c>
       <c r="D215" t="s">
-        <v>15</v>
-      </c>
-      <c r="E215" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F215" t="s">
         <v>682</v>
@@ -10552,13 +10549,16 @@
         <v>683</v>
       </c>
       <c r="I215" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J215" t="s">
+        <v>17</v>
+      </c>
+      <c r="K215" t="s">
+        <v>17</v>
+      </c>
+      <c r="L215" t="s">
         <v>369</v>
-      </c>
-      <c r="L215" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -10572,10 +10572,7 @@
         <v>675</v>
       </c>
       <c r="D216" t="s">
-        <v>15</v>
-      </c>
-      <c r="E216" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F216" t="s">
         <v>685</v>
@@ -10587,13 +10584,16 @@
         <v>686</v>
       </c>
       <c r="I216" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J216" t="s">
+        <v>17</v>
+      </c>
+      <c r="K216" t="s">
+        <v>17</v>
+      </c>
+      <c r="L216" t="s">
         <v>369</v>
-      </c>
-      <c r="L216" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -10607,10 +10607,7 @@
         <v>675</v>
       </c>
       <c r="D217" t="s">
-        <v>15</v>
-      </c>
-      <c r="E217" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F217" t="s">
         <v>688</v>
@@ -10622,13 +10619,16 @@
         <v>689</v>
       </c>
       <c r="I217" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J217" t="s">
+        <v>17</v>
+      </c>
+      <c r="K217" t="s">
+        <v>17</v>
+      </c>
+      <c r="L217" t="s">
         <v>369</v>
-      </c>
-      <c r="L217" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -10642,10 +10642,7 @@
         <v>675</v>
       </c>
       <c r="D218" t="s">
-        <v>15</v>
-      </c>
-      <c r="E218" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F218" t="s">
         <v>691</v>
@@ -10657,13 +10654,16 @@
         <v>692</v>
       </c>
       <c r="I218" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J218" t="s">
+        <v>17</v>
+      </c>
+      <c r="K218" t="s">
+        <v>17</v>
+      </c>
+      <c r="L218" t="s">
         <v>369</v>
-      </c>
-      <c r="L218" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -10677,10 +10677,7 @@
         <v>675</v>
       </c>
       <c r="D219" t="s">
-        <v>15</v>
-      </c>
-      <c r="E219" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F219" t="s">
         <v>694</v>
@@ -10692,13 +10689,16 @@
         <v>695</v>
       </c>
       <c r="I219" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J219" t="s">
+        <v>17</v>
+      </c>
+      <c r="K219" t="s">
+        <v>17</v>
+      </c>
+      <c r="L219" t="s">
         <v>369</v>
-      </c>
-      <c r="L219" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -10712,10 +10712,7 @@
         <v>675</v>
       </c>
       <c r="D220" t="s">
-        <v>15</v>
-      </c>
-      <c r="E220" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F220" t="s">
         <v>697</v>
@@ -10727,13 +10724,16 @@
         <v>698</v>
       </c>
       <c r="I220" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J220" t="s">
+        <v>17</v>
+      </c>
+      <c r="K220" t="s">
+        <v>17</v>
+      </c>
+      <c r="L220" t="s">
         <v>369</v>
-      </c>
-      <c r="L220" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -10747,10 +10747,7 @@
         <v>675</v>
       </c>
       <c r="D221" t="s">
-        <v>15</v>
-      </c>
-      <c r="E221" t="s">
-        <v>15</v>
+        <v>543</v>
       </c>
       <c r="F221" t="s">
         <v>700</v>
@@ -10762,13 +10759,16 @@
         <v>701</v>
       </c>
       <c r="I221" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J221" t="s">
+        <v>17</v>
+      </c>
+      <c r="K221" t="s">
+        <v>17</v>
+      </c>
+      <c r="L221" t="s">
         <v>369</v>
-      </c>
-      <c r="L221" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -10782,28 +10782,28 @@
         <v>703</v>
       </c>
       <c r="D222" t="s">
-        <v>15</v>
-      </c>
-      <c r="E222" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F222" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G222" t="s">
         <v>17</v>
       </c>
       <c r="H222" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="I222" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J222" t="s">
+        <v>17</v>
+      </c>
+      <c r="K222" t="s">
+        <v>17</v>
+      </c>
+      <c r="L222" t="s">
         <v>369</v>
-      </c>
-      <c r="L222" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -10817,10 +10817,7 @@
         <v>703</v>
       </c>
       <c r="D223" t="s">
-        <v>15</v>
-      </c>
-      <c r="E223" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F223" t="s">
         <v>708</v>
@@ -10832,13 +10829,16 @@
         <v>709</v>
       </c>
       <c r="I223" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J223" t="s">
+        <v>17</v>
+      </c>
+      <c r="K223" t="s">
+        <v>17</v>
+      </c>
+      <c r="L223" t="s">
         <v>369</v>
-      </c>
-      <c r="L223" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -10852,10 +10852,7 @@
         <v>703</v>
       </c>
       <c r="D224" t="s">
-        <v>15</v>
-      </c>
-      <c r="E224" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F224" t="s">
         <v>711</v>
@@ -10867,13 +10864,16 @@
         <v>712</v>
       </c>
       <c r="I224" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J224" t="s">
+        <v>17</v>
+      </c>
+      <c r="K224" t="s">
+        <v>17</v>
+      </c>
+      <c r="L224" t="s">
         <v>369</v>
-      </c>
-      <c r="L224" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -10887,10 +10887,7 @@
         <v>703</v>
       </c>
       <c r="D225" t="s">
-        <v>15</v>
-      </c>
-      <c r="E225" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F225" t="s">
         <v>714</v>
@@ -10902,13 +10899,16 @@
         <v>715</v>
       </c>
       <c r="I225" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J225" t="s">
+        <v>17</v>
+      </c>
+      <c r="K225" t="s">
+        <v>17</v>
+      </c>
+      <c r="L225" t="s">
         <v>369</v>
-      </c>
-      <c r="L225" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -10922,10 +10922,7 @@
         <v>703</v>
       </c>
       <c r="D226" t="s">
-        <v>15</v>
-      </c>
-      <c r="E226" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F226" t="s">
         <v>717</v>
@@ -10937,13 +10934,16 @@
         <v>718</v>
       </c>
       <c r="I226" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J226" t="s">
+        <v>17</v>
+      </c>
+      <c r="K226" t="s">
+        <v>17</v>
+      </c>
+      <c r="L226" t="s">
         <v>369</v>
-      </c>
-      <c r="L226" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -10957,10 +10957,7 @@
         <v>703</v>
       </c>
       <c r="D227" t="s">
-        <v>15</v>
-      </c>
-      <c r="E227" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F227" t="s">
         <v>720</v>
@@ -10972,13 +10969,16 @@
         <v>721</v>
       </c>
       <c r="I227" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J227" t="s">
+        <v>17</v>
+      </c>
+      <c r="K227" t="s">
+        <v>17</v>
+      </c>
+      <c r="L227" t="s">
         <v>369</v>
-      </c>
-      <c r="L227" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -10992,10 +10992,7 @@
         <v>723</v>
       </c>
       <c r="D228" t="s">
-        <v>15</v>
-      </c>
-      <c r="E228" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F228" t="s">
         <v>724</v>
@@ -11007,13 +11004,16 @@
         <v>725</v>
       </c>
       <c r="I228" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J228" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K228" t="s">
+        <v>32</v>
       </c>
       <c r="L228" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -11027,10 +11027,7 @@
         <v>723</v>
       </c>
       <c r="D229" t="s">
-        <v>15</v>
-      </c>
-      <c r="E229" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F229" t="s">
         <v>727</v>
@@ -11042,13 +11039,16 @@
         <v>728</v>
       </c>
       <c r="I229" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J229" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K229" t="s">
+        <v>32</v>
       </c>
       <c r="L229" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -11062,10 +11062,7 @@
         <v>723</v>
       </c>
       <c r="D230" t="s">
-        <v>15</v>
-      </c>
-      <c r="E230" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F230" t="s">
         <v>730</v>
@@ -11077,13 +11074,16 @@
         <v>731</v>
       </c>
       <c r="I230" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J230" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K230" t="s">
+        <v>32</v>
       </c>
       <c r="L230" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -11097,28 +11097,28 @@
         <v>723</v>
       </c>
       <c r="D231" t="s">
-        <v>31</v>
-      </c>
-      <c r="E231" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F231" t="s">
         <v>733</v>
       </c>
       <c r="G231" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H231" t="s">
         <v>734</v>
       </c>
       <c r="I231" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J231" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K231" t="s">
+        <v>32</v>
       </c>
       <c r="L231" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -11132,28 +11132,28 @@
         <v>723</v>
       </c>
       <c r="D232" t="s">
-        <v>31</v>
-      </c>
-      <c r="E232" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F232" t="s">
         <v>736</v>
       </c>
       <c r="G232" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H232" t="s">
         <v>737</v>
       </c>
       <c r="I232" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J232" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K232" t="s">
+        <v>32</v>
       </c>
       <c r="L232" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -11167,10 +11167,7 @@
         <v>739</v>
       </c>
       <c r="D233" t="s">
-        <v>15</v>
-      </c>
-      <c r="E233" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F233" t="s">
         <v>740</v>
@@ -11182,13 +11179,16 @@
         <v>741</v>
       </c>
       <c r="I233" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J233" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K233" t="s">
+        <v>32</v>
       </c>
       <c r="L233" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -11202,28 +11202,28 @@
         <v>739</v>
       </c>
       <c r="D234" t="s">
-        <v>31</v>
-      </c>
-      <c r="E234" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F234" t="s">
         <v>743</v>
       </c>
       <c r="G234" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H234" t="s">
         <v>744</v>
       </c>
       <c r="I234" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J234" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K234" t="s">
+        <v>32</v>
       </c>
       <c r="L234" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -11237,10 +11237,7 @@
         <v>739</v>
       </c>
       <c r="D235" t="s">
-        <v>15</v>
-      </c>
-      <c r="E235" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F235" t="s">
         <v>746</v>
@@ -11252,13 +11249,16 @@
         <v>747</v>
       </c>
       <c r="I235" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J235" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K235" t="s">
+        <v>32</v>
       </c>
       <c r="L235" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -11272,10 +11272,7 @@
         <v>739</v>
       </c>
       <c r="D236" t="s">
-        <v>15</v>
-      </c>
-      <c r="E236" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F236" t="s">
         <v>749</v>
@@ -11287,13 +11284,16 @@
         <v>750</v>
       </c>
       <c r="I236" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J236" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K236" t="s">
+        <v>32</v>
       </c>
       <c r="L236" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -11307,10 +11307,7 @@
         <v>739</v>
       </c>
       <c r="D237" t="s">
-        <v>15</v>
-      </c>
-      <c r="E237" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F237" t="s">
         <v>752</v>
@@ -11322,13 +11319,16 @@
         <v>753</v>
       </c>
       <c r="I237" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J237" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K237" t="s">
+        <v>32</v>
       </c>
       <c r="L237" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -11342,10 +11342,7 @@
         <v>739</v>
       </c>
       <c r="D238" t="s">
-        <v>15</v>
-      </c>
-      <c r="E238" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F238" t="s">
         <v>755</v>
@@ -11357,13 +11354,16 @@
         <v>756</v>
       </c>
       <c r="I238" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J238" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K238" t="s">
+        <v>32</v>
       </c>
       <c r="L238" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -11377,10 +11377,7 @@
         <v>739</v>
       </c>
       <c r="D239" t="s">
-        <v>15</v>
-      </c>
-      <c r="E239" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F239" t="s">
         <v>758</v>
@@ -11392,13 +11389,16 @@
         <v>759</v>
       </c>
       <c r="I239" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J239" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K239" t="s">
+        <v>32</v>
       </c>
       <c r="L239" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -11412,10 +11412,7 @@
         <v>739</v>
       </c>
       <c r="D240" t="s">
-        <v>15</v>
-      </c>
-      <c r="E240" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F240" t="s">
         <v>761</v>
@@ -11427,13 +11424,16 @@
         <v>762</v>
       </c>
       <c r="I240" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J240" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K240" t="s">
+        <v>17</v>
       </c>
       <c r="L240" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="241" spans="1:12">
@@ -11447,10 +11447,7 @@
         <v>764</v>
       </c>
       <c r="D241" t="s">
-        <v>15</v>
-      </c>
-      <c r="E241" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F241" t="s">
         <v>765</v>
@@ -11462,13 +11459,16 @@
         <v>766</v>
       </c>
       <c r="I241" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J241" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K241" t="s">
+        <v>32</v>
       </c>
       <c r="L241" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="242" spans="1:12">
@@ -11482,10 +11482,7 @@
         <v>764</v>
       </c>
       <c r="D242" t="s">
-        <v>15</v>
-      </c>
-      <c r="E242" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F242" t="s">
         <v>768</v>
@@ -11497,13 +11494,16 @@
         <v>769</v>
       </c>
       <c r="I242" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J242" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K242" t="s">
+        <v>32</v>
       </c>
       <c r="L242" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -11517,10 +11517,7 @@
         <v>764</v>
       </c>
       <c r="D243" t="s">
-        <v>15</v>
-      </c>
-      <c r="E243" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F243" t="s">
         <v>771</v>
@@ -11532,13 +11529,16 @@
         <v>772</v>
       </c>
       <c r="I243" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J243" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K243" t="s">
+        <v>32</v>
       </c>
       <c r="L243" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="244" spans="1:12">
@@ -11552,10 +11552,7 @@
         <v>764</v>
       </c>
       <c r="D244" t="s">
-        <v>15</v>
-      </c>
-      <c r="E244" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F244" t="s">
         <v>774</v>
@@ -11567,13 +11564,16 @@
         <v>775</v>
       </c>
       <c r="I244" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J244" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K244" t="s">
+        <v>32</v>
       </c>
       <c r="L244" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="245" spans="1:12">
@@ -11587,10 +11587,7 @@
         <v>764</v>
       </c>
       <c r="D245" t="s">
-        <v>15</v>
-      </c>
-      <c r="E245" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F245" t="s">
         <v>777</v>
@@ -11602,13 +11599,16 @@
         <v>778</v>
       </c>
       <c r="I245" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J245" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K245" t="s">
+        <v>17</v>
       </c>
       <c r="L245" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="246" spans="1:12">
@@ -11622,10 +11622,7 @@
         <v>764</v>
       </c>
       <c r="D246" t="s">
-        <v>15</v>
-      </c>
-      <c r="E246" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F246" t="s">
         <v>780</v>
@@ -11637,13 +11634,16 @@
         <v>781</v>
       </c>
       <c r="I246" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J246" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K246" t="s">
+        <v>32</v>
       </c>
       <c r="L246" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -11657,10 +11657,7 @@
         <v>764</v>
       </c>
       <c r="D247" t="s">
-        <v>15</v>
-      </c>
-      <c r="E247" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F247" t="s">
         <v>783</v>
@@ -11672,13 +11669,16 @@
         <v>784</v>
       </c>
       <c r="I247" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J247" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K247" t="s">
+        <v>17</v>
       </c>
       <c r="L247" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="248" spans="1:12">
@@ -11692,10 +11692,7 @@
         <v>764</v>
       </c>
       <c r="D248" t="s">
-        <v>15</v>
-      </c>
-      <c r="E248" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F248" t="s">
         <v>786</v>
@@ -11707,13 +11704,16 @@
         <v>787</v>
       </c>
       <c r="I248" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J248" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K248" t="s">
+        <v>32</v>
       </c>
       <c r="L248" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249" spans="1:12">
@@ -11727,28 +11727,28 @@
         <v>764</v>
       </c>
       <c r="D249" t="s">
-        <v>31</v>
-      </c>
-      <c r="E249" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F249" t="s">
         <v>789</v>
       </c>
       <c r="G249" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H249" t="s">
         <v>790</v>
       </c>
       <c r="I249" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J249" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K249" t="s">
+        <v>32</v>
       </c>
       <c r="L249" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -11762,10 +11762,7 @@
         <v>764</v>
       </c>
       <c r="D250" t="s">
-        <v>15</v>
-      </c>
-      <c r="E250" t="s">
-        <v>15</v>
+        <v>704</v>
       </c>
       <c r="F250" t="s">
         <v>792</v>
@@ -11777,13 +11774,16 @@
         <v>793</v>
       </c>
       <c r="I250" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J250" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="K250" t="s">
+        <v>17</v>
       </c>
       <c r="L250" t="s">
-        <v>706</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/clv3/xlsx/pt/RegionM49.xlsx
+++ b/api/2/clv3/xlsx/pt/RegionM49.xlsx
@@ -22,63 +22,63 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>codeforiati:global-code</t>
+  </si>
+  <si>
     <t>codeforiati:intermediate-region-code</t>
   </si>
   <si>
+    <t>codeforiati:sub-region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:region-code</t>
+  </si>
+  <si>
+    <t>codeforiati:small-island-developing-states</t>
+  </si>
+  <si>
+    <t>codeforiati:least-developed-countries</t>
+  </si>
+  <si>
     <t>codeforiati:land-locked-developing-countries</t>
   </si>
   <si>
-    <t>codeforiati:least-developed-countries</t>
+    <t>codeforiati:iso-alpha-3-code</t>
   </si>
   <si>
     <t>codeforiati:developed-developing</t>
   </si>
   <si>
-    <t>codeforiati:iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>codeforiati:sub-region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:region-code</t>
-  </si>
-  <si>
-    <t>codeforiati:small-island-developing-states</t>
-  </si>
-  <si>
-    <t>codeforiati:iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>codeforiati:global-code</t>
-  </si>
-  <si>
     <t>012</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
+    <t>DZA</t>
+  </si>
+  <si>
     <t>Developing</t>
   </si>
   <si>
-    <t>DZ</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>DZA</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
     <t>818</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>729</t>
   </si>
   <si>
+    <t>SD</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
     <t>SDN</t>
   </si>
   <si>
@@ -139,12 +139,12 @@
     <t>086</t>
   </si>
   <si>
+    <t>IO</t>
+  </si>
+  <si>
     <t>014</t>
   </si>
   <si>
-    <t>IO</t>
-  </si>
-  <si>
     <t>202</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>024</t>
   </si>
   <si>
+    <t>AO</t>
+  </si>
+  <si>
     <t>017</t>
   </si>
   <si>
-    <t>AO</t>
-  </si>
-  <si>
     <t>AGO</t>
   </si>
   <si>
@@ -427,12 +427,12 @@
     <t>072</t>
   </si>
   <si>
+    <t>BW</t>
+  </si>
+  <si>
     <t>018</t>
   </si>
   <si>
-    <t>BW</t>
-  </si>
-  <si>
     <t>BWA</t>
   </si>
   <si>
@@ -475,12 +475,12 @@
     <t>204</t>
   </si>
   <si>
+    <t>BJ</t>
+  </si>
+  <si>
     <t>011</t>
   </si>
   <si>
-    <t>BJ</t>
-  </si>
-  <si>
     <t>BEN</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>660</t>
   </si>
   <si>
+    <t>AI</t>
+  </si>
+  <si>
     <t>029</t>
   </si>
   <si>
-    <t>AI</t>
-  </si>
-  <si>
     <t>419</t>
   </si>
   <si>
@@ -892,12 +892,12 @@
     <t>084</t>
   </si>
   <si>
+    <t>BZ</t>
+  </si>
+  <si>
     <t>013</t>
   </si>
   <si>
-    <t>BZ</t>
-  </si>
-  <si>
     <t>BLZ</t>
   </si>
   <si>
@@ -967,12 +967,12 @@
     <t>032</t>
   </si>
   <si>
+    <t>AR</t>
+  </si>
+  <si>
     <t>005</t>
   </si>
   <si>
-    <t>AR</t>
-  </si>
-  <si>
     <t>ARG</t>
   </si>
   <si>
@@ -1114,16 +1114,16 @@
     <t>060</t>
   </si>
   <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>BMU</t>
+  </si>
+  <si>
     <t>Developed</t>
-  </si>
-  <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>021</t>
-  </si>
-  <si>
-    <t>BMU</t>
   </si>
   <si>
     <t>124</t>
@@ -2775,26 +2775,26 @@
       <c r="B2" t="s">
         <v>13</v>
       </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
       <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
         <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
         <v>19</v>
@@ -2810,26 +2810,26 @@
       <c r="B3" t="s">
         <v>13</v>
       </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
       <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
         <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s">
         <v>23</v>
@@ -2845,26 +2845,26 @@
       <c r="B4" t="s">
         <v>13</v>
       </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
       <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K4" t="s">
         <v>26</v>
@@ -2880,26 +2880,26 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
       <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K5" t="s">
         <v>29</v>
@@ -2915,26 +2915,26 @@
       <c r="B6" t="s">
         <v>13</v>
       </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
       <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K6" t="s">
         <v>33</v>
@@ -2950,26 +2950,26 @@
       <c r="B7" t="s">
         <v>13</v>
       </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
       <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K7" t="s">
         <v>36</v>
@@ -2985,26 +2985,26 @@
       <c r="B8" t="s">
         <v>13</v>
       </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
       <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K8" t="s">
         <v>39</v>
@@ -3024,25 +3024,25 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
         <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
         <v>44</v>
@@ -3059,28 +3059,28 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K10" t="s">
         <v>47</v>
@@ -3097,28 +3097,28 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J11" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s">
         <v>50</v>
@@ -3135,28 +3135,28 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s">
         <v>53</v>
@@ -3173,28 +3173,28 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
         <v>56</v>
@@ -3211,28 +3211,28 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K14" t="s">
         <v>59</v>
@@ -3249,28 +3249,28 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G15" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
         <v>62</v>
@@ -3287,28 +3287,28 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
         <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s">
         <v>65</v>
@@ -3325,28 +3325,28 @@
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G17" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s">
         <v>68</v>
@@ -3363,28 +3363,28 @@
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K18" t="s">
         <v>71</v>
@@ -3401,28 +3401,28 @@
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I19" t="s">
         <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s">
         <v>74</v>
@@ -3439,28 +3439,28 @@
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
         <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K20" t="s">
         <v>77</v>
@@ -3477,28 +3477,28 @@
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K21" t="s">
         <v>80</v>
@@ -3515,28 +3515,28 @@
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
         <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s">
         <v>83</v>
@@ -3553,28 +3553,28 @@
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K23" t="s">
         <v>86</v>
@@ -3591,28 +3591,28 @@
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
       </c>
       <c r="J24" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K24" t="s">
         <v>89</v>
@@ -3629,28 +3629,28 @@
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s">
         <v>92</v>
@@ -3667,28 +3667,28 @@
         <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="H26" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J26" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K26" t="s">
         <v>95</v>
@@ -3705,28 +3705,28 @@
         <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F27" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K27" t="s">
         <v>98</v>
@@ -3743,28 +3743,28 @@
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J28" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K28" t="s">
         <v>101</v>
@@ -3781,28 +3781,28 @@
         <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G29" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J29" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K29" t="s">
         <v>104</v>
@@ -3819,28 +3819,28 @@
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
       </c>
       <c r="J30" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K30" t="s">
         <v>107</v>
@@ -3860,25 +3860,25 @@
         <v>109</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G31" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K31" t="s">
         <v>111</v>
@@ -3895,28 +3895,28 @@
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G32" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
         <v>18</v>
       </c>
       <c r="J32" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K32" t="s">
         <v>114</v>
@@ -3933,28 +3933,28 @@
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G33" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K33" t="s">
         <v>117</v>
@@ -3971,28 +3971,28 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="F34" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G34" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J34" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K34" t="s">
         <v>120</v>
@@ -4009,28 +4009,28 @@
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
         <v>18</v>
       </c>
       <c r="J35" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K35" t="s">
         <v>123</v>
@@ -4047,28 +4047,28 @@
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="F36" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J36" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K36" t="s">
         <v>126</v>
@@ -4085,28 +4085,28 @@
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="F37" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G37" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I37" t="s">
         <v>18</v>
       </c>
       <c r="J37" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K37" t="s">
         <v>129</v>
@@ -4123,28 +4123,28 @@
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="F38" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G38" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
         <v>18</v>
       </c>
       <c r="J38" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K38" t="s">
         <v>132</v>
@@ -4161,28 +4161,28 @@
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="F39" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G39" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="H39" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I39" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J39" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K39" t="s">
         <v>135</v>
@@ -4202,25 +4202,25 @@
         <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="F40" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G40" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
         <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K40" t="s">
         <v>139</v>
@@ -4237,28 +4237,28 @@
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="F41" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G41" t="s">
-        <v>141</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I41" t="s">
         <v>18</v>
       </c>
       <c r="J41" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K41" t="s">
         <v>142</v>
@@ -4275,28 +4275,28 @@
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="F42" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G42" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J42" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K42" t="s">
         <v>145</v>
@@ -4313,28 +4313,28 @@
         <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="F43" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G43" t="s">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="H43" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s">
         <v>18</v>
       </c>
       <c r="J43" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K43" t="s">
         <v>148</v>
@@ -4351,28 +4351,28 @@
         <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="F44" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G44" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s">
         <v>18</v>
       </c>
       <c r="J44" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K44" t="s">
         <v>151</v>
@@ -4392,25 +4392,25 @@
         <v>153</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F45" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G45" t="s">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J45" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K45" t="s">
         <v>155</v>
@@ -4427,28 +4427,28 @@
         <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F46" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G46" t="s">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J46" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K46" t="s">
         <v>158</v>
@@ -4465,28 +4465,28 @@
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G47" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I47" t="s">
         <v>18</v>
       </c>
       <c r="J47" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K47" t="s">
         <v>161</v>
@@ -4503,28 +4503,28 @@
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="F48" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G48" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
         <v>18</v>
       </c>
       <c r="J48" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K48" t="s">
         <v>164</v>
@@ -4541,28 +4541,28 @@
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F49" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G49" t="s">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J49" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K49" t="s">
         <v>167</v>
@@ -4579,28 +4579,28 @@
         <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="F50" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G50" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
         <v>18</v>
       </c>
       <c r="J50" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K50" t="s">
         <v>170</v>
@@ -4617,28 +4617,28 @@
         <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F51" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G51" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J51" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K51" t="s">
         <v>173</v>
@@ -4655,28 +4655,28 @@
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D52" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G52" t="s">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I52" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J52" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K52" t="s">
         <v>176</v>
@@ -4693,28 +4693,28 @@
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F53" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G53" t="s">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="H53" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J53" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K53" t="s">
         <v>179</v>
@@ -4731,28 +4731,28 @@
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G54" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J54" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K54" t="s">
         <v>182</v>
@@ -4769,28 +4769,28 @@
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G55" t="s">
-        <v>184</v>
+        <v>17</v>
       </c>
       <c r="H55" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J55" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K55" t="s">
         <v>185</v>
@@ -4807,28 +4807,28 @@
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F56" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G56" t="s">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J56" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K56" t="s">
         <v>188</v>
@@ -4845,28 +4845,28 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E57" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="F57" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G57" t="s">
-        <v>190</v>
+        <v>17</v>
       </c>
       <c r="H57" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s">
         <v>18</v>
       </c>
       <c r="J57" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K57" t="s">
         <v>191</v>
@@ -4883,28 +4883,28 @@
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E58" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="F58" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G58" t="s">
-        <v>193</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
       </c>
       <c r="J58" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K58" t="s">
         <v>194</v>
@@ -4921,28 +4921,28 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E59" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F59" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G59" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J59" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K59" t="s">
         <v>197</v>
@@ -4959,28 +4959,28 @@
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E60" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F60" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G60" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="H60" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J60" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K60" t="s">
         <v>200</v>
@@ -4997,28 +4997,28 @@
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>202</v>
       </c>
       <c r="D61" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="F61" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G61" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J61" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K61" t="s">
         <v>203</v>
@@ -5038,25 +5038,25 @@
         <v>205</v>
       </c>
       <c r="D62" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E62" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G62" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H62" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I62" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J62" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K62" t="s">
         <v>209</v>
@@ -5073,28 +5073,28 @@
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F63" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G63" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H63" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I63" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J63" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K63" t="s">
         <v>212</v>
@@ -5111,28 +5111,28 @@
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E64" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F64" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G64" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="H64" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I64" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J64" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K64" t="s">
         <v>215</v>
@@ -5149,28 +5149,28 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E65" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F65" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G65" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="H65" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I65" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J65" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K65" t="s">
         <v>218</v>
@@ -5187,28 +5187,28 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="D66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E66" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G66" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="H66" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I66" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K66" t="s">
         <v>221</v>
@@ -5225,28 +5225,28 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E67" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F67" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G67" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="H67" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I67" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J67" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K67" t="s">
         <v>224</v>
@@ -5263,28 +5263,28 @@
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="D68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E68" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F68" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G68" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="H68" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I68" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J68" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K68" t="s">
         <v>227</v>
@@ -5301,28 +5301,28 @@
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="D69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E69" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F69" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G69" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="H69" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J69" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K69" t="s">
         <v>230</v>
@@ -5339,28 +5339,28 @@
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E70" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F70" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G70" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="H70" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I70" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J70" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K70" t="s">
         <v>233</v>
@@ -5377,28 +5377,28 @@
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E71" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F71" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G71" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="H71" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I71" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J71" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K71" t="s">
         <v>236</v>
@@ -5415,28 +5415,28 @@
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>238</v>
       </c>
       <c r="D72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E72" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F72" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G72" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="H72" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I72" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J72" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K72" t="s">
         <v>239</v>
@@ -5453,28 +5453,28 @@
         <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="D73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E73" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F73" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G73" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="H73" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I73" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J73" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K73" t="s">
         <v>242</v>
@@ -5491,28 +5491,28 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="D74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E74" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F74" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G74" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="H74" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I74" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J74" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K74" t="s">
         <v>245</v>
@@ -5529,28 +5529,28 @@
         <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
+        <v>247</v>
       </c>
       <c r="D75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E75" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F75" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G75" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="H75" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J75" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K75" t="s">
         <v>248</v>
@@ -5567,28 +5567,28 @@
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>205</v>
+        <v>250</v>
       </c>
       <c r="D76" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E76" t="s">
-        <v>31</v>
+        <v>206</v>
       </c>
       <c r="F76" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G76" t="s">
-        <v>250</v>
+        <v>208</v>
       </c>
       <c r="H76" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I76" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="J76" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K76" t="s">
         <v>251</v>
@@ -5605,28 +5605,28 @@
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>205</v>
+        <v>253</v>
       </c>
       <c r="D77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E77" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F77" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G77" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="H77" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I77" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J77" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K77" t="s">
         <v>254</v>
@@ -5643,28 +5643,28 @@
         <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="D78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F78" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G78" t="s">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="H78" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J78" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K78" t="s">
         <v>257</v>
@@ -5681,28 +5681,28 @@
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E79" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F79" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G79" t="s">
-        <v>259</v>
+        <v>208</v>
       </c>
       <c r="H79" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I79" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J79" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K79" t="s">
         <v>260</v>
@@ -5719,28 +5719,28 @@
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>205</v>
+        <v>262</v>
       </c>
       <c r="D80" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E80" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F80" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G80" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="H80" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I80" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J80" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K80" t="s">
         <v>263</v>
@@ -5757,28 +5757,28 @@
         <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E81" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F81" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G81" t="s">
-        <v>265</v>
+        <v>208</v>
       </c>
       <c r="H81" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J81" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K81" t="s">
         <v>266</v>
@@ -5795,28 +5795,28 @@
         <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>205</v>
+        <v>268</v>
       </c>
       <c r="D82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E82" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F82" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G82" t="s">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="H82" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I82" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J82" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K82" t="s">
         <v>269</v>
@@ -5833,28 +5833,28 @@
         <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>205</v>
+        <v>271</v>
       </c>
       <c r="D83" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E83" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F83" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G83" t="s">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="H83" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I83" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J83" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K83" t="s">
         <v>272</v>
@@ -5871,28 +5871,28 @@
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E84" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F84" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G84" t="s">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="H84" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J84" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K84" t="s">
         <v>275</v>
@@ -5909,28 +5909,28 @@
         <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>205</v>
+        <v>277</v>
       </c>
       <c r="D85" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E85" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F85" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G85" t="s">
-        <v>277</v>
+        <v>208</v>
       </c>
       <c r="H85" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I85" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J85" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K85" t="s">
         <v>278</v>
@@ -5947,28 +5947,28 @@
         <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>205</v>
+        <v>280</v>
       </c>
       <c r="D86" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E86" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F86" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G86" t="s">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H86" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I86" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J86" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K86" t="s">
         <v>281</v>
@@ -5985,28 +5985,28 @@
         <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>205</v>
+        <v>283</v>
       </c>
       <c r="D87" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E87" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F87" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G87" t="s">
-        <v>283</v>
+        <v>208</v>
       </c>
       <c r="H87" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I87" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J87" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K87" t="s">
         <v>284</v>
@@ -6023,28 +6023,28 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>205</v>
+        <v>286</v>
       </c>
       <c r="D88" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E88" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F88" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G88" t="s">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="H88" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J88" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K88" t="s">
         <v>287</v>
@@ -6061,28 +6061,28 @@
         <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>205</v>
+        <v>289</v>
       </c>
       <c r="D89" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E89" t="s">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F89" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G89" t="s">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="H89" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I89" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J89" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K89" t="s">
         <v>290</v>
@@ -6102,25 +6102,25 @@
         <v>292</v>
       </c>
       <c r="D90" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E90" t="s">
-        <v>14</v>
+        <v>293</v>
       </c>
       <c r="F90" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G90" t="s">
-        <v>293</v>
+        <v>208</v>
       </c>
       <c r="H90" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I90" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J90" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K90" t="s">
         <v>294</v>
@@ -6137,28 +6137,28 @@
         <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D91" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E91" t="s">
-        <v>14</v>
+        <v>293</v>
       </c>
       <c r="F91" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G91" t="s">
-        <v>296</v>
+        <v>208</v>
       </c>
       <c r="H91" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J91" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K91" t="s">
         <v>297</v>
@@ -6175,28 +6175,28 @@
         <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="D92" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E92" t="s">
-        <v>14</v>
+        <v>293</v>
       </c>
       <c r="F92" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G92" t="s">
-        <v>299</v>
+        <v>208</v>
       </c>
       <c r="H92" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J92" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K92" t="s">
         <v>300</v>
@@ -6213,28 +6213,28 @@
         <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="D93" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E93" t="s">
-        <v>14</v>
+        <v>293</v>
       </c>
       <c r="F93" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G93" t="s">
-        <v>302</v>
+        <v>208</v>
       </c>
       <c r="H93" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J93" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K93" t="s">
         <v>303</v>
@@ -6251,28 +6251,28 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E94" t="s">
-        <v>14</v>
+        <v>293</v>
       </c>
       <c r="F94" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G94" t="s">
-        <v>305</v>
+        <v>208</v>
       </c>
       <c r="H94" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J94" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K94" t="s">
         <v>306</v>
@@ -6289,28 +6289,28 @@
         <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="D95" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E95" t="s">
-        <v>14</v>
+        <v>293</v>
       </c>
       <c r="F95" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G95" t="s">
-        <v>308</v>
+        <v>208</v>
       </c>
       <c r="H95" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I95" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J95" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K95" t="s">
         <v>309</v>
@@ -6327,28 +6327,28 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="D96" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E96" t="s">
-        <v>14</v>
+        <v>293</v>
       </c>
       <c r="F96" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G96" t="s">
-        <v>311</v>
+        <v>208</v>
       </c>
       <c r="H96" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J96" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K96" t="s">
         <v>312</v>
@@ -6365,28 +6365,28 @@
         <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="D97" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E97" t="s">
-        <v>14</v>
+        <v>293</v>
       </c>
       <c r="F97" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G97" t="s">
-        <v>314</v>
+        <v>208</v>
       </c>
       <c r="H97" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J97" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K97" t="s">
         <v>315</v>
@@ -6406,25 +6406,25 @@
         <v>317</v>
       </c>
       <c r="D98" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E98" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F98" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G98" t="s">
-        <v>318</v>
+        <v>208</v>
       </c>
       <c r="H98" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J98" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K98" t="s">
         <v>319</v>
@@ -6441,28 +6441,28 @@
         <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D99" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E99" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F99" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G99" t="s">
-        <v>321</v>
+        <v>208</v>
       </c>
       <c r="H99" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J99" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K99" t="s">
         <v>322</v>
@@ -6479,28 +6479,28 @@
         <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D100" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E100" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F100" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G100" t="s">
-        <v>324</v>
+        <v>208</v>
       </c>
       <c r="H100" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J100" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K100" t="s">
         <v>325</v>
@@ -6517,28 +6517,28 @@
         <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="D101" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E101" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F101" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G101" t="s">
-        <v>327</v>
+        <v>208</v>
       </c>
       <c r="H101" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J101" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K101" t="s">
         <v>328</v>
@@ -6555,28 +6555,28 @@
         <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D102" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E102" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F102" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G102" t="s">
-        <v>330</v>
+        <v>208</v>
       </c>
       <c r="H102" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I102" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J102" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K102" t="s">
         <v>331</v>
@@ -6593,28 +6593,28 @@
         <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="D103" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E103" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F103" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G103" t="s">
-        <v>333</v>
+        <v>208</v>
       </c>
       <c r="H103" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J103" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K103" t="s">
         <v>334</v>
@@ -6631,28 +6631,28 @@
         <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="D104" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E104" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F104" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G104" t="s">
-        <v>336</v>
+        <v>208</v>
       </c>
       <c r="H104" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J104" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K104" t="s">
         <v>337</v>
@@ -6669,28 +6669,28 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="D105" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E105" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F105" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G105" t="s">
-        <v>339</v>
+        <v>208</v>
       </c>
       <c r="H105" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J105" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K105" t="s">
         <v>340</v>
@@ -6707,28 +6707,28 @@
         <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="D106" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E106" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F106" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G106" t="s">
-        <v>342</v>
+        <v>208</v>
       </c>
       <c r="H106" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I106" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J106" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K106" t="s">
         <v>343</v>
@@ -6745,28 +6745,28 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="D107" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E107" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F107" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G107" t="s">
-        <v>345</v>
+        <v>208</v>
       </c>
       <c r="H107" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I107" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J107" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K107" t="s">
         <v>346</v>
@@ -6783,28 +6783,28 @@
         <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="D108" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E108" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F108" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G108" t="s">
-        <v>348</v>
+        <v>208</v>
       </c>
       <c r="H108" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J108" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K108" t="s">
         <v>349</v>
@@ -6821,28 +6821,28 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="D109" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E109" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F109" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G109" t="s">
-        <v>351</v>
+        <v>208</v>
       </c>
       <c r="H109" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J109" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K109" t="s">
         <v>352</v>
@@ -6859,28 +6859,28 @@
         <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="D110" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E110" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F110" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G110" t="s">
-        <v>354</v>
+        <v>208</v>
       </c>
       <c r="H110" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J110" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K110" t="s">
         <v>355</v>
@@ -6897,28 +6897,28 @@
         <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="D111" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E111" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F111" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G111" t="s">
-        <v>357</v>
+        <v>208</v>
       </c>
       <c r="H111" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="I111" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J111" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K111" t="s">
         <v>358</v>
@@ -6935,28 +6935,28 @@
         <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="D112" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E112" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F112" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G112" t="s">
-        <v>360</v>
+        <v>208</v>
       </c>
       <c r="H112" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J112" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K112" t="s">
         <v>361</v>
@@ -6973,28 +6973,28 @@
         <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>317</v>
+        <v>363</v>
       </c>
       <c r="D113" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E113" t="s">
-        <v>14</v>
+        <v>318</v>
       </c>
       <c r="F113" t="s">
-        <v>15</v>
+        <v>207</v>
       </c>
       <c r="G113" t="s">
-        <v>363</v>
+        <v>208</v>
       </c>
       <c r="H113" t="s">
-        <v>207</v>
+        <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J113" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K113" t="s">
         <v>364</v>
@@ -7010,32 +7010,32 @@
       <c r="B114" t="s">
         <v>13</v>
       </c>
+      <c r="C114" t="s">
+        <v>366</v>
+      </c>
       <c r="D114" t="s">
-        <v>14</v>
-      </c>
-      <c r="E114" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F114" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G114" t="s">
-        <v>367</v>
+        <v>208</v>
       </c>
       <c r="H114" t="s">
+        <v>18</v>
+      </c>
+      <c r="I114" t="s">
+        <v>18</v>
+      </c>
+      <c r="J114" t="s">
+        <v>18</v>
+      </c>
+      <c r="K114" t="s">
         <v>368</v>
       </c>
-      <c r="I114" t="s">
-        <v>208</v>
-      </c>
-      <c r="J114" t="s">
-        <v>14</v>
-      </c>
-      <c r="K114" t="s">
+      <c r="L114" t="s">
         <v>369</v>
-      </c>
-      <c r="L114" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -7045,32 +7045,32 @@
       <c r="B115" t="s">
         <v>13</v>
       </c>
+      <c r="C115" t="s">
+        <v>371</v>
+      </c>
       <c r="D115" t="s">
-        <v>14</v>
-      </c>
-      <c r="E115" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F115" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G115" t="s">
-        <v>371</v>
+        <v>208</v>
       </c>
       <c r="H115" t="s">
-        <v>368</v>
+        <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J115" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K115" t="s">
         <v>372</v>
       </c>
       <c r="L115" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -7080,32 +7080,32 @@
       <c r="B116" t="s">
         <v>13</v>
       </c>
+      <c r="C116" t="s">
+        <v>374</v>
+      </c>
       <c r="D116" t="s">
-        <v>14</v>
-      </c>
-      <c r="E116" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F116" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G116" t="s">
-        <v>374</v>
+        <v>208</v>
       </c>
       <c r="H116" t="s">
-        <v>368</v>
+        <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J116" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K116" t="s">
         <v>375</v>
       </c>
       <c r="L116" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -7115,32 +7115,32 @@
       <c r="B117" t="s">
         <v>13</v>
       </c>
+      <c r="C117" t="s">
+        <v>377</v>
+      </c>
       <c r="D117" t="s">
-        <v>14</v>
-      </c>
-      <c r="E117" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F117" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G117" t="s">
-        <v>377</v>
+        <v>208</v>
       </c>
       <c r="H117" t="s">
-        <v>368</v>
+        <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J117" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K117" t="s">
         <v>378</v>
       </c>
       <c r="L117" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -7150,32 +7150,32 @@
       <c r="B118" t="s">
         <v>13</v>
       </c>
+      <c r="C118" t="s">
+        <v>380</v>
+      </c>
       <c r="D118" t="s">
-        <v>14</v>
-      </c>
-      <c r="E118" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F118" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G118" t="s">
-        <v>380</v>
+        <v>208</v>
       </c>
       <c r="H118" t="s">
-        <v>368</v>
+        <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J118" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K118" t="s">
         <v>381</v>
       </c>
       <c r="L118" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -7185,23 +7185,23 @@
       <c r="B119" t="s">
         <v>13</v>
       </c>
+      <c r="C119" t="s">
+        <v>383</v>
+      </c>
       <c r="D119" t="s">
-        <v>14</v>
-      </c>
-      <c r="E119" t="s">
-        <v>14</v>
-      </c>
-      <c r="G119" t="s">
-        <v>383</v>
+        <v>15</v>
+      </c>
+      <c r="H119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" t="s">
+        <v>18</v>
       </c>
       <c r="J119" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K119" t="s">
         <v>384</v>
-      </c>
-      <c r="L119" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -7211,26 +7211,26 @@
       <c r="B120" t="s">
         <v>13</v>
       </c>
+      <c r="C120" t="s">
+        <v>386</v>
+      </c>
       <c r="D120" t="s">
-        <v>31</v>
-      </c>
-      <c r="E120" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F120" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="G120" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H120" t="s">
-        <v>387</v>
+        <v>18</v>
       </c>
       <c r="I120" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J120" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K120" t="s">
         <v>389</v>
@@ -7246,26 +7246,26 @@
       <c r="B121" t="s">
         <v>13</v>
       </c>
+      <c r="C121" t="s">
+        <v>391</v>
+      </c>
       <c r="D121" t="s">
-        <v>31</v>
-      </c>
-      <c r="E121" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F121" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="G121" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H121" t="s">
-        <v>387</v>
+        <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J121" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K121" t="s">
         <v>392</v>
@@ -7281,26 +7281,26 @@
       <c r="B122" t="s">
         <v>13</v>
       </c>
+      <c r="C122" t="s">
+        <v>394</v>
+      </c>
       <c r="D122" t="s">
-        <v>31</v>
-      </c>
-      <c r="E122" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F122" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="G122" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H122" t="s">
-        <v>387</v>
+        <v>18</v>
       </c>
       <c r="I122" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J122" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K122" t="s">
         <v>395</v>
@@ -7316,26 +7316,26 @@
       <c r="B123" t="s">
         <v>13</v>
       </c>
+      <c r="C123" t="s">
+        <v>397</v>
+      </c>
       <c r="D123" t="s">
-        <v>31</v>
-      </c>
-      <c r="E123" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F123" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="G123" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="H123" t="s">
-        <v>387</v>
+        <v>18</v>
       </c>
       <c r="I123" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J123" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K123" t="s">
         <v>398</v>
@@ -7351,26 +7351,26 @@
       <c r="B124" t="s">
         <v>13</v>
       </c>
+      <c r="C124" t="s">
+        <v>400</v>
+      </c>
       <c r="D124" t="s">
-        <v>31</v>
-      </c>
-      <c r="E124" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F124" t="s">
-        <v>15</v>
+        <v>387</v>
       </c>
       <c r="G124" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="H124" t="s">
-        <v>387</v>
+        <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J124" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K124" t="s">
         <v>401</v>
@@ -7386,26 +7386,26 @@
       <c r="B125" t="s">
         <v>13</v>
       </c>
+      <c r="C125" t="s">
+        <v>403</v>
+      </c>
       <c r="D125" t="s">
-        <v>14</v>
-      </c>
-      <c r="E125" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>15</v>
+        <v>404</v>
       </c>
       <c r="G125" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="H125" t="s">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="I125" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J125" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K125" t="s">
         <v>405</v>
@@ -7421,26 +7421,26 @@
       <c r="B126" t="s">
         <v>13</v>
       </c>
+      <c r="C126" t="s">
+        <v>407</v>
+      </c>
       <c r="D126" t="s">
-        <v>14</v>
-      </c>
-      <c r="E126" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F126" t="s">
-        <v>15</v>
+        <v>404</v>
       </c>
       <c r="G126" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="H126" t="s">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="I126" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J126" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K126" t="s">
         <v>408</v>
@@ -7456,26 +7456,26 @@
       <c r="B127" t="s">
         <v>13</v>
       </c>
+      <c r="C127" t="s">
+        <v>410</v>
+      </c>
       <c r="D127" t="s">
-        <v>14</v>
-      </c>
-      <c r="E127" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F127" t="s">
-        <v>15</v>
+        <v>404</v>
       </c>
       <c r="G127" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="H127" t="s">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="I127" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J127" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K127" t="s">
         <v>411</v>
@@ -7491,26 +7491,26 @@
       <c r="B128" t="s">
         <v>13</v>
       </c>
+      <c r="C128" t="s">
+        <v>413</v>
+      </c>
       <c r="D128" t="s">
-        <v>14</v>
-      </c>
-      <c r="E128" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F128" t="s">
-        <v>15</v>
+        <v>404</v>
       </c>
       <c r="G128" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="H128" t="s">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="I128" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J128" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K128" t="s">
         <v>414</v>
@@ -7526,32 +7526,32 @@
       <c r="B129" t="s">
         <v>13</v>
       </c>
+      <c r="C129" t="s">
+        <v>416</v>
+      </c>
       <c r="D129" t="s">
-        <v>14</v>
-      </c>
-      <c r="E129" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F129" t="s">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="G129" t="s">
-        <v>416</v>
+        <v>388</v>
       </c>
       <c r="H129" t="s">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="I129" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J129" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K129" t="s">
         <v>417</v>
       </c>
       <c r="L129" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -7561,26 +7561,26 @@
       <c r="B130" t="s">
         <v>13</v>
       </c>
+      <c r="C130" t="s">
+        <v>419</v>
+      </c>
       <c r="D130" t="s">
-        <v>31</v>
-      </c>
-      <c r="E130" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F130" t="s">
-        <v>15</v>
+        <v>404</v>
       </c>
       <c r="G130" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="H130" t="s">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J130" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K130" t="s">
         <v>420</v>
@@ -7596,26 +7596,26 @@
       <c r="B131" t="s">
         <v>13</v>
       </c>
+      <c r="C131" t="s">
+        <v>422</v>
+      </c>
       <c r="D131" t="s">
-        <v>14</v>
-      </c>
-      <c r="E131" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F131" t="s">
-        <v>15</v>
+        <v>404</v>
       </c>
       <c r="G131" t="s">
-        <v>422</v>
+        <v>388</v>
       </c>
       <c r="H131" t="s">
-        <v>404</v>
+        <v>18</v>
       </c>
       <c r="I131" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J131" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K131" t="s">
         <v>423</v>
@@ -7631,26 +7631,26 @@
       <c r="B132" t="s">
         <v>13</v>
       </c>
+      <c r="C132" t="s">
+        <v>425</v>
+      </c>
       <c r="D132" t="s">
-        <v>14</v>
-      </c>
-      <c r="E132" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F132" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G132" t="s">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="H132" t="s">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="I132" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J132" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K132" t="s">
         <v>427</v>
@@ -7666,26 +7666,26 @@
       <c r="B133" t="s">
         <v>13</v>
       </c>
+      <c r="C133" t="s">
+        <v>429</v>
+      </c>
       <c r="D133" t="s">
-        <v>14</v>
-      </c>
-      <c r="E133" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F133" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G133" t="s">
-        <v>429</v>
+        <v>388</v>
       </c>
       <c r="H133" t="s">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="I133" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="J133" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K133" t="s">
         <v>430</v>
@@ -7701,26 +7701,26 @@
       <c r="B134" t="s">
         <v>13</v>
       </c>
+      <c r="C134" t="s">
+        <v>432</v>
+      </c>
       <c r="D134" t="s">
-        <v>14</v>
-      </c>
-      <c r="E134" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F134" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G134" t="s">
-        <v>432</v>
+        <v>388</v>
       </c>
       <c r="H134" t="s">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="I134" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J134" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K134" t="s">
         <v>433</v>
@@ -7736,26 +7736,26 @@
       <c r="B135" t="s">
         <v>13</v>
       </c>
+      <c r="C135" t="s">
+        <v>435</v>
+      </c>
       <c r="D135" t="s">
-        <v>31</v>
-      </c>
-      <c r="E135" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F135" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G135" t="s">
-        <v>435</v>
+        <v>388</v>
       </c>
       <c r="H135" t="s">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="I135" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="J135" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K135" t="s">
         <v>436</v>
@@ -7771,26 +7771,26 @@
       <c r="B136" t="s">
         <v>13</v>
       </c>
+      <c r="C136" t="s">
+        <v>438</v>
+      </c>
       <c r="D136" t="s">
-        <v>14</v>
-      </c>
-      <c r="E136" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F136" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G136" t="s">
-        <v>438</v>
+        <v>388</v>
       </c>
       <c r="H136" t="s">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="I136" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J136" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K136" t="s">
         <v>439</v>
@@ -7806,26 +7806,26 @@
       <c r="B137" t="s">
         <v>13</v>
       </c>
+      <c r="C137" t="s">
+        <v>441</v>
+      </c>
       <c r="D137" t="s">
-        <v>14</v>
-      </c>
-      <c r="E137" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G137" t="s">
-        <v>441</v>
+        <v>388</v>
       </c>
       <c r="H137" t="s">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="J137" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K137" t="s">
         <v>442</v>
@@ -7841,26 +7841,26 @@
       <c r="B138" t="s">
         <v>13</v>
       </c>
+      <c r="C138" t="s">
+        <v>444</v>
+      </c>
       <c r="D138" t="s">
-        <v>14</v>
-      </c>
-      <c r="E138" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F138" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G138" t="s">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="H138" t="s">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="I138" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J138" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K138" t="s">
         <v>445</v>
@@ -7876,26 +7876,26 @@
       <c r="B139" t="s">
         <v>13</v>
       </c>
+      <c r="C139" t="s">
+        <v>447</v>
+      </c>
       <c r="D139" t="s">
-        <v>14</v>
-      </c>
-      <c r="E139" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F139" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G139" t="s">
-        <v>447</v>
+        <v>388</v>
       </c>
       <c r="H139" t="s">
-        <v>426</v>
+        <v>32</v>
       </c>
       <c r="I139" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J139" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K139" t="s">
         <v>448</v>
@@ -7911,26 +7911,26 @@
       <c r="B140" t="s">
         <v>13</v>
       </c>
+      <c r="C140" t="s">
+        <v>450</v>
+      </c>
       <c r="D140" t="s">
-        <v>14</v>
-      </c>
-      <c r="E140" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F140" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G140" t="s">
-        <v>450</v>
+        <v>388</v>
       </c>
       <c r="H140" t="s">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="I140" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J140" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K140" t="s">
         <v>451</v>
@@ -7946,26 +7946,26 @@
       <c r="B141" t="s">
         <v>13</v>
       </c>
+      <c r="C141" t="s">
+        <v>453</v>
+      </c>
       <c r="D141" t="s">
-        <v>14</v>
-      </c>
-      <c r="E141" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F141" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G141" t="s">
-        <v>453</v>
+        <v>388</v>
       </c>
       <c r="H141" t="s">
-        <v>426</v>
+        <v>32</v>
       </c>
       <c r="I141" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="J141" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K141" t="s">
         <v>454</v>
@@ -7981,26 +7981,26 @@
       <c r="B142" t="s">
         <v>13</v>
       </c>
+      <c r="C142" t="s">
+        <v>456</v>
+      </c>
       <c r="D142" t="s">
-        <v>14</v>
-      </c>
-      <c r="E142" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F142" t="s">
-        <v>15</v>
+        <v>426</v>
       </c>
       <c r="G142" t="s">
-        <v>456</v>
+        <v>388</v>
       </c>
       <c r="H142" t="s">
-        <v>426</v>
+        <v>18</v>
       </c>
       <c r="I142" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J142" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K142" t="s">
         <v>457</v>
@@ -8016,26 +8016,26 @@
       <c r="B143" t="s">
         <v>13</v>
       </c>
+      <c r="C143" t="s">
+        <v>459</v>
+      </c>
       <c r="D143" t="s">
-        <v>31</v>
-      </c>
-      <c r="E143" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F143" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G143" t="s">
-        <v>459</v>
+        <v>388</v>
       </c>
       <c r="H143" t="s">
-        <v>460</v>
+        <v>18</v>
       </c>
       <c r="I143" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="J143" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K143" t="s">
         <v>461</v>
@@ -8051,26 +8051,26 @@
       <c r="B144" t="s">
         <v>13</v>
       </c>
+      <c r="C144" t="s">
+        <v>463</v>
+      </c>
       <c r="D144" t="s">
-        <v>14</v>
-      </c>
-      <c r="E144" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F144" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G144" t="s">
-        <v>463</v>
+        <v>388</v>
       </c>
       <c r="H144" t="s">
-        <v>460</v>
+        <v>18</v>
       </c>
       <c r="I144" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="J144" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K144" t="s">
         <v>464</v>
@@ -8086,26 +8086,26 @@
       <c r="B145" t="s">
         <v>13</v>
       </c>
+      <c r="C145" t="s">
+        <v>466</v>
+      </c>
       <c r="D145" t="s">
-        <v>31</v>
-      </c>
-      <c r="E145" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F145" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G145" t="s">
-        <v>466</v>
+        <v>388</v>
       </c>
       <c r="H145" t="s">
-        <v>460</v>
+        <v>18</v>
       </c>
       <c r="I145" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="J145" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K145" t="s">
         <v>467</v>
@@ -8121,26 +8121,26 @@
       <c r="B146" t="s">
         <v>13</v>
       </c>
+      <c r="C146" t="s">
+        <v>469</v>
+      </c>
       <c r="D146" t="s">
-        <v>14</v>
-      </c>
-      <c r="E146" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F146" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G146" t="s">
-        <v>469</v>
+        <v>388</v>
       </c>
       <c r="H146" t="s">
-        <v>460</v>
+        <v>18</v>
       </c>
       <c r="I146" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J146" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K146" t="s">
         <v>470</v>
@@ -8156,26 +8156,26 @@
       <c r="B147" t="s">
         <v>13</v>
       </c>
+      <c r="C147" t="s">
+        <v>472</v>
+      </c>
       <c r="D147" t="s">
-        <v>14</v>
-      </c>
-      <c r="E147" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F147" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G147" t="s">
-        <v>472</v>
+        <v>388</v>
       </c>
       <c r="H147" t="s">
-        <v>460</v>
+        <v>18</v>
       </c>
       <c r="I147" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J147" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K147" t="s">
         <v>473</v>
@@ -8191,26 +8191,26 @@
       <c r="B148" t="s">
         <v>13</v>
       </c>
+      <c r="C148" t="s">
+        <v>475</v>
+      </c>
       <c r="D148" t="s">
-        <v>14</v>
-      </c>
-      <c r="E148" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F148" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G148" t="s">
-        <v>475</v>
+        <v>388</v>
       </c>
       <c r="H148" t="s">
-        <v>460</v>
+        <v>32</v>
       </c>
       <c r="I148" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J148" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K148" t="s">
         <v>476</v>
@@ -8226,26 +8226,26 @@
       <c r="B149" t="s">
         <v>13</v>
       </c>
+      <c r="C149" t="s">
+        <v>478</v>
+      </c>
       <c r="D149" t="s">
-        <v>31</v>
-      </c>
-      <c r="E149" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F149" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G149" t="s">
-        <v>478</v>
+        <v>388</v>
       </c>
       <c r="H149" t="s">
-        <v>460</v>
+        <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="J149" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K149" t="s">
         <v>479</v>
@@ -8261,26 +8261,26 @@
       <c r="B150" t="s">
         <v>13</v>
       </c>
+      <c r="C150" t="s">
+        <v>481</v>
+      </c>
       <c r="D150" t="s">
-        <v>14</v>
-      </c>
-      <c r="E150" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F150" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G150" t="s">
-        <v>481</v>
+        <v>388</v>
       </c>
       <c r="H150" t="s">
-        <v>460</v>
+        <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J150" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K150" t="s">
         <v>482</v>
@@ -8296,26 +8296,26 @@
       <c r="B151" t="s">
         <v>13</v>
       </c>
+      <c r="C151" t="s">
+        <v>484</v>
+      </c>
       <c r="D151" t="s">
-        <v>14</v>
-      </c>
-      <c r="E151" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F151" t="s">
-        <v>15</v>
+        <v>460</v>
       </c>
       <c r="G151" t="s">
-        <v>484</v>
+        <v>388</v>
       </c>
       <c r="H151" t="s">
-        <v>460</v>
+        <v>18</v>
       </c>
       <c r="I151" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J151" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K151" t="s">
         <v>485</v>
@@ -8331,26 +8331,26 @@
       <c r="B152" t="s">
         <v>13</v>
       </c>
+      <c r="C152" t="s">
+        <v>487</v>
+      </c>
       <c r="D152" t="s">
-        <v>31</v>
-      </c>
-      <c r="E152" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F152" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G152" t="s">
-        <v>487</v>
+        <v>388</v>
       </c>
       <c r="H152" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J152" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K152" t="s">
         <v>489</v>
@@ -8366,26 +8366,26 @@
       <c r="B153" t="s">
         <v>13</v>
       </c>
+      <c r="C153" t="s">
+        <v>491</v>
+      </c>
       <c r="D153" t="s">
-        <v>31</v>
-      </c>
-      <c r="E153" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F153" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G153" t="s">
-        <v>491</v>
+        <v>388</v>
       </c>
       <c r="H153" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I153" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J153" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K153" t="s">
         <v>492</v>
@@ -8401,26 +8401,26 @@
       <c r="B154" t="s">
         <v>13</v>
       </c>
+      <c r="C154" t="s">
+        <v>494</v>
+      </c>
       <c r="D154" t="s">
-        <v>14</v>
-      </c>
-      <c r="E154" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F154" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G154" t="s">
-        <v>494</v>
+        <v>388</v>
       </c>
       <c r="H154" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I154" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J154" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K154" t="s">
         <v>495</v>
@@ -8436,32 +8436,32 @@
       <c r="B155" t="s">
         <v>13</v>
       </c>
+      <c r="C155" t="s">
+        <v>497</v>
+      </c>
       <c r="D155" t="s">
-        <v>14</v>
-      </c>
-      <c r="E155" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F155" t="s">
-        <v>366</v>
+        <v>488</v>
       </c>
       <c r="G155" t="s">
-        <v>497</v>
+        <v>388</v>
       </c>
       <c r="H155" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I155" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J155" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K155" t="s">
         <v>498</v>
       </c>
       <c r="L155" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -8471,26 +8471,26 @@
       <c r="B156" t="s">
         <v>13</v>
       </c>
+      <c r="C156" t="s">
+        <v>500</v>
+      </c>
       <c r="D156" t="s">
-        <v>14</v>
-      </c>
-      <c r="E156" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F156" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G156" t="s">
-        <v>500</v>
+        <v>388</v>
       </c>
       <c r="H156" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J156" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K156" t="s">
         <v>501</v>
@@ -8506,26 +8506,26 @@
       <c r="B157" t="s">
         <v>13</v>
       </c>
+      <c r="C157" t="s">
+        <v>503</v>
+      </c>
       <c r="D157" t="s">
-        <v>14</v>
-      </c>
-      <c r="E157" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F157" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G157" t="s">
-        <v>503</v>
+        <v>388</v>
       </c>
       <c r="H157" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I157" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J157" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K157" t="s">
         <v>504</v>
@@ -8541,32 +8541,32 @@
       <c r="B158" t="s">
         <v>13</v>
       </c>
+      <c r="C158" t="s">
+        <v>506</v>
+      </c>
       <c r="D158" t="s">
-        <v>14</v>
-      </c>
-      <c r="E158" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F158" t="s">
-        <v>366</v>
+        <v>488</v>
       </c>
       <c r="G158" t="s">
-        <v>506</v>
+        <v>388</v>
       </c>
       <c r="H158" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J158" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K158" t="s">
         <v>507</v>
       </c>
       <c r="L158" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="159" spans="1:12">
@@ -8576,26 +8576,26 @@
       <c r="B159" t="s">
         <v>13</v>
       </c>
+      <c r="C159" t="s">
+        <v>509</v>
+      </c>
       <c r="D159" t="s">
-        <v>14</v>
-      </c>
-      <c r="E159" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F159" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G159" t="s">
-        <v>509</v>
+        <v>388</v>
       </c>
       <c r="H159" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J159" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K159" t="s">
         <v>510</v>
@@ -8611,26 +8611,26 @@
       <c r="B160" t="s">
         <v>13</v>
       </c>
+      <c r="C160" t="s">
+        <v>512</v>
+      </c>
       <c r="D160" t="s">
-        <v>14</v>
-      </c>
-      <c r="E160" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F160" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G160" t="s">
-        <v>512</v>
+        <v>388</v>
       </c>
       <c r="H160" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I160" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J160" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K160" t="s">
         <v>513</v>
@@ -8646,26 +8646,26 @@
       <c r="B161" t="s">
         <v>13</v>
       </c>
+      <c r="C161" t="s">
+        <v>515</v>
+      </c>
       <c r="D161" t="s">
-        <v>14</v>
-      </c>
-      <c r="E161" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F161" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G161" t="s">
-        <v>515</v>
+        <v>388</v>
       </c>
       <c r="H161" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I161" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J161" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K161" t="s">
         <v>516</v>
@@ -8681,26 +8681,26 @@
       <c r="B162" t="s">
         <v>13</v>
       </c>
+      <c r="C162" t="s">
+        <v>518</v>
+      </c>
       <c r="D162" t="s">
-        <v>14</v>
-      </c>
-      <c r="E162" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F162" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G162" t="s">
-        <v>518</v>
+        <v>388</v>
       </c>
       <c r="H162" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I162" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J162" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K162" t="s">
         <v>519</v>
@@ -8716,26 +8716,26 @@
       <c r="B163" t="s">
         <v>13</v>
       </c>
+      <c r="C163" t="s">
+        <v>521</v>
+      </c>
       <c r="D163" t="s">
-        <v>14</v>
-      </c>
-      <c r="E163" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F163" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G163" t="s">
-        <v>521</v>
+        <v>388</v>
       </c>
       <c r="H163" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I163" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J163" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K163" t="s">
         <v>522</v>
@@ -8751,26 +8751,26 @@
       <c r="B164" t="s">
         <v>13</v>
       </c>
+      <c r="C164" t="s">
+        <v>524</v>
+      </c>
       <c r="D164" t="s">
-        <v>14</v>
-      </c>
-      <c r="E164" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F164" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G164" t="s">
-        <v>524</v>
+        <v>388</v>
       </c>
       <c r="H164" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I164" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J164" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K164" t="s">
         <v>525</v>
@@ -8786,26 +8786,26 @@
       <c r="B165" t="s">
         <v>13</v>
       </c>
+      <c r="C165" t="s">
+        <v>527</v>
+      </c>
       <c r="D165" t="s">
-        <v>14</v>
-      </c>
-      <c r="E165" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F165" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G165" t="s">
-        <v>527</v>
+        <v>388</v>
       </c>
       <c r="H165" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J165" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K165" t="s">
         <v>528</v>
@@ -8821,26 +8821,26 @@
       <c r="B166" t="s">
         <v>13</v>
       </c>
+      <c r="C166" t="s">
+        <v>530</v>
+      </c>
       <c r="D166" t="s">
-        <v>14</v>
-      </c>
-      <c r="E166" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F166" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G166" t="s">
-        <v>530</v>
+        <v>388</v>
       </c>
       <c r="H166" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J166" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K166" t="s">
         <v>531</v>
@@ -8856,26 +8856,26 @@
       <c r="B167" t="s">
         <v>13</v>
       </c>
+      <c r="C167" t="s">
+        <v>533</v>
+      </c>
       <c r="D167" t="s">
-        <v>14</v>
-      </c>
-      <c r="E167" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F167" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G167" t="s">
-        <v>533</v>
+        <v>388</v>
       </c>
       <c r="H167" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I167" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J167" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K167" t="s">
         <v>534</v>
@@ -8891,26 +8891,26 @@
       <c r="B168" t="s">
         <v>13</v>
       </c>
+      <c r="C168" t="s">
+        <v>536</v>
+      </c>
       <c r="D168" t="s">
-        <v>14</v>
-      </c>
-      <c r="E168" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F168" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G168" t="s">
-        <v>536</v>
+        <v>388</v>
       </c>
       <c r="H168" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I168" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="J168" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K168" t="s">
         <v>537</v>
@@ -8926,26 +8926,26 @@
       <c r="B169" t="s">
         <v>13</v>
       </c>
+      <c r="C169" t="s">
+        <v>539</v>
+      </c>
       <c r="D169" t="s">
-        <v>14</v>
-      </c>
-      <c r="E169" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F169" t="s">
-        <v>15</v>
+        <v>488</v>
       </c>
       <c r="G169" t="s">
-        <v>539</v>
+        <v>388</v>
       </c>
       <c r="H169" t="s">
-        <v>488</v>
+        <v>18</v>
       </c>
       <c r="I169" t="s">
-        <v>388</v>
+        <v>32</v>
       </c>
       <c r="J169" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K169" t="s">
         <v>540</v>
@@ -8961,32 +8961,32 @@
       <c r="B170" t="s">
         <v>13</v>
       </c>
+      <c r="C170" t="s">
+        <v>542</v>
+      </c>
       <c r="D170" t="s">
-        <v>14</v>
-      </c>
-      <c r="E170" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F170" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="G170" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="H170" t="s">
-        <v>543</v>
+        <v>18</v>
       </c>
       <c r="I170" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J170" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K170" t="s">
         <v>545</v>
       </c>
       <c r="L170" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="171" spans="1:12">
@@ -8996,32 +8996,32 @@
       <c r="B171" t="s">
         <v>13</v>
       </c>
+      <c r="C171" t="s">
+        <v>547</v>
+      </c>
       <c r="D171" t="s">
-        <v>14</v>
-      </c>
-      <c r="E171" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F171" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="G171" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H171" t="s">
-        <v>543</v>
+        <v>18</v>
       </c>
       <c r="I171" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J171" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K171" t="s">
         <v>548</v>
       </c>
       <c r="L171" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -9031,32 +9031,32 @@
       <c r="B172" t="s">
         <v>13</v>
       </c>
+      <c r="C172" t="s">
+        <v>550</v>
+      </c>
       <c r="D172" t="s">
-        <v>14</v>
-      </c>
-      <c r="E172" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F172" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="G172" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H172" t="s">
-        <v>543</v>
+        <v>18</v>
       </c>
       <c r="I172" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J172" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K172" t="s">
         <v>551</v>
       </c>
       <c r="L172" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -9066,32 +9066,32 @@
       <c r="B173" t="s">
         <v>13</v>
       </c>
+      <c r="C173" t="s">
+        <v>553</v>
+      </c>
       <c r="D173" t="s">
-        <v>14</v>
-      </c>
-      <c r="E173" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F173" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="G173" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="H173" t="s">
-        <v>543</v>
+        <v>18</v>
       </c>
       <c r="I173" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J173" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K173" t="s">
         <v>554</v>
       </c>
       <c r="L173" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="174" spans="1:12">
@@ -9101,32 +9101,32 @@
       <c r="B174" t="s">
         <v>13</v>
       </c>
+      <c r="C174" t="s">
+        <v>556</v>
+      </c>
       <c r="D174" t="s">
-        <v>14</v>
-      </c>
-      <c r="E174" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F174" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="G174" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="H174" t="s">
-        <v>543</v>
+        <v>18</v>
       </c>
       <c r="I174" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J174" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K174" t="s">
         <v>557</v>
       </c>
       <c r="L174" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -9136,32 +9136,32 @@
       <c r="B175" t="s">
         <v>13</v>
       </c>
+      <c r="C175" t="s">
+        <v>559</v>
+      </c>
       <c r="D175" t="s">
-        <v>31</v>
-      </c>
-      <c r="E175" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F175" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="G175" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="H175" t="s">
-        <v>543</v>
+        <v>18</v>
       </c>
       <c r="I175" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J175" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K175" t="s">
         <v>560</v>
       </c>
       <c r="L175" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -9171,32 +9171,32 @@
       <c r="B176" t="s">
         <v>13</v>
       </c>
+      <c r="C176" t="s">
+        <v>562</v>
+      </c>
       <c r="D176" t="s">
-        <v>14</v>
-      </c>
-      <c r="E176" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F176" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="G176" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="H176" t="s">
-        <v>543</v>
+        <v>18</v>
       </c>
       <c r="I176" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J176" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K176" t="s">
         <v>563</v>
       </c>
       <c r="L176" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -9206,32 +9206,32 @@
       <c r="B177" t="s">
         <v>13</v>
       </c>
+      <c r="C177" t="s">
+        <v>565</v>
+      </c>
       <c r="D177" t="s">
-        <v>14</v>
-      </c>
-      <c r="E177" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F177" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="G177" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
       <c r="H177" t="s">
-        <v>543</v>
+        <v>18</v>
       </c>
       <c r="I177" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J177" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K177" t="s">
         <v>566</v>
       </c>
       <c r="L177" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -9241,32 +9241,32 @@
       <c r="B178" t="s">
         <v>13</v>
       </c>
+      <c r="C178" t="s">
+        <v>568</v>
+      </c>
       <c r="D178" t="s">
-        <v>14</v>
-      </c>
-      <c r="E178" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F178" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="G178" t="s">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="H178" t="s">
-        <v>543</v>
+        <v>18</v>
       </c>
       <c r="I178" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J178" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K178" t="s">
         <v>569</v>
       </c>
       <c r="L178" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -9276,32 +9276,32 @@
       <c r="B179" t="s">
         <v>13</v>
       </c>
+      <c r="C179" t="s">
+        <v>571</v>
+      </c>
       <c r="D179" t="s">
-        <v>14</v>
-      </c>
-      <c r="E179" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F179" t="s">
-        <v>366</v>
+        <v>543</v>
       </c>
       <c r="G179" t="s">
-        <v>571</v>
+        <v>544</v>
       </c>
       <c r="H179" t="s">
-        <v>543</v>
+        <v>18</v>
       </c>
       <c r="I179" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J179" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K179" t="s">
         <v>572</v>
       </c>
       <c r="L179" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -9311,32 +9311,32 @@
       <c r="B180" t="s">
         <v>13</v>
       </c>
+      <c r="C180" t="s">
+        <v>574</v>
+      </c>
       <c r="D180" t="s">
-        <v>14</v>
-      </c>
-      <c r="E180" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F180" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G180" t="s">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="H180" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I180" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J180" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K180" t="s">
         <v>576</v>
       </c>
       <c r="L180" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -9346,32 +9346,32 @@
       <c r="B181" t="s">
         <v>13</v>
       </c>
+      <c r="C181" t="s">
+        <v>578</v>
+      </c>
       <c r="D181" t="s">
-        <v>14</v>
-      </c>
-      <c r="E181" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F181" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G181" t="s">
-        <v>578</v>
+        <v>544</v>
       </c>
       <c r="H181" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I181" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J181" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K181" t="s">
         <v>579</v>
       </c>
       <c r="L181" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -9381,32 +9381,32 @@
       <c r="B182" t="s">
         <v>13</v>
       </c>
+      <c r="C182" t="s">
+        <v>581</v>
+      </c>
       <c r="D182" t="s">
-        <v>14</v>
-      </c>
-      <c r="E182" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F182" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G182" t="s">
-        <v>581</v>
+        <v>544</v>
       </c>
       <c r="H182" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I182" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J182" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K182" t="s">
         <v>582</v>
       </c>
       <c r="L182" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -9416,29 +9416,29 @@
       <c r="B183" t="s">
         <v>584</v>
       </c>
-      <c r="C183" t="s">
+      <c r="D183" t="s">
+        <v>15</v>
+      </c>
+      <c r="E183" t="s">
         <v>585</v>
       </c>
-      <c r="D183" t="s">
-        <v>14</v>
-      </c>
-      <c r="E183" t="s">
-        <v>14</v>
-      </c>
       <c r="F183" t="s">
-        <v>366</v>
+        <v>575</v>
+      </c>
+      <c r="G183" t="s">
+        <v>544</v>
       </c>
       <c r="H183" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I183" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J183" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L183" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -9448,32 +9448,32 @@
       <c r="B184" t="s">
         <v>13</v>
       </c>
+      <c r="C184" t="s">
+        <v>587</v>
+      </c>
       <c r="D184" t="s">
-        <v>14</v>
-      </c>
-      <c r="E184" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F184" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G184" t="s">
-        <v>587</v>
+        <v>544</v>
       </c>
       <c r="H184" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I184" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J184" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K184" t="s">
         <v>588</v>
       </c>
       <c r="L184" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -9483,32 +9483,32 @@
       <c r="B185" t="s">
         <v>13</v>
       </c>
+      <c r="C185" t="s">
+        <v>590</v>
+      </c>
       <c r="D185" t="s">
-        <v>14</v>
-      </c>
-      <c r="E185" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F185" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G185" t="s">
-        <v>590</v>
+        <v>544</v>
       </c>
       <c r="H185" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I185" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J185" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K185" t="s">
         <v>591</v>
       </c>
       <c r="L185" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -9518,32 +9518,32 @@
       <c r="B186" t="s">
         <v>13</v>
       </c>
+      <c r="C186" t="s">
+        <v>593</v>
+      </c>
       <c r="D186" t="s">
-        <v>14</v>
-      </c>
-      <c r="E186" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F186" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G186" t="s">
-        <v>593</v>
+        <v>544</v>
       </c>
       <c r="H186" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I186" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J186" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K186" t="s">
         <v>594</v>
       </c>
       <c r="L186" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -9553,32 +9553,32 @@
       <c r="B187" t="s">
         <v>13</v>
       </c>
+      <c r="C187" t="s">
+        <v>596</v>
+      </c>
       <c r="D187" t="s">
-        <v>14</v>
-      </c>
-      <c r="E187" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F187" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G187" t="s">
-        <v>596</v>
+        <v>544</v>
       </c>
       <c r="H187" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I187" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J187" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K187" t="s">
         <v>597</v>
       </c>
       <c r="L187" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -9588,32 +9588,32 @@
       <c r="B188" t="s">
         <v>13</v>
       </c>
+      <c r="C188" t="s">
+        <v>599</v>
+      </c>
       <c r="D188" t="s">
-        <v>14</v>
-      </c>
-      <c r="E188" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F188" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G188" t="s">
-        <v>599</v>
+        <v>544</v>
       </c>
       <c r="H188" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I188" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J188" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K188" t="s">
         <v>600</v>
       </c>
       <c r="L188" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -9623,32 +9623,32 @@
       <c r="B189" t="s">
         <v>13</v>
       </c>
+      <c r="C189" t="s">
+        <v>602</v>
+      </c>
       <c r="D189" t="s">
-        <v>14</v>
-      </c>
-      <c r="E189" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F189" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G189" t="s">
-        <v>602</v>
+        <v>544</v>
       </c>
       <c r="H189" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I189" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J189" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K189" t="s">
         <v>603</v>
       </c>
       <c r="L189" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -9658,32 +9658,32 @@
       <c r="B190" t="s">
         <v>13</v>
       </c>
+      <c r="C190" t="s">
+        <v>605</v>
+      </c>
       <c r="D190" t="s">
-        <v>14</v>
-      </c>
-      <c r="E190" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F190" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G190" t="s">
-        <v>605</v>
+        <v>544</v>
       </c>
       <c r="H190" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I190" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J190" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K190" t="s">
         <v>606</v>
       </c>
       <c r="L190" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -9693,32 +9693,32 @@
       <c r="B191" t="s">
         <v>13</v>
       </c>
+      <c r="C191" t="s">
+        <v>608</v>
+      </c>
       <c r="D191" t="s">
-        <v>14</v>
-      </c>
-      <c r="E191" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F191" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G191" t="s">
-        <v>608</v>
+        <v>544</v>
       </c>
       <c r="H191" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I191" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J191" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K191" t="s">
         <v>609</v>
       </c>
       <c r="L191" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -9728,32 +9728,32 @@
       <c r="B192" t="s">
         <v>13</v>
       </c>
+      <c r="C192" t="s">
+        <v>611</v>
+      </c>
       <c r="D192" t="s">
-        <v>14</v>
-      </c>
-      <c r="E192" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F192" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G192" t="s">
-        <v>611</v>
+        <v>544</v>
       </c>
       <c r="H192" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I192" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J192" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K192" t="s">
         <v>612</v>
       </c>
       <c r="L192" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -9763,32 +9763,32 @@
       <c r="B193" t="s">
         <v>13</v>
       </c>
+      <c r="C193" t="s">
+        <v>614</v>
+      </c>
       <c r="D193" t="s">
-        <v>14</v>
-      </c>
-      <c r="E193" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F193" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G193" t="s">
-        <v>614</v>
+        <v>544</v>
       </c>
       <c r="H193" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I193" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J193" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K193" t="s">
         <v>615</v>
       </c>
       <c r="L193" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -9798,32 +9798,32 @@
       <c r="B194" t="s">
         <v>13</v>
       </c>
+      <c r="C194" t="s">
+        <v>617</v>
+      </c>
       <c r="D194" t="s">
-        <v>14</v>
-      </c>
-      <c r="E194" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F194" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G194" t="s">
-        <v>617</v>
+        <v>544</v>
       </c>
       <c r="H194" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I194" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J194" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K194" t="s">
         <v>618</v>
       </c>
       <c r="L194" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -9833,32 +9833,32 @@
       <c r="B195" t="s">
         <v>13</v>
       </c>
+      <c r="C195" t="s">
+        <v>620</v>
+      </c>
       <c r="D195" t="s">
-        <v>14</v>
-      </c>
-      <c r="E195" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F195" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G195" t="s">
-        <v>620</v>
+        <v>544</v>
       </c>
       <c r="H195" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I195" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J195" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K195" t="s">
         <v>621</v>
       </c>
       <c r="L195" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -9868,32 +9868,32 @@
       <c r="B196" t="s">
         <v>13</v>
       </c>
+      <c r="C196" t="s">
+        <v>623</v>
+      </c>
       <c r="D196" t="s">
-        <v>14</v>
-      </c>
-      <c r="E196" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F196" t="s">
-        <v>366</v>
+        <v>575</v>
       </c>
       <c r="G196" t="s">
-        <v>623</v>
+        <v>544</v>
       </c>
       <c r="H196" t="s">
-        <v>575</v>
+        <v>18</v>
       </c>
       <c r="I196" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J196" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K196" t="s">
         <v>624</v>
       </c>
       <c r="L196" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -9903,32 +9903,32 @@
       <c r="B197" t="s">
         <v>13</v>
       </c>
+      <c r="C197" t="s">
+        <v>626</v>
+      </c>
       <c r="D197" t="s">
-        <v>14</v>
-      </c>
-      <c r="E197" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F197" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G197" t="s">
-        <v>626</v>
+        <v>544</v>
       </c>
       <c r="H197" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I197" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J197" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K197" t="s">
         <v>628</v>
       </c>
       <c r="L197" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -9938,32 +9938,32 @@
       <c r="B198" t="s">
         <v>13</v>
       </c>
+      <c r="C198" t="s">
+        <v>630</v>
+      </c>
       <c r="D198" t="s">
-        <v>14</v>
-      </c>
-      <c r="E198" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F198" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G198" t="s">
-        <v>630</v>
+        <v>544</v>
       </c>
       <c r="H198" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I198" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J198" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K198" t="s">
         <v>631</v>
       </c>
       <c r="L198" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -9973,32 +9973,32 @@
       <c r="B199" t="s">
         <v>13</v>
       </c>
+      <c r="C199" t="s">
+        <v>633</v>
+      </c>
       <c r="D199" t="s">
-        <v>14</v>
-      </c>
-      <c r="E199" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F199" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G199" t="s">
-        <v>633</v>
+        <v>544</v>
       </c>
       <c r="H199" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I199" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J199" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K199" t="s">
         <v>634</v>
       </c>
       <c r="L199" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -10008,32 +10008,32 @@
       <c r="B200" t="s">
         <v>13</v>
       </c>
+      <c r="C200" t="s">
+        <v>636</v>
+      </c>
       <c r="D200" t="s">
-        <v>14</v>
-      </c>
-      <c r="E200" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F200" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G200" t="s">
-        <v>636</v>
+        <v>544</v>
       </c>
       <c r="H200" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I200" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J200" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K200" t="s">
         <v>637</v>
       </c>
       <c r="L200" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -10043,32 +10043,32 @@
       <c r="B201" t="s">
         <v>13</v>
       </c>
+      <c r="C201" t="s">
+        <v>639</v>
+      </c>
       <c r="D201" t="s">
-        <v>14</v>
-      </c>
-      <c r="E201" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F201" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G201" t="s">
-        <v>639</v>
+        <v>544</v>
       </c>
       <c r="H201" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I201" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J201" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K201" t="s">
         <v>640</v>
       </c>
       <c r="L201" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -10078,32 +10078,32 @@
       <c r="B202" t="s">
         <v>13</v>
       </c>
+      <c r="C202" t="s">
+        <v>642</v>
+      </c>
       <c r="D202" t="s">
-        <v>14</v>
-      </c>
-      <c r="E202" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F202" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G202" t="s">
-        <v>642</v>
+        <v>544</v>
       </c>
       <c r="H202" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I202" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J202" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K202" t="s">
         <v>643</v>
       </c>
       <c r="L202" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -10113,32 +10113,32 @@
       <c r="B203" t="s">
         <v>13</v>
       </c>
+      <c r="C203" t="s">
+        <v>645</v>
+      </c>
       <c r="D203" t="s">
-        <v>14</v>
-      </c>
-      <c r="E203" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F203" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G203" t="s">
-        <v>645</v>
+        <v>544</v>
       </c>
       <c r="H203" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I203" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J203" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K203" t="s">
         <v>646</v>
       </c>
       <c r="L203" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -10148,32 +10148,32 @@
       <c r="B204" t="s">
         <v>13</v>
       </c>
+      <c r="C204" t="s">
+        <v>648</v>
+      </c>
       <c r="D204" t="s">
-        <v>14</v>
-      </c>
-      <c r="E204" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F204" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G204" t="s">
-        <v>648</v>
+        <v>544</v>
       </c>
       <c r="H204" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I204" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J204" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K204" t="s">
         <v>649</v>
       </c>
       <c r="L204" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -10183,32 +10183,32 @@
       <c r="B205" t="s">
         <v>13</v>
       </c>
+      <c r="C205" t="s">
+        <v>651</v>
+      </c>
       <c r="D205" t="s">
-        <v>14</v>
-      </c>
-      <c r="E205" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F205" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G205" t="s">
-        <v>651</v>
+        <v>544</v>
       </c>
       <c r="H205" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I205" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J205" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K205" t="s">
         <v>652</v>
       </c>
       <c r="L205" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -10218,32 +10218,32 @@
       <c r="B206" t="s">
         <v>13</v>
       </c>
+      <c r="C206" t="s">
+        <v>654</v>
+      </c>
       <c r="D206" t="s">
-        <v>14</v>
-      </c>
-      <c r="E206" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F206" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G206" t="s">
-        <v>654</v>
+        <v>544</v>
       </c>
       <c r="H206" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I206" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J206" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K206" t="s">
         <v>655</v>
       </c>
       <c r="L206" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -10253,32 +10253,32 @@
       <c r="B207" t="s">
         <v>13</v>
       </c>
+      <c r="C207" t="s">
+        <v>657</v>
+      </c>
       <c r="D207" t="s">
-        <v>31</v>
-      </c>
-      <c r="E207" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F207" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G207" t="s">
-        <v>657</v>
+        <v>544</v>
       </c>
       <c r="H207" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I207" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J207" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K207" t="s">
         <v>658</v>
       </c>
       <c r="L207" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -10288,32 +10288,32 @@
       <c r="B208" t="s">
         <v>13</v>
       </c>
+      <c r="C208" t="s">
+        <v>660</v>
+      </c>
       <c r="D208" t="s">
-        <v>14</v>
-      </c>
-      <c r="E208" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F208" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G208" t="s">
-        <v>660</v>
+        <v>544</v>
       </c>
       <c r="H208" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I208" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J208" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K208" t="s">
         <v>661</v>
       </c>
       <c r="L208" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -10323,32 +10323,32 @@
       <c r="B209" t="s">
         <v>13</v>
       </c>
+      <c r="C209" t="s">
+        <v>663</v>
+      </c>
       <c r="D209" t="s">
-        <v>14</v>
-      </c>
-      <c r="E209" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F209" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G209" t="s">
-        <v>663</v>
+        <v>544</v>
       </c>
       <c r="H209" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I209" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J209" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K209" t="s">
         <v>664</v>
       </c>
       <c r="L209" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -10358,32 +10358,32 @@
       <c r="B210" t="s">
         <v>13</v>
       </c>
+      <c r="C210" t="s">
+        <v>666</v>
+      </c>
       <c r="D210" t="s">
-        <v>14</v>
-      </c>
-      <c r="E210" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F210" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G210" t="s">
-        <v>666</v>
+        <v>544</v>
       </c>
       <c r="H210" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I210" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J210" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K210" t="s">
         <v>667</v>
       </c>
       <c r="L210" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -10393,32 +10393,32 @@
       <c r="B211" t="s">
         <v>13</v>
       </c>
+      <c r="C211" t="s">
+        <v>669</v>
+      </c>
       <c r="D211" t="s">
-        <v>14</v>
-      </c>
-      <c r="E211" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F211" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G211" t="s">
-        <v>669</v>
+        <v>544</v>
       </c>
       <c r="H211" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I211" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J211" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K211" t="s">
         <v>670</v>
       </c>
       <c r="L211" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -10428,32 +10428,32 @@
       <c r="B212" t="s">
         <v>13</v>
       </c>
+      <c r="C212" t="s">
+        <v>672</v>
+      </c>
       <c r="D212" t="s">
-        <v>14</v>
-      </c>
-      <c r="E212" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F212" t="s">
-        <v>366</v>
+        <v>627</v>
       </c>
       <c r="G212" t="s">
-        <v>672</v>
+        <v>544</v>
       </c>
       <c r="H212" t="s">
-        <v>627</v>
+        <v>18</v>
       </c>
       <c r="I212" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J212" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K212" t="s">
         <v>673</v>
       </c>
       <c r="L212" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -10463,32 +10463,32 @@
       <c r="B213" t="s">
         <v>13</v>
       </c>
+      <c r="C213" t="s">
+        <v>675</v>
+      </c>
       <c r="D213" t="s">
-        <v>14</v>
-      </c>
-      <c r="E213" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F213" t="s">
-        <v>366</v>
+        <v>676</v>
       </c>
       <c r="G213" t="s">
-        <v>675</v>
+        <v>544</v>
       </c>
       <c r="H213" t="s">
-        <v>676</v>
+        <v>18</v>
       </c>
       <c r="I213" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J213" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K213" t="s">
         <v>677</v>
       </c>
       <c r="L213" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -10498,32 +10498,32 @@
       <c r="B214" t="s">
         <v>13</v>
       </c>
+      <c r="C214" t="s">
+        <v>679</v>
+      </c>
       <c r="D214" t="s">
-        <v>14</v>
-      </c>
-      <c r="E214" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F214" t="s">
-        <v>366</v>
+        <v>676</v>
       </c>
       <c r="G214" t="s">
-        <v>679</v>
+        <v>544</v>
       </c>
       <c r="H214" t="s">
-        <v>676</v>
+        <v>18</v>
       </c>
       <c r="I214" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J214" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K214" t="s">
         <v>680</v>
       </c>
       <c r="L214" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -10533,32 +10533,32 @@
       <c r="B215" t="s">
         <v>13</v>
       </c>
+      <c r="C215" t="s">
+        <v>682</v>
+      </c>
       <c r="D215" t="s">
-        <v>14</v>
-      </c>
-      <c r="E215" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F215" t="s">
-        <v>366</v>
+        <v>676</v>
       </c>
       <c r="G215" t="s">
-        <v>682</v>
+        <v>544</v>
       </c>
       <c r="H215" t="s">
-        <v>676</v>
+        <v>18</v>
       </c>
       <c r="I215" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J215" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K215" t="s">
         <v>683</v>
       </c>
       <c r="L215" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -10568,32 +10568,32 @@
       <c r="B216" t="s">
         <v>13</v>
       </c>
+      <c r="C216" t="s">
+        <v>685</v>
+      </c>
       <c r="D216" t="s">
-        <v>14</v>
-      </c>
-      <c r="E216" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F216" t="s">
-        <v>366</v>
+        <v>676</v>
       </c>
       <c r="G216" t="s">
-        <v>685</v>
+        <v>544</v>
       </c>
       <c r="H216" t="s">
-        <v>676</v>
+        <v>18</v>
       </c>
       <c r="I216" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J216" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K216" t="s">
         <v>686</v>
       </c>
       <c r="L216" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -10603,32 +10603,32 @@
       <c r="B217" t="s">
         <v>13</v>
       </c>
+      <c r="C217" t="s">
+        <v>688</v>
+      </c>
       <c r="D217" t="s">
-        <v>14</v>
-      </c>
-      <c r="E217" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F217" t="s">
-        <v>366</v>
+        <v>676</v>
       </c>
       <c r="G217" t="s">
-        <v>688</v>
+        <v>544</v>
       </c>
       <c r="H217" t="s">
-        <v>676</v>
+        <v>18</v>
       </c>
       <c r="I217" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J217" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K217" t="s">
         <v>689</v>
       </c>
       <c r="L217" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -10638,32 +10638,32 @@
       <c r="B218" t="s">
         <v>13</v>
       </c>
+      <c r="C218" t="s">
+        <v>691</v>
+      </c>
       <c r="D218" t="s">
-        <v>14</v>
-      </c>
-      <c r="E218" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F218" t="s">
-        <v>366</v>
+        <v>676</v>
       </c>
       <c r="G218" t="s">
-        <v>691</v>
+        <v>544</v>
       </c>
       <c r="H218" t="s">
-        <v>676</v>
+        <v>18</v>
       </c>
       <c r="I218" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J218" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K218" t="s">
         <v>692</v>
       </c>
       <c r="L218" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -10673,32 +10673,32 @@
       <c r="B219" t="s">
         <v>13</v>
       </c>
+      <c r="C219" t="s">
+        <v>694</v>
+      </c>
       <c r="D219" t="s">
-        <v>14</v>
-      </c>
-      <c r="E219" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F219" t="s">
-        <v>366</v>
+        <v>676</v>
       </c>
       <c r="G219" t="s">
-        <v>694</v>
+        <v>544</v>
       </c>
       <c r="H219" t="s">
-        <v>676</v>
+        <v>18</v>
       </c>
       <c r="I219" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J219" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K219" t="s">
         <v>695</v>
       </c>
       <c r="L219" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -10708,32 +10708,32 @@
       <c r="B220" t="s">
         <v>13</v>
       </c>
+      <c r="C220" t="s">
+        <v>697</v>
+      </c>
       <c r="D220" t="s">
-        <v>14</v>
-      </c>
-      <c r="E220" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F220" t="s">
-        <v>366</v>
+        <v>676</v>
       </c>
       <c r="G220" t="s">
-        <v>697</v>
+        <v>544</v>
       </c>
       <c r="H220" t="s">
-        <v>676</v>
+        <v>18</v>
       </c>
       <c r="I220" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J220" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K220" t="s">
         <v>698</v>
       </c>
       <c r="L220" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -10743,32 +10743,32 @@
       <c r="B221" t="s">
         <v>13</v>
       </c>
+      <c r="C221" t="s">
+        <v>700</v>
+      </c>
       <c r="D221" t="s">
-        <v>14</v>
-      </c>
-      <c r="E221" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F221" t="s">
-        <v>366</v>
+        <v>676</v>
       </c>
       <c r="G221" t="s">
-        <v>700</v>
+        <v>544</v>
       </c>
       <c r="H221" t="s">
-        <v>676</v>
+        <v>18</v>
       </c>
       <c r="I221" t="s">
-        <v>544</v>
+        <v>18</v>
       </c>
       <c r="J221" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K221" t="s">
         <v>701</v>
       </c>
       <c r="L221" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -10778,32 +10778,32 @@
       <c r="B222" t="s">
         <v>13</v>
       </c>
+      <c r="C222" t="s">
+        <v>703</v>
+      </c>
       <c r="D222" t="s">
-        <v>14</v>
-      </c>
-      <c r="E222" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F222" t="s">
-        <v>366</v>
+        <v>704</v>
       </c>
       <c r="G222" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H222" t="s">
-        <v>704</v>
+        <v>18</v>
       </c>
       <c r="I222" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J222" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K222" t="s">
         <v>706</v>
       </c>
       <c r="L222" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -10813,32 +10813,32 @@
       <c r="B223" t="s">
         <v>13</v>
       </c>
+      <c r="C223" t="s">
+        <v>708</v>
+      </c>
       <c r="D223" t="s">
-        <v>14</v>
-      </c>
-      <c r="E223" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F223" t="s">
-        <v>366</v>
+        <v>704</v>
       </c>
       <c r="G223" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="H223" t="s">
-        <v>704</v>
+        <v>18</v>
       </c>
       <c r="I223" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J223" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K223" t="s">
         <v>709</v>
       </c>
       <c r="L223" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -10848,32 +10848,32 @@
       <c r="B224" t="s">
         <v>13</v>
       </c>
+      <c r="C224" t="s">
+        <v>711</v>
+      </c>
       <c r="D224" t="s">
-        <v>14</v>
-      </c>
-      <c r="E224" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F224" t="s">
-        <v>366</v>
+        <v>704</v>
       </c>
       <c r="G224" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="H224" t="s">
-        <v>704</v>
+        <v>18</v>
       </c>
       <c r="I224" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J224" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K224" t="s">
         <v>712</v>
       </c>
       <c r="L224" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -10883,32 +10883,32 @@
       <c r="B225" t="s">
         <v>13</v>
       </c>
+      <c r="C225" t="s">
+        <v>714</v>
+      </c>
       <c r="D225" t="s">
-        <v>14</v>
-      </c>
-      <c r="E225" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F225" t="s">
-        <v>366</v>
+        <v>704</v>
       </c>
       <c r="G225" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="H225" t="s">
-        <v>704</v>
+        <v>18</v>
       </c>
       <c r="I225" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J225" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K225" t="s">
         <v>715</v>
       </c>
       <c r="L225" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -10918,32 +10918,32 @@
       <c r="B226" t="s">
         <v>13</v>
       </c>
+      <c r="C226" t="s">
+        <v>717</v>
+      </c>
       <c r="D226" t="s">
-        <v>14</v>
-      </c>
-      <c r="E226" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F226" t="s">
-        <v>366</v>
+        <v>704</v>
       </c>
       <c r="G226" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="H226" t="s">
-        <v>704</v>
+        <v>18</v>
       </c>
       <c r="I226" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J226" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K226" t="s">
         <v>718</v>
       </c>
       <c r="L226" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -10953,32 +10953,32 @@
       <c r="B227" t="s">
         <v>13</v>
       </c>
+      <c r="C227" t="s">
+        <v>720</v>
+      </c>
       <c r="D227" t="s">
-        <v>14</v>
-      </c>
-      <c r="E227" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F227" t="s">
-        <v>366</v>
+        <v>704</v>
       </c>
       <c r="G227" t="s">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="H227" t="s">
-        <v>704</v>
+        <v>18</v>
       </c>
       <c r="I227" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J227" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K227" t="s">
         <v>721</v>
       </c>
       <c r="L227" t="s">
-        <v>20</v>
+        <v>369</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -10988,26 +10988,26 @@
       <c r="B228" t="s">
         <v>13</v>
       </c>
+      <c r="C228" t="s">
+        <v>723</v>
+      </c>
       <c r="D228" t="s">
-        <v>14</v>
-      </c>
-      <c r="E228" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F228" t="s">
-        <v>15</v>
+        <v>724</v>
       </c>
       <c r="G228" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="H228" t="s">
-        <v>724</v>
+        <v>32</v>
       </c>
       <c r="I228" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J228" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K228" t="s">
         <v>725</v>
@@ -11023,26 +11023,26 @@
       <c r="B229" t="s">
         <v>13</v>
       </c>
+      <c r="C229" t="s">
+        <v>727</v>
+      </c>
       <c r="D229" t="s">
-        <v>14</v>
-      </c>
-      <c r="E229" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F229" t="s">
-        <v>15</v>
+        <v>724</v>
       </c>
       <c r="G229" t="s">
-        <v>727</v>
+        <v>705</v>
       </c>
       <c r="H229" t="s">
-        <v>724</v>
+        <v>32</v>
       </c>
       <c r="I229" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J229" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K229" t="s">
         <v>728</v>
@@ -11058,26 +11058,26 @@
       <c r="B230" t="s">
         <v>13</v>
       </c>
+      <c r="C230" t="s">
+        <v>730</v>
+      </c>
       <c r="D230" t="s">
-        <v>14</v>
-      </c>
-      <c r="E230" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F230" t="s">
-        <v>15</v>
+        <v>724</v>
       </c>
       <c r="G230" t="s">
-        <v>730</v>
+        <v>705</v>
       </c>
       <c r="H230" t="s">
-        <v>724</v>
+        <v>32</v>
       </c>
       <c r="I230" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J230" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K230" t="s">
         <v>731</v>
@@ -11093,26 +11093,26 @@
       <c r="B231" t="s">
         <v>13</v>
       </c>
+      <c r="C231" t="s">
+        <v>733</v>
+      </c>
       <c r="D231" t="s">
-        <v>14</v>
-      </c>
-      <c r="E231" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F231" t="s">
-        <v>15</v>
+        <v>724</v>
       </c>
       <c r="G231" t="s">
-        <v>733</v>
+        <v>705</v>
       </c>
       <c r="H231" t="s">
-        <v>724</v>
+        <v>32</v>
       </c>
       <c r="I231" t="s">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="J231" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K231" t="s">
         <v>734</v>
@@ -11128,26 +11128,26 @@
       <c r="B232" t="s">
         <v>13</v>
       </c>
+      <c r="C232" t="s">
+        <v>736</v>
+      </c>
       <c r="D232" t="s">
-        <v>14</v>
-      </c>
-      <c r="E232" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F232" t="s">
-        <v>15</v>
+        <v>724</v>
       </c>
       <c r="G232" t="s">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="H232" t="s">
-        <v>724</v>
+        <v>32</v>
       </c>
       <c r="I232" t="s">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="J232" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K232" t="s">
         <v>737</v>
@@ -11163,26 +11163,26 @@
       <c r="B233" t="s">
         <v>13</v>
       </c>
+      <c r="C233" t="s">
+        <v>739</v>
+      </c>
       <c r="D233" t="s">
-        <v>14</v>
-      </c>
-      <c r="E233" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F233" t="s">
-        <v>15</v>
+        <v>740</v>
       </c>
       <c r="G233" t="s">
-        <v>739</v>
+        <v>705</v>
       </c>
       <c r="H233" t="s">
-        <v>740</v>
+        <v>32</v>
       </c>
       <c r="I233" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J233" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K233" t="s">
         <v>741</v>
@@ -11198,26 +11198,26 @@
       <c r="B234" t="s">
         <v>13</v>
       </c>
+      <c r="C234" t="s">
+        <v>743</v>
+      </c>
       <c r="D234" t="s">
-        <v>14</v>
-      </c>
-      <c r="E234" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F234" t="s">
-        <v>15</v>
+        <v>740</v>
       </c>
       <c r="G234" t="s">
-        <v>743</v>
+        <v>705</v>
       </c>
       <c r="H234" t="s">
-        <v>740</v>
+        <v>32</v>
       </c>
       <c r="I234" t="s">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="J234" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K234" t="s">
         <v>744</v>
@@ -11233,26 +11233,26 @@
       <c r="B235" t="s">
         <v>13</v>
       </c>
+      <c r="C235" t="s">
+        <v>746</v>
+      </c>
       <c r="D235" t="s">
-        <v>14</v>
-      </c>
-      <c r="E235" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F235" t="s">
-        <v>15</v>
+        <v>740</v>
       </c>
       <c r="G235" t="s">
-        <v>746</v>
+        <v>705</v>
       </c>
       <c r="H235" t="s">
-        <v>740</v>
+        <v>32</v>
       </c>
       <c r="I235" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J235" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K235" t="s">
         <v>747</v>
@@ -11268,26 +11268,26 @@
       <c r="B236" t="s">
         <v>13</v>
       </c>
+      <c r="C236" t="s">
+        <v>749</v>
+      </c>
       <c r="D236" t="s">
-        <v>14</v>
-      </c>
-      <c r="E236" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F236" t="s">
-        <v>15</v>
+        <v>740</v>
       </c>
       <c r="G236" t="s">
-        <v>749</v>
+        <v>705</v>
       </c>
       <c r="H236" t="s">
-        <v>740</v>
+        <v>32</v>
       </c>
       <c r="I236" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J236" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K236" t="s">
         <v>750</v>
@@ -11303,26 +11303,26 @@
       <c r="B237" t="s">
         <v>13</v>
       </c>
+      <c r="C237" t="s">
+        <v>752</v>
+      </c>
       <c r="D237" t="s">
-        <v>14</v>
-      </c>
-      <c r="E237" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F237" t="s">
-        <v>15</v>
+        <v>740</v>
       </c>
       <c r="G237" t="s">
-        <v>752</v>
+        <v>705</v>
       </c>
       <c r="H237" t="s">
-        <v>740</v>
+        <v>32</v>
       </c>
       <c r="I237" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J237" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K237" t="s">
         <v>753</v>
@@ -11338,26 +11338,26 @@
       <c r="B238" t="s">
         <v>13</v>
       </c>
+      <c r="C238" t="s">
+        <v>755</v>
+      </c>
       <c r="D238" t="s">
-        <v>14</v>
-      </c>
-      <c r="E238" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F238" t="s">
-        <v>15</v>
+        <v>740</v>
       </c>
       <c r="G238" t="s">
-        <v>755</v>
+        <v>705</v>
       </c>
       <c r="H238" t="s">
-        <v>740</v>
+        <v>32</v>
       </c>
       <c r="I238" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J238" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K238" t="s">
         <v>756</v>
@@ -11373,26 +11373,26 @@
       <c r="B239" t="s">
         <v>13</v>
       </c>
+      <c r="C239" t="s">
+        <v>758</v>
+      </c>
       <c r="D239" t="s">
-        <v>14</v>
-      </c>
-      <c r="E239" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F239" t="s">
-        <v>15</v>
+        <v>740</v>
       </c>
       <c r="G239" t="s">
-        <v>758</v>
+        <v>705</v>
       </c>
       <c r="H239" t="s">
-        <v>740</v>
+        <v>32</v>
       </c>
       <c r="I239" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J239" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K239" t="s">
         <v>759</v>
@@ -11408,26 +11408,26 @@
       <c r="B240" t="s">
         <v>13</v>
       </c>
+      <c r="C240" t="s">
+        <v>761</v>
+      </c>
       <c r="D240" t="s">
-        <v>14</v>
-      </c>
-      <c r="E240" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F240" t="s">
-        <v>15</v>
+        <v>740</v>
       </c>
       <c r="G240" t="s">
-        <v>761</v>
+        <v>705</v>
       </c>
       <c r="H240" t="s">
-        <v>740</v>
+        <v>18</v>
       </c>
       <c r="I240" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J240" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K240" t="s">
         <v>762</v>
@@ -11443,26 +11443,26 @@
       <c r="B241" t="s">
         <v>13</v>
       </c>
+      <c r="C241" t="s">
+        <v>764</v>
+      </c>
       <c r="D241" t="s">
-        <v>14</v>
-      </c>
-      <c r="E241" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F241" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="G241" t="s">
-        <v>764</v>
+        <v>705</v>
       </c>
       <c r="H241" t="s">
-        <v>765</v>
+        <v>32</v>
       </c>
       <c r="I241" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J241" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K241" t="s">
         <v>766</v>
@@ -11478,26 +11478,26 @@
       <c r="B242" t="s">
         <v>13</v>
       </c>
+      <c r="C242" t="s">
+        <v>768</v>
+      </c>
       <c r="D242" t="s">
-        <v>14</v>
-      </c>
-      <c r="E242" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F242" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="G242" t="s">
-        <v>768</v>
+        <v>705</v>
       </c>
       <c r="H242" t="s">
-        <v>765</v>
+        <v>32</v>
       </c>
       <c r="I242" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J242" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K242" t="s">
         <v>769</v>
@@ -11513,26 +11513,26 @@
       <c r="B243" t="s">
         <v>13</v>
       </c>
+      <c r="C243" t="s">
+        <v>771</v>
+      </c>
       <c r="D243" t="s">
-        <v>14</v>
-      </c>
-      <c r="E243" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F243" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="G243" t="s">
-        <v>771</v>
+        <v>705</v>
       </c>
       <c r="H243" t="s">
-        <v>765</v>
+        <v>32</v>
       </c>
       <c r="I243" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J243" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K243" t="s">
         <v>772</v>
@@ -11548,26 +11548,26 @@
       <c r="B244" t="s">
         <v>13</v>
       </c>
+      <c r="C244" t="s">
+        <v>774</v>
+      </c>
       <c r="D244" t="s">
-        <v>14</v>
-      </c>
-      <c r="E244" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F244" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="G244" t="s">
-        <v>774</v>
+        <v>705</v>
       </c>
       <c r="H244" t="s">
-        <v>765</v>
+        <v>32</v>
       </c>
       <c r="I244" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J244" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K244" t="s">
         <v>775</v>
@@ -11583,26 +11583,26 @@
       <c r="B245" t="s">
         <v>13</v>
       </c>
+      <c r="C245" t="s">
+        <v>777</v>
+      </c>
       <c r="D245" t="s">
-        <v>14</v>
-      </c>
-      <c r="E245" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F245" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="G245" t="s">
-        <v>777</v>
+        <v>705</v>
       </c>
       <c r="H245" t="s">
-        <v>765</v>
+        <v>18</v>
       </c>
       <c r="I245" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J245" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K245" t="s">
         <v>778</v>
@@ -11618,26 +11618,26 @@
       <c r="B246" t="s">
         <v>13</v>
       </c>
+      <c r="C246" t="s">
+        <v>780</v>
+      </c>
       <c r="D246" t="s">
-        <v>14</v>
-      </c>
-      <c r="E246" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F246" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="G246" t="s">
-        <v>780</v>
+        <v>705</v>
       </c>
       <c r="H246" t="s">
-        <v>765</v>
+        <v>32</v>
       </c>
       <c r="I246" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J246" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K246" t="s">
         <v>781</v>
@@ -11653,26 +11653,26 @@
       <c r="B247" t="s">
         <v>13</v>
       </c>
+      <c r="C247" t="s">
+        <v>783</v>
+      </c>
       <c r="D247" t="s">
-        <v>14</v>
-      </c>
-      <c r="E247" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F247" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="G247" t="s">
-        <v>783</v>
+        <v>705</v>
       </c>
       <c r="H247" t="s">
-        <v>765</v>
+        <v>18</v>
       </c>
       <c r="I247" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J247" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K247" t="s">
         <v>784</v>
@@ -11688,26 +11688,26 @@
       <c r="B248" t="s">
         <v>13</v>
       </c>
+      <c r="C248" t="s">
+        <v>786</v>
+      </c>
       <c r="D248" t="s">
-        <v>14</v>
-      </c>
-      <c r="E248" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F248" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="G248" t="s">
-        <v>786</v>
+        <v>705</v>
       </c>
       <c r="H248" t="s">
-        <v>765</v>
+        <v>32</v>
       </c>
       <c r="I248" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J248" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K248" t="s">
         <v>787</v>
@@ -11723,26 +11723,26 @@
       <c r="B249" t="s">
         <v>13</v>
       </c>
+      <c r="C249" t="s">
+        <v>789</v>
+      </c>
       <c r="D249" t="s">
-        <v>14</v>
-      </c>
-      <c r="E249" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F249" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="G249" t="s">
-        <v>789</v>
+        <v>705</v>
       </c>
       <c r="H249" t="s">
-        <v>765</v>
+        <v>32</v>
       </c>
       <c r="I249" t="s">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="J249" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K249" t="s">
         <v>790</v>
@@ -11758,26 +11758,26 @@
       <c r="B250" t="s">
         <v>13</v>
       </c>
+      <c r="C250" t="s">
+        <v>792</v>
+      </c>
       <c r="D250" t="s">
-        <v>14</v>
-      </c>
-      <c r="E250" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F250" t="s">
-        <v>15</v>
+        <v>765</v>
       </c>
       <c r="G250" t="s">
-        <v>792</v>
+        <v>705</v>
       </c>
       <c r="H250" t="s">
-        <v>765</v>
+        <v>18</v>
       </c>
       <c r="I250" t="s">
-        <v>705</v>
+        <v>18</v>
       </c>
       <c r="J250" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K250" t="s">
         <v>793</v>
